--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2727" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2718" uniqueCount="477">
   <si>
     <t>trade_time</t>
   </si>
@@ -628,12 +628,12 @@
     <t>2021-07-06</t>
   </si>
   <si>
+    <t>2021-07-23</t>
+  </si>
+  <si>
     <t>2021-07-14</t>
   </si>
   <si>
-    <t>2021-07-16</t>
-  </si>
-  <si>
     <t>2016-07-25</t>
   </si>
   <si>
@@ -1027,13 +1027,16 @@
     <t>2021-06-15</t>
   </si>
   <si>
-    <t>2021-06-17</t>
+    <t>2021-07-26</t>
   </si>
   <si>
     <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-07-20</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
   </si>
   <si>
     <t>2016-06-21</t>
@@ -1799,7 +1802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P905"/>
+  <dimension ref="A1:P902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1896,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1946,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1996,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2046,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2096,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2146,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2196,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2246,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2296,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2346,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2396,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2446,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2496,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2546,7 +2549,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2596,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2646,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2696,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2746,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2796,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2846,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2896,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2946,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2996,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3046,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3096,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3146,7 +3149,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3196,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3246,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3296,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3346,7 +3349,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3396,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3446,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3496,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3546,7 +3549,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3596,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3646,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3696,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3746,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3796,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3846,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3896,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3946,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3996,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4046,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4096,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4146,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4196,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4246,7 +4249,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4296,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4346,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4396,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4646,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4696,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4746,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4796,7 +4799,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4846,7 +4849,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4896,7 +4899,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5046,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5096,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5246,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5296,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5346,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5396,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5546,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5596,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5646,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5696,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5746,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5996,7 +5999,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6046,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6096,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6146,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6496,7 +6499,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6546,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6596,7 +6599,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6846,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6896,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6946,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6996,7 +6999,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7046,7 +7049,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7096,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7146,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7346,7 +7349,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7396,7 +7399,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7446,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7496,7 +7499,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7546,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7596,7 +7599,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7646,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7696,7 +7699,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7746,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7796,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7846,7 +7849,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7896,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7946,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7996,7 +7999,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8046,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8096,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8146,7 +8149,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8196,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8246,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8296,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8346,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8396,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8996,7 +8999,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9046,7 +9049,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9096,7 +9099,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9146,7 +9149,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9196,7 +9199,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9246,7 +9249,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9296,7 +9299,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9446,7 +9449,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10046,7 +10049,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10096,7 +10099,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10146,7 +10149,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10196,7 +10199,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10246,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10446,7 +10449,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10496,7 +10499,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10546,7 +10549,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10746,7 +10749,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10796,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10846,7 +10849,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10896,7 +10899,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10946,7 +10949,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10996,7 +10999,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11046,7 +11049,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11096,7 +11099,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11146,7 +11149,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11346,7 +11349,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11396,7 +11399,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11446,7 +11449,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11496,7 +11499,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11546,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11596,7 +11599,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11646,7 +11649,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11696,7 +11699,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11746,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11796,7 +11799,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11846,7 +11849,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11896,7 +11899,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12146,7 +12149,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12196,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12246,7 +12249,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12296,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12346,7 +12349,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12646,7 +12649,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12696,7 +12699,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12746,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12796,7 +12799,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12846,7 +12849,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12896,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12946,7 +12949,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12996,7 +12999,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -13046,7 +13049,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13096,7 +13099,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -13146,7 +13149,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13546,7 +13549,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13596,7 +13599,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13646,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13696,7 +13699,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -14196,7 +14199,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14246,7 +14249,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14296,7 +14299,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14346,7 +14349,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14396,7 +14399,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14446,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14496,7 +14499,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14546,7 +14549,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14596,7 +14599,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14646,7 +14649,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14696,7 +14699,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14746,7 +14749,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14796,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14846,7 +14849,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14896,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14946,7 +14949,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14996,7 +14999,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15046,7 +15049,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15096,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15146,7 +15149,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15196,7 +15199,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15746,7 +15749,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15796,7 +15799,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15846,7 +15849,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15896,7 +15899,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15946,7 +15949,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15996,7 +15999,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16046,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16096,7 +16099,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16146,7 +16149,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16196,7 +16199,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16246,7 +16249,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16296,7 +16299,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16346,7 +16349,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16396,7 +16399,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16446,7 +16449,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16496,7 +16499,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16546,7 +16549,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16596,7 +16599,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16646,7 +16649,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16846,7 +16849,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16896,7 +16899,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16946,7 +16949,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17346,7 +17349,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17396,7 +17399,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17446,7 +17449,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17496,7 +17499,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17746,7 +17749,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17796,7 +17799,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17846,7 +17849,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17896,7 +17899,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18896,7 +18899,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18946,7 +18949,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18996,7 +18999,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19046,7 +19049,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19096,7 +19099,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19146,7 +19149,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19196,7 +19199,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19246,7 +19249,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19296,7 +19299,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19346,7 +19349,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19396,7 +19399,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19446,7 +19449,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19496,7 +19499,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19546,7 +19549,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19596,7 +19599,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19646,7 +19649,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19696,7 +19699,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19996,7 +19999,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20046,7 +20049,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20096,7 +20099,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20146,7 +20149,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20196,7 +20199,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20246,7 +20249,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20296,7 +20299,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20346,7 +20349,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20396,7 +20399,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20446,7 +20449,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20496,7 +20499,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20546,7 +20549,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20596,7 +20599,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20646,7 +20649,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20946,7 +20949,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20996,7 +20999,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21046,7 +21049,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21096,7 +21099,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21146,7 +21149,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21196,7 +21199,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21246,7 +21249,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21296,7 +21299,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21546,7 +21549,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21596,7 +21599,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21646,7 +21649,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21696,7 +21699,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21746,7 +21749,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21796,7 +21799,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21846,7 +21849,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21896,7 +21899,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21946,7 +21949,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21996,7 +21999,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -24146,7 +24149,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24196,7 +24199,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24246,7 +24249,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24296,7 +24299,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24346,7 +24349,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24396,7 +24399,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24446,7 +24449,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24496,7 +24499,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -27596,7 +27599,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27646,7 +27649,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27696,7 +27699,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27746,7 +27749,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27796,7 +27799,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27846,7 +27849,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27896,7 +27899,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27946,7 +27949,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27996,7 +27999,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28046,7 +28049,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28096,7 +28099,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28146,7 +28149,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28196,7 +28199,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28246,7 +28249,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28296,7 +28299,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28746,7 +28749,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28796,7 +28799,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28846,7 +28849,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28896,7 +28899,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29096,7 +29099,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29146,7 +29149,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29196,7 +29199,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29246,7 +29249,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29296,7 +29299,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29346,7 +29349,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29396,7 +29399,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29446,7 +29449,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29496,7 +29499,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29546,7 +29549,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29596,7 +29599,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29646,7 +29649,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30146,7 +30149,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30196,7 +30199,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30246,7 +30249,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30296,7 +30299,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30346,7 +30349,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30396,7 +30399,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30446,7 +30449,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30496,7 +30499,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30546,7 +30549,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30596,7 +30599,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31196,7 +31199,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31246,7 +31249,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31296,7 +31299,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31346,7 +31349,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31396,7 +31399,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31446,7 +31449,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31496,7 +31499,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31946,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31996,7 +31999,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32146,7 +32149,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32196,7 +32199,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32246,7 +32249,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32296,7 +32299,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32346,7 +32349,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32396,7 +32399,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -35346,7 +35349,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35396,7 +35399,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35446,7 +35449,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35496,7 +35499,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35546,7 +35549,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35596,7 +35599,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35646,7 +35649,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35696,7 +35699,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35746,7 +35749,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35796,7 +35799,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35846,7 +35849,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35896,7 +35899,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35946,7 +35949,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35996,7 +35999,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36046,7 +36049,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36096,7 +36099,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36146,7 +36149,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36196,7 +36199,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36246,7 +36249,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36446,7 +36449,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36496,7 +36499,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36546,7 +36549,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36596,7 +36599,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36646,7 +36649,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36696,7 +36699,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36746,7 +36749,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36796,7 +36799,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36846,7 +36849,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36896,7 +36899,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36946,7 +36949,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36996,7 +36999,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37046,7 +37049,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37096,7 +37099,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37146,7 +37149,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37196,7 +37199,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37246,7 +37249,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37296,7 +37299,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37346,7 +37349,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37396,7 +37399,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37446,7 +37449,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37696,7 +37699,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37746,7 +37749,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37796,7 +37799,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37846,7 +37849,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37896,7 +37899,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37946,7 +37949,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37996,7 +37999,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38046,7 +38049,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38096,7 +38099,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38146,7 +38149,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38196,7 +38199,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38246,7 +38249,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38296,7 +38299,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38346,7 +38349,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38396,7 +38399,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38446,7 +38449,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38496,7 +38499,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38546,7 +38549,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38596,7 +38599,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38646,7 +38649,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38696,7 +38699,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38746,7 +38749,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38796,7 +38799,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38846,7 +38849,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38896,7 +38899,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38946,7 +38949,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38996,7 +38999,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39046,7 +39049,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39096,7 +39099,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39146,7 +39149,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39196,7 +39199,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39246,7 +39249,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39296,7 +39299,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39346,7 +39349,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39396,7 +39399,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39446,7 +39449,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39496,7 +39499,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39546,7 +39549,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39596,7 +39599,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39646,7 +39649,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39696,7 +39699,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39746,7 +39749,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39796,7 +39799,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39846,7 +39849,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39896,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39946,7 +39949,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -39996,7 +39999,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40046,7 +40049,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40246,7 +40249,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40296,7 +40299,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40346,7 +40349,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40446,7 +40449,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40496,7 +40499,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40546,7 +40549,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40596,7 +40599,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40646,7 +40649,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40696,7 +40699,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -40746,7 +40749,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40796,7 +40799,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40846,7 +40849,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40896,7 +40899,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40946,7 +40949,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40996,7 +40999,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41046,7 +41049,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41096,7 +41099,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41146,7 +41149,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41196,7 +41199,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41246,7 +41249,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41296,7 +41299,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41346,7 +41349,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41396,7 +41399,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41446,7 +41449,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41496,7 +41499,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41546,7 +41549,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41596,7 +41599,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41646,7 +41649,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -41946,7 +41949,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41996,7 +41999,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42046,7 +42049,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42096,7 +42099,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42246,7 +42249,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42296,7 +42299,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42446,7 +42449,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42496,7 +42499,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42546,7 +42549,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42596,7 +42599,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42646,7 +42649,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42846,7 +42849,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42896,7 +42899,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42946,7 +42949,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -42996,7 +42999,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43046,7 +43049,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43096,7 +43099,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43146,7 +43149,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43196,7 +43199,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43246,7 +43249,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43596,7 +43599,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43646,7 +43649,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43696,7 +43699,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43896,7 +43899,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43946,7 +43949,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43996,7 +43999,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44046,7 +44049,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44096,7 +44099,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44146,7 +44149,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44296,7 +44299,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44346,7 +44349,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44396,7 +44399,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44446,7 +44449,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44496,7 +44499,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44746,7 +44749,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44796,7 +44799,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44846,7 +44849,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44896,7 +44899,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45110,7 +45113,7 @@
         <v>0.7719106232022783</v>
       </c>
       <c r="D867" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E867">
         <v>0.5400163417687507</v>
@@ -45196,7 +45199,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45210,7 +45213,7 @@
         <v>0.7576723026745622</v>
       </c>
       <c r="D869" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E869">
         <v>0.5250813450072629</v>
@@ -45246,7 +45249,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45296,7 +45299,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45310,7 +45313,7 @@
         <v>0.7257735001824654</v>
       </c>
       <c r="D871" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E871">
         <v>0.4916217448397111</v>
@@ -45346,7 +45349,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45410,7 +45413,7 @@
         <v>0.7114203326982134</v>
       </c>
       <c r="D873" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E873">
         <v>0.4765662816987373</v>
@@ -45496,7 +45499,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45510,7 +45513,7 @@
         <v>0.6922020910541313</v>
       </c>
       <c r="D875" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E875">
         <v>0.4564076979558633</v>
@@ -45546,7 +45549,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45596,7 +45599,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45610,7 +45613,7 @@
         <v>0.6746197386642372</v>
       </c>
       <c r="D877" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E877">
         <v>0.4379650469780838</v>
@@ -45646,7 +45649,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45710,7 +45713,7 @@
         <v>0.6658747168932573</v>
       </c>
       <c r="D879" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E879">
         <v>0.4287921342335999</v>
@@ -45810,7 +45813,7 @@
         <v>0.6087670811874686</v>
       </c>
       <c r="D881" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E881">
         <v>0.4389572093313259</v>
@@ -45854,13 +45857,13 @@
         <v>2</v>
       </c>
       <c r="B882" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C882">
-        <v>0.6032994399902716</v>
+        <v>0.6755656193916719</v>
       </c>
       <c r="D882" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E882">
         <v>0.4389572093313259</v>
@@ -45869,22 +45872,22 @@
         <v>-1</v>
       </c>
       <c r="G882">
-        <v>0.01131670056000973</v>
+        <v>0.01116443438060833</v>
       </c>
       <c r="H882">
         <v>0.01144104279066867</v>
       </c>
       <c r="I882">
-        <v>0.1643422306589457</v>
+        <v>0.2366084100603461</v>
       </c>
       <c r="J882">
         <v>1.603802562877164</v>
       </c>
       <c r="K882">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="L882">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="M882">
         <v>3.43</v>
@@ -45901,96 +45904,96 @@
     </row>
     <row r="883" spans="1:16">
       <c r="A883" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B883" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C883">
-        <v>0.6755656193916719</v>
+        <v>0.2246564252284724</v>
       </c>
       <c r="D883" t="s">
-        <v>204</v>
+        <v>336</v>
       </c>
       <c r="E883">
-        <v>0.4389572093313259</v>
+        <v>0.1669471259084254</v>
       </c>
       <c r="F883">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G883">
-        <v>0.01116443438060833</v>
+        <v>0.01207534357477153</v>
       </c>
       <c r="H883">
-        <v>0.01144104279066867</v>
+        <v>0.01195305287409157</v>
       </c>
       <c r="I883">
-        <v>0.2366084100603461</v>
+        <v>-0.05770929932004698</v>
       </c>
       <c r="J883">
-        <v>1.603802562877164</v>
+        <v>1.614535033997692</v>
       </c>
       <c r="K883">
-        <v>3.27</v>
+        <v>3.67</v>
       </c>
       <c r="L883">
-        <v>5.92</v>
+        <v>6.15</v>
       </c>
       <c r="M883">
-        <v>3.43</v>
+        <v>3.65</v>
       </c>
       <c r="N883">
-        <v>5.94</v>
+        <v>6.06</v>
       </c>
       <c r="O883">
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="884" spans="1:16">
       <c r="A884" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B884" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C884">
-        <v>0.2246564252284724</v>
+        <v>0.5714180816880337</v>
       </c>
       <c r="D884" t="s">
-        <v>336</v>
+        <v>205</v>
       </c>
       <c r="E884">
-        <v>0.1669471259084254</v>
+        <v>0.4021448333879176</v>
       </c>
       <c r="F884">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G884">
-        <v>0.01207534357477153</v>
+        <v>0.01180858191831197</v>
       </c>
       <c r="H884">
-        <v>0.01195305287409157</v>
+        <v>0.01147785516661208</v>
       </c>
       <c r="I884">
-        <v>-0.05770929932004698</v>
+        <v>0.169273248300116</v>
       </c>
       <c r="J884">
         <v>1.614535033997692</v>
       </c>
       <c r="K884">
-        <v>3.67</v>
+        <v>3.48</v>
       </c>
       <c r="L884">
-        <v>6.15</v>
+        <v>6.19</v>
       </c>
       <c r="M884">
-        <v>3.65</v>
+        <v>3.43</v>
       </c>
       <c r="N884">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="O884">
         <v>1</v>
@@ -46001,16 +46004,16 @@
     </row>
     <row r="885" spans="1:16">
       <c r="A885" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B885" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C885">
-        <v>0.5714180816880337</v>
+        <v>0.5674529864477105</v>
       </c>
       <c r="D885" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E885">
         <v>0.4021448333879176</v>
@@ -46019,22 +46022,22 @@
         <v>-1</v>
       </c>
       <c r="G885">
-        <v>0.01180858191831197</v>
+        <v>0.01135254701355229</v>
       </c>
       <c r="H885">
         <v>0.01147785516661208</v>
       </c>
       <c r="I885">
-        <v>0.169273248300116</v>
+        <v>0.1653081530597929</v>
       </c>
       <c r="J885">
         <v>1.614535033997692</v>
       </c>
       <c r="K885">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="L885">
-        <v>6.19</v>
+        <v>5.96</v>
       </c>
       <c r="M885">
         <v>3.43</v>
@@ -46051,16 +46054,16 @@
     </row>
     <row r="886" spans="1:16">
       <c r="A886" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B886" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C886">
-        <v>0.5674529864477105</v>
+        <v>0.6404704388275482</v>
       </c>
       <c r="D886" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E886">
         <v>0.4021448333879176</v>
@@ -46069,22 +46072,22 @@
         <v>-1</v>
       </c>
       <c r="G886">
-        <v>0.01135254701355229</v>
+        <v>0.01119952956117245</v>
       </c>
       <c r="H886">
         <v>0.01147785516661208</v>
       </c>
       <c r="I886">
-        <v>0.1653081530597929</v>
+        <v>0.2383256054396306</v>
       </c>
       <c r="J886">
         <v>1.614535033997692</v>
       </c>
       <c r="K886">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="L886">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="M886">
         <v>3.43</v>
@@ -46101,116 +46104,116 @@
     </row>
     <row r="887" spans="1:16">
       <c r="A887" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B887" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C887">
-        <v>0.6404704388275482</v>
+        <v>0.1598063964288423</v>
       </c>
       <c r="D887" t="s">
-        <v>204</v>
+        <v>336</v>
       </c>
       <c r="E887">
-        <v>0.4021448333879176</v>
+        <v>0.1024505032602923</v>
       </c>
       <c r="F887">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G887">
-        <v>0.01119952956117245</v>
+        <v>0.01214019360357116</v>
       </c>
       <c r="H887">
-        <v>0.01147785516661208</v>
+        <v>0.01201754949673971</v>
       </c>
       <c r="I887">
-        <v>0.2383256054396306</v>
+        <v>-0.05735589316855005</v>
       </c>
       <c r="J887">
-        <v>1.614535033997692</v>
+        <v>1.632205341572523</v>
       </c>
       <c r="K887">
-        <v>3.27</v>
+        <v>3.67</v>
       </c>
       <c r="L887">
-        <v>5.92</v>
+        <v>6.15</v>
       </c>
       <c r="M887">
-        <v>3.43</v>
+        <v>3.65</v>
       </c>
       <c r="N887">
-        <v>5.94</v>
+        <v>6.06</v>
       </c>
       <c r="O887">
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>193</v>
+        <v>474</v>
       </c>
     </row>
     <row r="888" spans="1:16">
       <c r="A888" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B888" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C888">
-        <v>0.1598063964288423</v>
+        <v>0.5099254113276217</v>
       </c>
       <c r="D888" t="s">
-        <v>336</v>
+        <v>205</v>
       </c>
       <c r="E888">
-        <v>0.1024505032602923</v>
+        <v>0.341535678406248</v>
       </c>
       <c r="F888">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G888">
-        <v>0.01214019360357116</v>
+        <v>0.01187007458867238</v>
       </c>
       <c r="H888">
-        <v>0.01201754949673971</v>
+        <v>0.01153846432159375</v>
       </c>
       <c r="I888">
-        <v>-0.05735589316855005</v>
+        <v>0.1683897329213737</v>
       </c>
       <c r="J888">
         <v>1.632205341572523</v>
       </c>
       <c r="K888">
-        <v>3.67</v>
+        <v>3.48</v>
       </c>
       <c r="L888">
-        <v>6.15</v>
+        <v>6.19</v>
       </c>
       <c r="M888">
-        <v>3.65</v>
+        <v>3.43</v>
       </c>
       <c r="N888">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="O888">
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="889" spans="1:16">
       <c r="A889" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B889" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C889">
-        <v>0.5099254113276217</v>
+        <v>0.5084341591477743</v>
       </c>
       <c r="D889" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E889">
         <v>0.341535678406248</v>
@@ -46219,22 +46222,22 @@
         <v>-1</v>
       </c>
       <c r="G889">
-        <v>0.01187007458867238</v>
+        <v>0.01141156584085223</v>
       </c>
       <c r="H889">
         <v>0.01153846432159375</v>
       </c>
       <c r="I889">
-        <v>0.1683897329213737</v>
+        <v>0.1668984807415264</v>
       </c>
       <c r="J889">
         <v>1.632205341572523</v>
       </c>
       <c r="K889">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="L889">
-        <v>6.19</v>
+        <v>5.96</v>
       </c>
       <c r="M889">
         <v>3.43</v>
@@ -46246,21 +46249,21 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="890" spans="1:16">
       <c r="A890" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B890" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C890">
-        <v>0.5084341591477743</v>
+        <v>0.5826885330578513</v>
       </c>
       <c r="D890" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E890">
         <v>0.341535678406248</v>
@@ -46269,22 +46272,22 @@
         <v>-1</v>
       </c>
       <c r="G890">
-        <v>0.01141156584085223</v>
+        <v>0.01125731146694215</v>
       </c>
       <c r="H890">
         <v>0.01153846432159375</v>
       </c>
       <c r="I890">
-        <v>0.1668984807415264</v>
+        <v>0.2411528546516033</v>
       </c>
       <c r="J890">
         <v>1.632205341572523</v>
       </c>
       <c r="K890">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="L890">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="M890">
         <v>3.43</v>
@@ -46296,101 +46299,101 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="891" spans="1:16">
       <c r="A891" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B891" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C891">
-        <v>0.5826885330578513</v>
+        <v>0.011804494898219</v>
       </c>
       <c r="D891" t="s">
-        <v>204</v>
+        <v>336</v>
       </c>
       <c r="E891">
-        <v>0.341535678406248</v>
+        <v>-0.04474484839823045</v>
       </c>
       <c r="F891">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G891">
-        <v>0.01125731146694215</v>
+        <v>0.01228819550510178</v>
       </c>
       <c r="H891">
-        <v>0.01153846432159375</v>
+        <v>0.01216474484839823</v>
       </c>
       <c r="I891">
-        <v>0.2411528546516033</v>
+        <v>-0.05654934329644945</v>
       </c>
       <c r="J891">
-        <v>1.632205341572523</v>
+        <v>1.672532835177597</v>
       </c>
       <c r="K891">
-        <v>3.27</v>
+        <v>3.67</v>
       </c>
       <c r="L891">
-        <v>5.92</v>
+        <v>6.15</v>
       </c>
       <c r="M891">
-        <v>3.43</v>
+        <v>3.65</v>
       </c>
       <c r="N891">
-        <v>5.94</v>
+        <v>6.06</v>
       </c>
       <c r="O891">
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>473</v>
+        <v>195</v>
       </c>
     </row>
     <row r="892" spans="1:16">
       <c r="A892" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B892" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C892">
-        <v>0.011804494898219</v>
+        <v>0.3737403305068252</v>
       </c>
       <c r="D892" t="s">
-        <v>337</v>
+        <v>205</v>
       </c>
       <c r="E892">
-        <v>-0.07872346026776533</v>
+        <v>0.2032123753408417</v>
       </c>
       <c r="F892">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G892">
-        <v>0.01228819550510178</v>
+        <v>0.01154625966949317</v>
       </c>
       <c r="H892">
-        <v>0.01249872346026777</v>
+        <v>0.01167678762465916</v>
       </c>
       <c r="I892">
-        <v>-0.09052795516598433</v>
+        <v>0.1705279551659835</v>
       </c>
       <c r="J892">
         <v>1.672532835177597</v>
       </c>
       <c r="K892">
-        <v>3.67</v>
+        <v>3.34</v>
       </c>
       <c r="L892">
-        <v>6.15</v>
+        <v>5.96</v>
       </c>
       <c r="M892">
-        <v>3.76</v>
+        <v>3.43</v>
       </c>
       <c r="N892">
-        <v>6.21</v>
+        <v>5.94</v>
       </c>
       <c r="O892">
         <v>1</v>
@@ -46401,16 +46404,16 @@
     </row>
     <row r="893" spans="1:16">
       <c r="A893" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B893" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C893">
-        <v>0.3695857335819621</v>
+        <v>0.4508176289692569</v>
       </c>
       <c r="D893" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E893">
         <v>0.2032123753408417</v>
@@ -46419,22 +46422,22 @@
         <v>-1</v>
       </c>
       <c r="G893">
-        <v>0.01201041426641804</v>
+        <v>0.01138918237103074</v>
       </c>
       <c r="H893">
         <v>0.01167678762465916</v>
       </c>
       <c r="I893">
-        <v>0.1663733582411204</v>
+        <v>0.2476052536284152</v>
       </c>
       <c r="J893">
         <v>1.672532835177597</v>
       </c>
       <c r="K893">
-        <v>3.48</v>
+        <v>3.27</v>
       </c>
       <c r="L893">
-        <v>6.19</v>
+        <v>5.92</v>
       </c>
       <c r="M893">
         <v>3.43</v>
@@ -46451,40 +46454,40 @@
     </row>
     <row r="894" spans="1:16">
       <c r="A894" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B894" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C894">
-        <v>0.3737403305068252</v>
+        <v>0.2968499181634146</v>
       </c>
       <c r="D894" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E894">
-        <v>0.2032123753408417</v>
+        <v>0.04171107623868942</v>
       </c>
       <c r="F894">
         <v>-1</v>
       </c>
       <c r="G894">
-        <v>0.01154625966949317</v>
+        <v>0.01154315008183659</v>
       </c>
       <c r="H894">
-        <v>0.01167678762465916</v>
+        <v>0.01183828892376131</v>
       </c>
       <c r="I894">
-        <v>0.1705279551659835</v>
+        <v>0.2551388419247251</v>
       </c>
       <c r="J894">
-        <v>1.672532835177597</v>
+        <v>1.719617762029537</v>
       </c>
       <c r="K894">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="L894">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="M894">
         <v>3.43</v>
@@ -46496,39 +46499,39 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="895" spans="1:16">
       <c r="A895" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B895" t="s">
         <v>201</v>
       </c>
       <c r="C895">
-        <v>0.4508176289692569</v>
+        <v>0.3224506058857468</v>
       </c>
       <c r="D895" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E895">
-        <v>0.2032123753408417</v>
+        <v>0.06856439699942296</v>
       </c>
       <c r="F895">
         <v>-1</v>
       </c>
       <c r="G895">
-        <v>0.01138918237103074</v>
+        <v>0.01151754939411425</v>
       </c>
       <c r="H895">
-        <v>0.01167678762465916</v>
+        <v>0.01181143560300058</v>
       </c>
       <c r="I895">
-        <v>0.2476052536284152</v>
+        <v>0.2538862088863238</v>
       </c>
       <c r="J895">
-        <v>1.672532835177597</v>
+        <v>1.711788805539527</v>
       </c>
       <c r="K895">
         <v>3.27</v>
@@ -46546,7 +46549,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>195</v>
+        <v>335</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46554,37 +46557,37 @@
         <v>0</v>
       </c>
       <c r="B896" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C896">
-        <v>0.2164766748213474</v>
+        <v>0.4717536877718773</v>
       </c>
       <c r="D896" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E896">
-        <v>0.04171107623868942</v>
+        <v>0.2251728284579633</v>
       </c>
       <c r="F896">
         <v>-1</v>
       </c>
       <c r="G896">
-        <v>0.01170352332517865</v>
+        <v>0.01136824631222812</v>
       </c>
       <c r="H896">
-        <v>0.01183828892376131</v>
+        <v>0.01165482717154204</v>
       </c>
       <c r="I896">
-        <v>0.1747655985826579</v>
+        <v>0.246580859313914</v>
       </c>
       <c r="J896">
-        <v>1.719617762029537</v>
+        <v>1.666130370711964</v>
       </c>
       <c r="K896">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="L896">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="M896">
         <v>3.43</v>
@@ -46596,39 +46599,39 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>196</v>
+        <v>336</v>
       </c>
     </row>
     <row r="897" spans="1:16">
       <c r="A897" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B897" t="s">
         <v>201</v>
       </c>
       <c r="C897">
-        <v>0.2968499181634146</v>
+        <v>0.5136993922788848</v>
       </c>
       <c r="D897" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E897">
-        <v>0.04171107623868942</v>
+        <v>0.2691709221763228</v>
       </c>
       <c r="F897">
         <v>-1</v>
       </c>
       <c r="G897">
-        <v>0.01154315008183659</v>
+        <v>0.01132630060772112</v>
       </c>
       <c r="H897">
-        <v>0.01183828892376131</v>
+        <v>0.01161082907782368</v>
       </c>
       <c r="I897">
-        <v>0.2551388419247251</v>
+        <v>0.2445284701025621</v>
       </c>
       <c r="J897">
-        <v>1.719617762029537</v>
+        <v>1.653302938141014</v>
       </c>
       <c r="K897">
         <v>3.27</v>
@@ -46646,57 +46649,57 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>196</v>
+        <v>475</v>
       </c>
     </row>
     <row r="898" spans="1:16">
       <c r="A898" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B898" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C898">
-        <v>0.3224506058857468</v>
+        <v>0.2077085108365813</v>
       </c>
       <c r="D898" t="s">
-        <v>204</v>
+        <v>337</v>
       </c>
       <c r="E898">
-        <v>0.06856439699942296</v>
+        <v>0.3330388046506823</v>
       </c>
       <c r="F898">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G898">
-        <v>0.01151754939411425</v>
+        <v>0.01201229148916342</v>
       </c>
       <c r="H898">
-        <v>0.01181143560300058</v>
+        <v>0.01180696119534932</v>
       </c>
       <c r="I898">
-        <v>0.2538862088863238</v>
+        <v>0.125330293814101</v>
       </c>
       <c r="J898">
-        <v>1.711788805539527</v>
+        <v>1.653302938141014</v>
       </c>
       <c r="K898">
-        <v>3.27</v>
+        <v>3.57</v>
       </c>
       <c r="L898">
-        <v>5.92</v>
+        <v>6.11</v>
       </c>
       <c r="M898">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="N898">
-        <v>5.94</v>
+        <v>6.07</v>
       </c>
       <c r="O898">
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>335</v>
+        <v>475</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -46707,28 +46710,28 @@
         <v>201</v>
       </c>
       <c r="C899">
-        <v>0.4717536877718773</v>
+        <v>1.339409495526739</v>
       </c>
       <c r="D899" t="s">
-        <v>204</v>
+        <v>338</v>
       </c>
       <c r="E899">
-        <v>0.2251728284579633</v>
+        <v>1.219290665046315</v>
       </c>
       <c r="F899">
         <v>-1</v>
       </c>
       <c r="G899">
-        <v>0.01136824631222812</v>
+        <v>0.01050059050447326</v>
       </c>
       <c r="H899">
-        <v>0.01165482717154204</v>
+        <v>0.01080070933495368</v>
       </c>
       <c r="I899">
-        <v>0.246580859313914</v>
+        <v>0.1201188304804246</v>
       </c>
       <c r="J899">
-        <v>1.666130370711964</v>
+        <v>1.400792203202832</v>
       </c>
       <c r="K899">
         <v>3.27</v>
@@ -46737,110 +46740,110 @@
         <v>5.92</v>
       </c>
       <c r="M899">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="N899">
-        <v>5.94</v>
+        <v>6.01</v>
       </c>
       <c r="O899">
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>336</v>
+        <v>202</v>
       </c>
     </row>
     <row r="900" spans="1:16">
       <c r="A900" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B900" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C900">
-        <v>0.5136993922788848</v>
+        <v>1.135282743014287</v>
       </c>
       <c r="D900" t="s">
-        <v>204</v>
+        <v>339</v>
       </c>
       <c r="E900">
-        <v>0.2691709221763228</v>
+        <v>1.269330275206457</v>
       </c>
       <c r="F900">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G900">
-        <v>0.01132630060772112</v>
+        <v>0.01074471725698571</v>
       </c>
       <c r="H900">
-        <v>0.01161082907782368</v>
+        <v>0.01071066972479354</v>
       </c>
       <c r="I900">
-        <v>0.2445284701025621</v>
+        <v>0.1340475321921701</v>
       </c>
       <c r="J900">
-        <v>1.653302938141014</v>
+        <v>1.400792203202832</v>
       </c>
       <c r="K900">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="L900">
-        <v>5.92</v>
+        <v>5.94</v>
       </c>
       <c r="M900">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="N900">
-        <v>5.94</v>
+        <v>5.99</v>
       </c>
       <c r="O900">
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>474</v>
+        <v>202</v>
       </c>
     </row>
     <row r="901" spans="1:16">
       <c r="A901" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B901" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C901">
-        <v>1.339409495526739</v>
+        <v>1.109171834565891</v>
       </c>
       <c r="D901" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E901">
-        <v>1.219290665046315</v>
+        <v>1.245361963334569</v>
       </c>
       <c r="F901">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G901">
-        <v>0.01050059050447326</v>
+        <v>0.01111082816543411</v>
       </c>
       <c r="H901">
-        <v>0.01080070933495368</v>
+        <v>0.01057463803666543</v>
       </c>
       <c r="I901">
-        <v>0.1201188304804246</v>
+        <v>0.1361901287686784</v>
       </c>
       <c r="J901">
         <v>1.400792203202832</v>
       </c>
       <c r="K901">
-        <v>3.27</v>
+        <v>3.57</v>
       </c>
       <c r="L901">
-        <v>5.92</v>
+        <v>6.11</v>
       </c>
       <c r="M901">
-        <v>3.42</v>
+        <v>3.33</v>
       </c>
       <c r="N901">
-        <v>6.01</v>
+        <v>5.91</v>
       </c>
       <c r="O901">
         <v>1</v>
@@ -46851,34 +46854,34 @@
     </row>
     <row r="902" spans="1:16">
       <c r="A902" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B902" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C902">
-        <v>1.135282743014287</v>
+        <v>1.05728794369645</v>
       </c>
       <c r="D902" t="s">
         <v>339</v>
       </c>
       <c r="E902">
-        <v>1.269330275206457</v>
+        <v>1.192699816401468</v>
       </c>
       <c r="F902">
         <v>1</v>
       </c>
       <c r="G902">
-        <v>0.01074471725698571</v>
+        <v>0.01082271205630355</v>
       </c>
       <c r="H902">
-        <v>0.01071066972479354</v>
+        <v>0.01078730018359853</v>
       </c>
       <c r="I902">
-        <v>0.1340475321921701</v>
+        <v>0.135411872705018</v>
       </c>
       <c r="J902">
-        <v>1.400792203202832</v>
+        <v>1.423531211750306</v>
       </c>
       <c r="K902">
         <v>3.43</v>
@@ -46896,157 +46899,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="903" spans="1:16">
-      <c r="A903" s="1">
-        <v>0</v>
-      </c>
-      <c r="B903" t="s">
-        <v>201</v>
-      </c>
-      <c r="C903">
-        <v>1.265052937576499</v>
-      </c>
-      <c r="D903" t="s">
-        <v>338</v>
-      </c>
-      <c r="E903">
-        <v>1.141523255813953</v>
-      </c>
-      <c r="F903">
-        <v>-1</v>
-      </c>
-      <c r="G903">
-        <v>0.0105749470624235</v>
-      </c>
-      <c r="H903">
-        <v>0.01087847674418605</v>
-      </c>
-      <c r="I903">
-        <v>0.1235296817625455</v>
-      </c>
-      <c r="J903">
-        <v>1.423531211750306</v>
-      </c>
-      <c r="K903">
-        <v>3.27</v>
-      </c>
-      <c r="L903">
-        <v>5.92</v>
-      </c>
-      <c r="M903">
-        <v>3.42</v>
-      </c>
-      <c r="N903">
-        <v>6.01</v>
-      </c>
-      <c r="O903">
-        <v>1</v>
-      </c>
-      <c r="P903" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="904" spans="1:16">
-      <c r="A904" s="1">
-        <v>1</v>
-      </c>
-      <c r="B904" t="s">
-        <v>204</v>
-      </c>
-      <c r="C904">
-        <v>1.05728794369645</v>
-      </c>
-      <c r="D904" t="s">
-        <v>339</v>
-      </c>
-      <c r="E904">
-        <v>1.192699816401468</v>
-      </c>
-      <c r="F904">
-        <v>1</v>
-      </c>
-      <c r="G904">
-        <v>0.01082271205630355</v>
-      </c>
-      <c r="H904">
-        <v>0.01078730018359853</v>
-      </c>
-      <c r="I904">
-        <v>0.135411872705018</v>
-      </c>
-      <c r="J904">
-        <v>1.423531211750306</v>
-      </c>
-      <c r="K904">
-        <v>3.43</v>
-      </c>
-      <c r="L904">
-        <v>5.94</v>
-      </c>
-      <c r="M904">
-        <v>3.37</v>
-      </c>
-      <c r="N904">
-        <v>5.99</v>
-      </c>
-      <c r="O904">
-        <v>1</v>
-      </c>
-      <c r="P904" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="905" spans="1:16">
-      <c r="A905" s="1">
-        <v>2</v>
-      </c>
-      <c r="B905" t="s">
-        <v>205</v>
-      </c>
-      <c r="C905">
-        <v>1.069993880048959</v>
-      </c>
-      <c r="D905" t="s">
-        <v>339</v>
-      </c>
-      <c r="E905">
-        <v>1.192699816401468</v>
-      </c>
-      <c r="F905">
-        <v>1</v>
-      </c>
-      <c r="G905">
-        <v>0.01075000611995104</v>
-      </c>
-      <c r="H905">
-        <v>0.01078730018359853</v>
-      </c>
-      <c r="I905">
-        <v>0.1227059363525091</v>
-      </c>
-      <c r="J905">
-        <v>1.423531211750306</v>
-      </c>
-      <c r="K905">
-        <v>3.4</v>
-      </c>
-      <c r="L905">
-        <v>5.91</v>
-      </c>
-      <c r="M905">
-        <v>3.37</v>
-      </c>
-      <c r="N905">
-        <v>5.99</v>
-      </c>
-      <c r="O905">
-        <v>1</v>
-      </c>
-      <c r="P905" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2718" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="478">
   <si>
     <t>trade_time</t>
   </si>
@@ -625,15 +625,15 @@
     <t>2021-06-25</t>
   </si>
   <si>
-    <t>2021-07-06</t>
-  </si>
-  <si>
     <t>2021-07-23</t>
   </si>
   <si>
     <t>2021-07-14</t>
   </si>
   <si>
+    <t>2021-08-03</t>
+  </si>
+  <si>
     <t>2016-07-25</t>
   </si>
   <si>
@@ -1030,13 +1030,16 @@
     <t>2021-07-26</t>
   </si>
   <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
     <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-07-20</t>
   </si>
   <si>
-    <t>2021-07-27</t>
+    <t>2021-08-04</t>
   </si>
   <si>
     <t>2016-06-21</t>
@@ -1802,7 +1805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P902"/>
+  <dimension ref="A1:P899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1899,7 +1902,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1949,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1999,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2049,7 +2052,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2099,7 +2102,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2149,7 +2152,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2199,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2249,7 +2252,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2299,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2349,7 +2352,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2399,7 +2402,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2449,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2499,7 +2502,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2549,7 +2552,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2599,7 +2602,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2649,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2699,7 +2702,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2749,7 +2752,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2799,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2849,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2899,7 +2902,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2949,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2999,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3049,7 +3052,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3099,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3149,7 +3152,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3199,7 +3202,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3249,7 +3252,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3299,7 +3302,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3349,7 +3352,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3399,7 +3402,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3449,7 +3452,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3499,7 +3502,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3549,7 +3552,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3599,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3649,7 +3652,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3699,7 +3702,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3749,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3799,7 +3802,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3849,7 +3852,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3899,7 +3902,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3949,7 +3952,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3999,7 +4002,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4049,7 +4052,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4099,7 +4102,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4149,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4199,7 +4202,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4249,7 +4252,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4299,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4349,7 +4352,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4399,7 +4402,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4649,7 +4652,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4699,7 +4702,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4749,7 +4752,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4799,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4849,7 +4852,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4899,7 +4902,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5049,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5099,7 +5102,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5249,7 +5252,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5299,7 +5302,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5349,7 +5352,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5399,7 +5402,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5549,7 +5552,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5599,7 +5602,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5649,7 +5652,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5699,7 +5702,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5749,7 +5752,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5999,7 +6002,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6049,7 +6052,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6099,7 +6102,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6149,7 +6152,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6499,7 +6502,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6549,7 +6552,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6599,7 +6602,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6849,7 +6852,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6899,7 +6902,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6949,7 +6952,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6999,7 +7002,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7049,7 +7052,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7099,7 +7102,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7149,7 +7152,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7349,7 +7352,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7399,7 +7402,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7449,7 +7452,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7499,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7549,7 +7552,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7599,7 +7602,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7649,7 +7652,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7699,7 +7702,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7749,7 +7752,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7799,7 +7802,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7849,7 +7852,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7899,7 +7902,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7949,7 +7952,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7999,7 +8002,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8049,7 +8052,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8099,7 +8102,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8149,7 +8152,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8199,7 +8202,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8249,7 +8252,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8299,7 +8302,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8349,7 +8352,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8399,7 +8402,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8999,7 +9002,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9049,7 +9052,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9099,7 +9102,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9149,7 +9152,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9199,7 +9202,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9249,7 +9252,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9299,7 +9302,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9449,7 +9452,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10049,7 +10052,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10099,7 +10102,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10149,7 +10152,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10199,7 +10202,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10249,7 +10252,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10449,7 +10452,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10499,7 +10502,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10549,7 +10552,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10749,7 +10752,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10799,7 +10802,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10849,7 +10852,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10899,7 +10902,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10949,7 +10952,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10999,7 +11002,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11049,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11099,7 +11102,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11149,7 +11152,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11349,7 +11352,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11399,7 +11402,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11449,7 +11452,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11499,7 +11502,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11549,7 +11552,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11599,7 +11602,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11649,7 +11652,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11699,7 +11702,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11749,7 +11752,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11799,7 +11802,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11849,7 +11852,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11899,7 +11902,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12149,7 +12152,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12199,7 +12202,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12249,7 +12252,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12299,7 +12302,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12349,7 +12352,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12649,7 +12652,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12699,7 +12702,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12749,7 +12752,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12799,7 +12802,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12849,7 +12852,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12899,7 +12902,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12949,7 +12952,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12999,7 +13002,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -13049,7 +13052,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13099,7 +13102,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -13149,7 +13152,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13549,7 +13552,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13599,7 +13602,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13649,7 +13652,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13699,7 +13702,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -14199,7 +14202,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14249,7 +14252,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14299,7 +14302,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14349,7 +14352,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14399,7 +14402,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14449,7 +14452,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14499,7 +14502,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14549,7 +14552,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14599,7 +14602,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14649,7 +14652,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14699,7 +14702,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14749,7 +14752,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14799,7 +14802,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14849,7 +14852,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14899,7 +14902,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14949,7 +14952,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14999,7 +15002,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15049,7 +15052,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15099,7 +15102,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15149,7 +15152,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15199,7 +15202,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15749,7 +15752,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15799,7 +15802,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15849,7 +15852,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15899,7 +15902,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15949,7 +15952,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15999,7 +16002,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16049,7 +16052,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16099,7 +16102,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16149,7 +16152,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16199,7 +16202,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16249,7 +16252,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16299,7 +16302,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16349,7 +16352,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16399,7 +16402,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16449,7 +16452,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16499,7 +16502,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16549,7 +16552,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16599,7 +16602,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16649,7 +16652,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16849,7 +16852,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16899,7 +16902,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16949,7 +16952,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17349,7 +17352,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17399,7 +17402,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17449,7 +17452,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17499,7 +17502,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17749,7 +17752,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17799,7 +17802,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17849,7 +17852,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17899,7 +17902,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18899,7 +18902,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18949,7 +18952,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18999,7 +19002,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19049,7 +19052,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19099,7 +19102,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19149,7 +19152,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19199,7 +19202,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19249,7 +19252,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19299,7 +19302,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19349,7 +19352,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19399,7 +19402,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19449,7 +19452,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19499,7 +19502,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19549,7 +19552,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19599,7 +19602,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19649,7 +19652,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19699,7 +19702,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19999,7 +20002,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20049,7 +20052,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20099,7 +20102,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20149,7 +20152,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20199,7 +20202,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20249,7 +20252,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20299,7 +20302,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20349,7 +20352,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20399,7 +20402,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20449,7 +20452,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20499,7 +20502,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20549,7 +20552,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20599,7 +20602,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20649,7 +20652,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20949,7 +20952,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20999,7 +21002,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21049,7 +21052,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21099,7 +21102,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21149,7 +21152,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21199,7 +21202,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21249,7 +21252,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21299,7 +21302,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21549,7 +21552,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21599,7 +21602,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21649,7 +21652,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21699,7 +21702,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21749,7 +21752,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21799,7 +21802,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21849,7 +21852,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21899,7 +21902,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21949,7 +21952,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21999,7 +22002,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -24149,7 +24152,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24199,7 +24202,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24249,7 +24252,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24299,7 +24302,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24349,7 +24352,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24399,7 +24402,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24449,7 +24452,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24499,7 +24502,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -27599,7 +27602,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27649,7 +27652,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27699,7 +27702,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27749,7 +27752,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27799,7 +27802,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27849,7 +27852,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27899,7 +27902,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27949,7 +27952,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27999,7 +28002,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28049,7 +28052,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28099,7 +28102,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28149,7 +28152,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28199,7 +28202,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28249,7 +28252,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28299,7 +28302,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28749,7 +28752,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28799,7 +28802,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28849,7 +28852,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28899,7 +28902,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29099,7 +29102,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29149,7 +29152,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29199,7 +29202,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29249,7 +29252,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29299,7 +29302,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29349,7 +29352,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29399,7 +29402,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29449,7 +29452,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29499,7 +29502,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29549,7 +29552,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29599,7 +29602,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29649,7 +29652,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30149,7 +30152,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30199,7 +30202,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30249,7 +30252,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30299,7 +30302,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30349,7 +30352,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30399,7 +30402,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30449,7 +30452,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30499,7 +30502,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30549,7 +30552,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30599,7 +30602,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31199,7 +31202,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31249,7 +31252,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31299,7 +31302,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31349,7 +31352,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31399,7 +31402,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31449,7 +31452,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31499,7 +31502,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31949,7 +31952,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31999,7 +32002,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32149,7 +32152,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32199,7 +32202,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32249,7 +32252,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32299,7 +32302,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32349,7 +32352,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32399,7 +32402,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -35349,7 +35352,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35399,7 +35402,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35449,7 +35452,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35499,7 +35502,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35549,7 +35552,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35599,7 +35602,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35649,7 +35652,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35699,7 +35702,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35749,7 +35752,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35799,7 +35802,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35849,7 +35852,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35899,7 +35902,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35949,7 +35952,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35999,7 +36002,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36049,7 +36052,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36099,7 +36102,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36149,7 +36152,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36199,7 +36202,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36249,7 +36252,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36449,7 +36452,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36499,7 +36502,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36549,7 +36552,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36599,7 +36602,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36649,7 +36652,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36699,7 +36702,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36749,7 +36752,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36799,7 +36802,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36849,7 +36852,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36899,7 +36902,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36949,7 +36952,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36999,7 +37002,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37049,7 +37052,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37099,7 +37102,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37149,7 +37152,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37199,7 +37202,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37249,7 +37252,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37299,7 +37302,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37349,7 +37352,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37399,7 +37402,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37449,7 +37452,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37699,7 +37702,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37749,7 +37752,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37799,7 +37802,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37849,7 +37852,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37899,7 +37902,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37949,7 +37952,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37999,7 +38002,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38049,7 +38052,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38099,7 +38102,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38149,7 +38152,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38199,7 +38202,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38249,7 +38252,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38299,7 +38302,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38349,7 +38352,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38399,7 +38402,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38449,7 +38452,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38499,7 +38502,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38549,7 +38552,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38599,7 +38602,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38649,7 +38652,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38699,7 +38702,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38749,7 +38752,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38799,7 +38802,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38849,7 +38852,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38899,7 +38902,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38949,7 +38952,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38999,7 +39002,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39049,7 +39052,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39099,7 +39102,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39149,7 +39152,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39199,7 +39202,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39249,7 +39252,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39299,7 +39302,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39349,7 +39352,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39399,7 +39402,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39449,7 +39452,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39499,7 +39502,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39549,7 +39552,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39599,7 +39602,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39649,7 +39652,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39699,7 +39702,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39749,7 +39752,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39799,7 +39802,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39849,7 +39852,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39899,7 +39902,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39949,7 +39952,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -39999,7 +40002,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40049,7 +40052,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40249,7 +40252,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40299,7 +40302,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40349,7 +40352,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40449,7 +40452,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40499,7 +40502,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40549,7 +40552,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40599,7 +40602,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40649,7 +40652,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40699,7 +40702,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -40749,7 +40752,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40799,7 +40802,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40849,7 +40852,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40899,7 +40902,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40949,7 +40952,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40999,7 +41002,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41049,7 +41052,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41099,7 +41102,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41149,7 +41152,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41199,7 +41202,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41249,7 +41252,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41299,7 +41302,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41349,7 +41352,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41399,7 +41402,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41449,7 +41452,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41499,7 +41502,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41549,7 +41552,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41599,7 +41602,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41649,7 +41652,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -41949,7 +41952,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41999,7 +42002,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42049,7 +42052,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42099,7 +42102,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42249,7 +42252,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42299,7 +42302,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42449,7 +42452,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42499,7 +42502,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42549,7 +42552,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42599,7 +42602,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42649,7 +42652,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42849,7 +42852,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42899,7 +42902,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42949,7 +42952,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -42999,7 +43002,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43049,7 +43052,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43099,7 +43102,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43149,7 +43152,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43199,7 +43202,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43249,7 +43252,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43599,7 +43602,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43649,7 +43652,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43699,7 +43702,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43899,7 +43902,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43949,7 +43952,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43999,7 +44002,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44049,7 +44052,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44099,7 +44102,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44149,7 +44152,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44299,7 +44302,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44349,7 +44352,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44399,7 +44402,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44449,7 +44452,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44499,7 +44502,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44749,7 +44752,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44799,7 +44802,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44849,7 +44852,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44899,7 +44902,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45113,7 +45116,7 @@
         <v>0.7719106232022783</v>
       </c>
       <c r="D867" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E867">
         <v>0.5400163417687507</v>
@@ -45199,7 +45202,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45213,7 +45216,7 @@
         <v>0.7576723026745622</v>
       </c>
       <c r="D869" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E869">
         <v>0.5250813450072629</v>
@@ -45249,7 +45252,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45299,7 +45302,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45313,7 +45316,7 @@
         <v>0.7257735001824654</v>
       </c>
       <c r="D871" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E871">
         <v>0.4916217448397111</v>
@@ -45349,7 +45352,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45413,7 +45416,7 @@
         <v>0.7114203326982134</v>
       </c>
       <c r="D873" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E873">
         <v>0.4765662816987373</v>
@@ -45499,7 +45502,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45513,7 +45516,7 @@
         <v>0.6922020910541313</v>
       </c>
       <c r="D875" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E875">
         <v>0.4564076979558633</v>
@@ -45549,7 +45552,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45599,7 +45602,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45613,7 +45616,7 @@
         <v>0.6746197386642372</v>
       </c>
       <c r="D877" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E877">
         <v>0.4379650469780838</v>
@@ -45649,7 +45652,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -45713,7 +45716,7 @@
         <v>0.6658747168932573</v>
       </c>
       <c r="D879" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E879">
         <v>0.4287921342335999</v>
@@ -45813,7 +45816,7 @@
         <v>0.6087670811874686</v>
       </c>
       <c r="D881" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E881">
         <v>0.4389572093313259</v>
@@ -45863,7 +45866,7 @@
         <v>0.6755656193916719</v>
       </c>
       <c r="D882" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E882">
         <v>0.4389572093313259</v>
@@ -45963,7 +45966,7 @@
         <v>0.5714180816880337</v>
       </c>
       <c r="D884" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E884">
         <v>0.4021448333879176</v>
@@ -46007,13 +46010,13 @@
         <v>2</v>
       </c>
       <c r="B885" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C885">
-        <v>0.5674529864477105</v>
+        <v>0.6404704388275482</v>
       </c>
       <c r="D885" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E885">
         <v>0.4021448333879176</v>
@@ -46022,22 +46025,22 @@
         <v>-1</v>
       </c>
       <c r="G885">
-        <v>0.01135254701355229</v>
+        <v>0.01119952956117245</v>
       </c>
       <c r="H885">
         <v>0.01147785516661208</v>
       </c>
       <c r="I885">
-        <v>0.1653081530597929</v>
+        <v>0.2383256054396306</v>
       </c>
       <c r="J885">
         <v>1.614535033997692</v>
       </c>
       <c r="K885">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="L885">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="M885">
         <v>3.43</v>
@@ -46054,190 +46057,190 @@
     </row>
     <row r="886" spans="1:16">
       <c r="A886" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B886" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C886">
-        <v>0.6404704388275482</v>
+        <v>0.1598063964288423</v>
       </c>
       <c r="D886" t="s">
-        <v>205</v>
+        <v>335</v>
       </c>
       <c r="E886">
-        <v>0.4021448333879176</v>
+        <v>0.1371622895973914</v>
       </c>
       <c r="F886">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G886">
-        <v>0.01119952956117245</v>
+        <v>0.01214019360357116</v>
       </c>
       <c r="H886">
-        <v>0.01147785516661208</v>
+        <v>0.01218283771040261</v>
       </c>
       <c r="I886">
-        <v>0.2383256054396306</v>
+        <v>-0.02264410683145091</v>
       </c>
       <c r="J886">
-        <v>1.614535033997692</v>
+        <v>1.632205341572523</v>
       </c>
       <c r="K886">
-        <v>3.27</v>
+        <v>3.67</v>
       </c>
       <c r="L886">
-        <v>5.92</v>
+        <v>6.15</v>
       </c>
       <c r="M886">
-        <v>3.43</v>
+        <v>3.69</v>
       </c>
       <c r="N886">
-        <v>5.94</v>
+        <v>6.16</v>
       </c>
       <c r="O886">
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>193</v>
+        <v>475</v>
       </c>
     </row>
     <row r="887" spans="1:16">
       <c r="A887" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B887" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C887">
-        <v>0.1598063964288423</v>
+        <v>0.5826885330578513</v>
       </c>
       <c r="D887" t="s">
-        <v>336</v>
+        <v>204</v>
       </c>
       <c r="E887">
-        <v>0.1024505032602923</v>
+        <v>0.341535678406248</v>
       </c>
       <c r="F887">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G887">
-        <v>0.01214019360357116</v>
+        <v>0.01125731146694215</v>
       </c>
       <c r="H887">
-        <v>0.01201754949673971</v>
+        <v>0.01153846432159375</v>
       </c>
       <c r="I887">
-        <v>-0.05735589316855005</v>
+        <v>0.2411528546516033</v>
       </c>
       <c r="J887">
         <v>1.632205341572523</v>
       </c>
       <c r="K887">
-        <v>3.67</v>
+        <v>3.27</v>
       </c>
       <c r="L887">
-        <v>6.15</v>
+        <v>5.92</v>
       </c>
       <c r="M887">
-        <v>3.65</v>
+        <v>3.43</v>
       </c>
       <c r="N887">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="O887">
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="888" spans="1:16">
       <c r="A888" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B888" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C888">
-        <v>0.5099254113276217</v>
+        <v>0.011804494898219</v>
       </c>
       <c r="D888" t="s">
-        <v>205</v>
+        <v>336</v>
       </c>
       <c r="E888">
-        <v>0.341535678406248</v>
+        <v>-0.04474484839823045</v>
       </c>
       <c r="F888">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G888">
-        <v>0.01187007458867238</v>
+        <v>0.01228819550510178</v>
       </c>
       <c r="H888">
-        <v>0.01153846432159375</v>
+        <v>0.01216474484839823</v>
       </c>
       <c r="I888">
-        <v>0.1683897329213737</v>
+        <v>-0.05654934329644945</v>
       </c>
       <c r="J888">
-        <v>1.632205341572523</v>
+        <v>1.672532835177597</v>
       </c>
       <c r="K888">
-        <v>3.48</v>
+        <v>3.67</v>
       </c>
       <c r="L888">
-        <v>6.19</v>
+        <v>6.15</v>
       </c>
       <c r="M888">
-        <v>3.43</v>
+        <v>3.65</v>
       </c>
       <c r="N888">
-        <v>5.94</v>
+        <v>6.06</v>
       </c>
       <c r="O888">
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>474</v>
+        <v>195</v>
       </c>
     </row>
     <row r="889" spans="1:16">
       <c r="A889" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B889" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C889">
-        <v>0.5084341591477743</v>
+        <v>0.4508176289692569</v>
       </c>
       <c r="D889" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E889">
-        <v>0.341535678406248</v>
+        <v>0.2032123753408417</v>
       </c>
       <c r="F889">
         <v>-1</v>
       </c>
       <c r="G889">
-        <v>0.01141156584085223</v>
+        <v>0.01138918237103074</v>
       </c>
       <c r="H889">
-        <v>0.01153846432159375</v>
+        <v>0.01167678762465916</v>
       </c>
       <c r="I889">
-        <v>0.1668984807415264</v>
+        <v>0.2476052536284152</v>
       </c>
       <c r="J889">
-        <v>1.632205341572523</v>
+        <v>1.672532835177597</v>
       </c>
       <c r="K889">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="L889">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="M889">
         <v>3.43</v>
@@ -46249,39 +46252,39 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>474</v>
+        <v>195</v>
       </c>
     </row>
     <row r="890" spans="1:16">
       <c r="A890" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B890" t="s">
         <v>201</v>
       </c>
       <c r="C890">
-        <v>0.5826885330578513</v>
+        <v>0.2968499181634146</v>
       </c>
       <c r="D890" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E890">
-        <v>0.341535678406248</v>
+        <v>0.04171107623868942</v>
       </c>
       <c r="F890">
         <v>-1</v>
       </c>
       <c r="G890">
-        <v>0.01125731146694215</v>
+        <v>0.01154315008183659</v>
       </c>
       <c r="H890">
-        <v>0.01153846432159375</v>
+        <v>0.01183828892376131</v>
       </c>
       <c r="I890">
-        <v>0.2411528546516033</v>
+        <v>0.2551388419247251</v>
       </c>
       <c r="J890">
-        <v>1.632205341572523</v>
+        <v>1.719617762029537</v>
       </c>
       <c r="K890">
         <v>3.27</v>
@@ -46299,7 +46302,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>474</v>
+        <v>196</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46307,87 +46310,87 @@
         <v>0</v>
       </c>
       <c r="B891" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C891">
-        <v>0.011804494898219</v>
+        <v>0.3224506058857468</v>
       </c>
       <c r="D891" t="s">
-        <v>336</v>
+        <v>204</v>
       </c>
       <c r="E891">
-        <v>-0.04474484839823045</v>
+        <v>0.06856439699942296</v>
       </c>
       <c r="F891">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G891">
-        <v>0.01228819550510178</v>
+        <v>0.01151754939411425</v>
       </c>
       <c r="H891">
-        <v>0.01216474484839823</v>
+        <v>0.01181143560300058</v>
       </c>
       <c r="I891">
-        <v>-0.05654934329644945</v>
+        <v>0.2538862088863238</v>
       </c>
       <c r="J891">
-        <v>1.672532835177597</v>
+        <v>1.711788805539527</v>
       </c>
       <c r="K891">
-        <v>3.67</v>
+        <v>3.27</v>
       </c>
       <c r="L891">
-        <v>6.15</v>
+        <v>5.92</v>
       </c>
       <c r="M891">
-        <v>3.65</v>
+        <v>3.43</v>
       </c>
       <c r="N891">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="O891">
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>195</v>
+        <v>335</v>
       </c>
     </row>
     <row r="892" spans="1:16">
       <c r="A892" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B892" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C892">
-        <v>0.3737403305068252</v>
+        <v>0.4717536877718773</v>
       </c>
       <c r="D892" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E892">
-        <v>0.2032123753408417</v>
+        <v>0.2251728284579633</v>
       </c>
       <c r="F892">
         <v>-1</v>
       </c>
       <c r="G892">
-        <v>0.01154625966949317</v>
+        <v>0.01136824631222812</v>
       </c>
       <c r="H892">
-        <v>0.01167678762465916</v>
+        <v>0.01165482717154204</v>
       </c>
       <c r="I892">
-        <v>0.1705279551659835</v>
+        <v>0.246580859313914</v>
       </c>
       <c r="J892">
-        <v>1.672532835177597</v>
+        <v>1.666130370711964</v>
       </c>
       <c r="K892">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="L892">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="M892">
         <v>3.43</v>
@@ -46399,57 +46402,57 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>195</v>
+        <v>336</v>
       </c>
     </row>
     <row r="893" spans="1:16">
       <c r="A893" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B893" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C893">
-        <v>0.4508176289692569</v>
+        <v>0.1619145765582886</v>
       </c>
       <c r="D893" t="s">
-        <v>205</v>
+        <v>337</v>
       </c>
       <c r="E893">
-        <v>0.2032123753408417</v>
+        <v>0.2885276136294843</v>
       </c>
       <c r="F893">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G893">
-        <v>0.01138918237103074</v>
+        <v>0.01205808542344171</v>
       </c>
       <c r="H893">
-        <v>0.01167678762465916</v>
+        <v>0.01185147238637052</v>
       </c>
       <c r="I893">
-        <v>0.2476052536284152</v>
+        <v>0.1266130370711958</v>
       </c>
       <c r="J893">
-        <v>1.672532835177597</v>
+        <v>1.666130370711964</v>
       </c>
       <c r="K893">
-        <v>3.27</v>
+        <v>3.57</v>
       </c>
       <c r="L893">
-        <v>5.92</v>
+        <v>6.11</v>
       </c>
       <c r="M893">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="N893">
-        <v>5.94</v>
+        <v>6.07</v>
       </c>
       <c r="O893">
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>195</v>
+        <v>336</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46460,28 +46463,28 @@
         <v>201</v>
       </c>
       <c r="C894">
-        <v>0.2968499181634146</v>
+        <v>0.5136993922788848</v>
       </c>
       <c r="D894" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E894">
-        <v>0.04171107623868942</v>
+        <v>0.2691709221763228</v>
       </c>
       <c r="F894">
         <v>-1</v>
       </c>
       <c r="G894">
-        <v>0.01154315008183659</v>
+        <v>0.01132630060772112</v>
       </c>
       <c r="H894">
-        <v>0.01183828892376131</v>
+        <v>0.01161082907782368</v>
       </c>
       <c r="I894">
-        <v>0.2551388419247251</v>
+        <v>0.2445284701025621</v>
       </c>
       <c r="J894">
-        <v>1.719617762029537</v>
+        <v>1.653302938141014</v>
       </c>
       <c r="K894">
         <v>3.27</v>
@@ -46499,57 +46502,57 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>196</v>
+        <v>476</v>
       </c>
     </row>
     <row r="895" spans="1:16">
       <c r="A895" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B895" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C895">
-        <v>0.3224506058857468</v>
+        <v>0.2077085108365813</v>
       </c>
       <c r="D895" t="s">
-        <v>205</v>
+        <v>338</v>
       </c>
       <c r="E895">
-        <v>0.06856439699942296</v>
+        <v>0.4045012159904244</v>
       </c>
       <c r="F895">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G895">
-        <v>0.01151754939411425</v>
+        <v>0.01201229148916342</v>
       </c>
       <c r="H895">
-        <v>0.01181143560300058</v>
+        <v>0.01141549878400958</v>
       </c>
       <c r="I895">
-        <v>0.2538862088863238</v>
+        <v>0.1967927051538432</v>
       </c>
       <c r="J895">
-        <v>1.711788805539527</v>
+        <v>1.653302938141014</v>
       </c>
       <c r="K895">
-        <v>3.27</v>
+        <v>3.57</v>
       </c>
       <c r="L895">
-        <v>5.92</v>
+        <v>6.11</v>
       </c>
       <c r="M895">
-        <v>3.43</v>
+        <v>3.33</v>
       </c>
       <c r="N895">
-        <v>5.94</v>
+        <v>5.91</v>
       </c>
       <c r="O895">
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>335</v>
+        <v>476</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46560,28 +46563,28 @@
         <v>201</v>
       </c>
       <c r="C896">
-        <v>0.4717536877718773</v>
+        <v>1.339409495526739</v>
       </c>
       <c r="D896" t="s">
-        <v>205</v>
+        <v>339</v>
       </c>
       <c r="E896">
-        <v>0.2251728284579633</v>
+        <v>1.219290665046315</v>
       </c>
       <c r="F896">
         <v>-1</v>
       </c>
       <c r="G896">
-        <v>0.01136824631222812</v>
+        <v>0.01050059050447326</v>
       </c>
       <c r="H896">
-        <v>0.01165482717154204</v>
+        <v>0.01080070933495368</v>
       </c>
       <c r="I896">
-        <v>0.246580859313914</v>
+        <v>0.1201188304804246</v>
       </c>
       <c r="J896">
-        <v>1.666130370711964</v>
+        <v>1.400792203202832</v>
       </c>
       <c r="K896">
         <v>3.27</v>
@@ -46590,316 +46593,166 @@
         <v>5.92</v>
       </c>
       <c r="M896">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="N896">
-        <v>5.94</v>
+        <v>6.01</v>
       </c>
       <c r="O896">
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>336</v>
+        <v>202</v>
       </c>
     </row>
     <row r="897" spans="1:16">
       <c r="A897" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B897" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C897">
-        <v>0.5136993922788848</v>
+        <v>1.135282743014287</v>
       </c>
       <c r="D897" t="s">
-        <v>205</v>
+        <v>340</v>
       </c>
       <c r="E897">
-        <v>0.2691709221763228</v>
+        <v>1.269330275206457</v>
       </c>
       <c r="F897">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G897">
-        <v>0.01132630060772112</v>
+        <v>0.01074471725698571</v>
       </c>
       <c r="H897">
-        <v>0.01161082907782368</v>
+        <v>0.01071066972479354</v>
       </c>
       <c r="I897">
-        <v>0.2445284701025621</v>
+        <v>0.1340475321921701</v>
       </c>
       <c r="J897">
-        <v>1.653302938141014</v>
+        <v>1.400792203202832</v>
       </c>
       <c r="K897">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="L897">
-        <v>5.92</v>
+        <v>5.94</v>
       </c>
       <c r="M897">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="N897">
-        <v>5.94</v>
+        <v>5.99</v>
       </c>
       <c r="O897">
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>475</v>
+        <v>202</v>
       </c>
     </row>
     <row r="898" spans="1:16">
       <c r="A898" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B898" t="s">
         <v>204</v>
       </c>
       <c r="C898">
-        <v>0.2077085108365813</v>
+        <v>1.05728794369645</v>
       </c>
       <c r="D898" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E898">
-        <v>0.3330388046506823</v>
+        <v>1.192699816401468</v>
       </c>
       <c r="F898">
         <v>1</v>
       </c>
       <c r="G898">
-        <v>0.01201229148916342</v>
+        <v>0.01082271205630355</v>
       </c>
       <c r="H898">
-        <v>0.01180696119534932</v>
+        <v>0.01078730018359853</v>
       </c>
       <c r="I898">
-        <v>0.125330293814101</v>
+        <v>0.135411872705018</v>
       </c>
       <c r="J898">
-        <v>1.653302938141014</v>
+        <v>1.423531211750306</v>
       </c>
       <c r="K898">
-        <v>3.57</v>
+        <v>3.43</v>
       </c>
       <c r="L898">
-        <v>6.11</v>
+        <v>5.94</v>
       </c>
       <c r="M898">
-        <v>3.47</v>
+        <v>3.37</v>
       </c>
       <c r="N898">
-        <v>6.07</v>
+        <v>5.99</v>
       </c>
       <c r="O898">
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="899" spans="1:16">
       <c r="A899" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B899" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C899">
-        <v>1.339409495526739</v>
+        <v>1.205758567931456</v>
       </c>
       <c r="D899" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E899">
-        <v>1.219290665046315</v>
+        <v>1.131523255813954</v>
       </c>
       <c r="F899">
         <v>-1</v>
       </c>
       <c r="G899">
-        <v>0.01050059050447326</v>
+        <v>0.01091424143206854</v>
       </c>
       <c r="H899">
-        <v>0.01080070933495368</v>
+        <v>0.01086847674418605</v>
       </c>
       <c r="I899">
-        <v>0.1201188304804246</v>
+        <v>0.07423531211750234</v>
       </c>
       <c r="J899">
-        <v>1.400792203202832</v>
+        <v>1.423531211750306</v>
       </c>
       <c r="K899">
-        <v>3.27</v>
+        <v>3.41</v>
       </c>
       <c r="L899">
-        <v>5.92</v>
+        <v>6.06</v>
       </c>
       <c r="M899">
         <v>3.42</v>
       </c>
       <c r="N899">
-        <v>6.01</v>
+        <v>6</v>
       </c>
       <c r="O899">
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="900" spans="1:16">
-      <c r="A900" s="1">
-        <v>1</v>
-      </c>
-      <c r="B900" t="s">
-        <v>205</v>
-      </c>
-      <c r="C900">
-        <v>1.135282743014287</v>
-      </c>
-      <c r="D900" t="s">
-        <v>339</v>
-      </c>
-      <c r="E900">
-        <v>1.269330275206457</v>
-      </c>
-      <c r="F900">
-        <v>1</v>
-      </c>
-      <c r="G900">
-        <v>0.01074471725698571</v>
-      </c>
-      <c r="H900">
-        <v>0.01071066972479354</v>
-      </c>
-      <c r="I900">
-        <v>0.1340475321921701</v>
-      </c>
-      <c r="J900">
-        <v>1.400792203202832</v>
-      </c>
-      <c r="K900">
-        <v>3.43</v>
-      </c>
-      <c r="L900">
-        <v>5.94</v>
-      </c>
-      <c r="M900">
-        <v>3.37</v>
-      </c>
-      <c r="N900">
-        <v>5.99</v>
-      </c>
-      <c r="O900">
-        <v>1</v>
-      </c>
-      <c r="P900" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="901" spans="1:16">
-      <c r="A901" s="1">
-        <v>2</v>
-      </c>
-      <c r="B901" t="s">
-        <v>204</v>
-      </c>
-      <c r="C901">
-        <v>1.109171834565891</v>
-      </c>
-      <c r="D901" t="s">
-        <v>340</v>
-      </c>
-      <c r="E901">
-        <v>1.245361963334569</v>
-      </c>
-      <c r="F901">
-        <v>1</v>
-      </c>
-      <c r="G901">
-        <v>0.01111082816543411</v>
-      </c>
-      <c r="H901">
-        <v>0.01057463803666543</v>
-      </c>
-      <c r="I901">
-        <v>0.1361901287686784</v>
-      </c>
-      <c r="J901">
-        <v>1.400792203202832</v>
-      </c>
-      <c r="K901">
-        <v>3.57</v>
-      </c>
-      <c r="L901">
-        <v>6.11</v>
-      </c>
-      <c r="M901">
-        <v>3.33</v>
-      </c>
-      <c r="N901">
-        <v>5.91</v>
-      </c>
-      <c r="O901">
-        <v>1</v>
-      </c>
-      <c r="P901" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="902" spans="1:16">
-      <c r="A902" s="1">
-        <v>0</v>
-      </c>
-      <c r="B902" t="s">
-        <v>205</v>
-      </c>
-      <c r="C902">
-        <v>1.05728794369645</v>
-      </c>
-      <c r="D902" t="s">
-        <v>339</v>
-      </c>
-      <c r="E902">
-        <v>1.192699816401468</v>
-      </c>
-      <c r="F902">
-        <v>1</v>
-      </c>
-      <c r="G902">
-        <v>0.01082271205630355</v>
-      </c>
-      <c r="H902">
-        <v>0.01078730018359853</v>
-      </c>
-      <c r="I902">
-        <v>0.135411872705018</v>
-      </c>
-      <c r="J902">
-        <v>1.423531211750306</v>
-      </c>
-      <c r="K902">
-        <v>3.43</v>
-      </c>
-      <c r="L902">
-        <v>5.94</v>
-      </c>
-      <c r="M902">
-        <v>3.37</v>
-      </c>
-      <c r="N902">
-        <v>5.99</v>
-      </c>
-      <c r="O902">
-        <v>1</v>
-      </c>
-      <c r="P902" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="477">
   <si>
     <t>trade_time</t>
   </si>
@@ -1031,9 +1031,6 @@
   </si>
   <si>
     <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-07-20</t>
@@ -1902,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1952,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2002,7 +1999,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2052,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2102,7 +2099,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2152,7 +2149,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2202,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2252,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2302,7 +2299,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2352,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2402,7 +2399,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2452,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2502,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2552,7 +2549,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2602,7 +2599,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2652,7 +2649,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2702,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2752,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2802,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2852,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2902,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2952,7 +2949,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3002,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3052,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3102,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3152,7 +3149,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3202,7 +3199,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3252,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3302,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3352,7 +3349,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3402,7 +3399,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3452,7 +3449,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3502,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3552,7 +3549,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3602,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3652,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3702,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3752,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3802,7 +3799,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3852,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3902,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3952,7 +3949,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4002,7 +3999,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4052,7 +4049,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4102,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4152,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4202,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4252,7 +4249,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4302,7 +4299,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4352,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4402,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4652,7 +4649,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4702,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4752,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4802,7 +4799,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4852,7 +4849,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4902,7 +4899,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5052,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5102,7 +5099,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5252,7 +5249,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5302,7 +5299,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5352,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5402,7 +5399,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5552,7 +5549,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5602,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5652,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5702,7 +5699,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5752,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6002,7 +5999,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6052,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6102,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6152,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6502,7 +6499,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6552,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6602,7 +6599,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6852,7 +6849,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6902,7 +6899,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6952,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7002,7 +6999,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7052,7 +7049,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7102,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7152,7 +7149,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7352,7 +7349,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7402,7 +7399,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7452,7 +7449,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7502,7 +7499,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7552,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7602,7 +7599,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7652,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7702,7 +7699,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7752,7 +7749,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7802,7 +7799,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7852,7 +7849,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7902,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7952,7 +7949,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8002,7 +7999,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8052,7 +8049,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8102,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8152,7 +8149,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8202,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8252,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8302,7 +8299,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8352,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8402,7 +8399,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -9002,7 +8999,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9052,7 +9049,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9102,7 +9099,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9152,7 +9149,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9202,7 +9199,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9252,7 +9249,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9302,7 +9299,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9452,7 +9449,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10052,7 +10049,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10102,7 +10099,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10152,7 +10149,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10202,7 +10199,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10252,7 +10249,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10452,7 +10449,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10502,7 +10499,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10552,7 +10549,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10752,7 +10749,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10802,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10852,7 +10849,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10902,7 +10899,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10952,7 +10949,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11002,7 +10999,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11052,7 +11049,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11102,7 +11099,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11152,7 +11149,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11352,7 +11349,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11402,7 +11399,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11452,7 +11449,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11502,7 +11499,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11552,7 +11549,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11602,7 +11599,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11652,7 +11649,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11702,7 +11699,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11752,7 +11749,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11802,7 +11799,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11852,7 +11849,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11902,7 +11899,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12152,7 +12149,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12202,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12252,7 +12249,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12302,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12352,7 +12349,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12652,7 +12649,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12702,7 +12699,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12752,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12802,7 +12799,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12852,7 +12849,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12902,7 +12899,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12952,7 +12949,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -13002,7 +12999,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -13052,7 +13049,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13102,7 +13099,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -13152,7 +13149,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13552,7 +13549,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13602,7 +13599,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13652,7 +13649,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13702,7 +13699,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -14202,7 +14199,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14252,7 +14249,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14302,7 +14299,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14352,7 +14349,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14402,7 +14399,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14452,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14502,7 +14499,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14552,7 +14549,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14602,7 +14599,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14652,7 +14649,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14702,7 +14699,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14752,7 +14749,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14802,7 +14799,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14852,7 +14849,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14902,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14952,7 +14949,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15002,7 +14999,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15052,7 +15049,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15102,7 +15099,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15152,7 +15149,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15202,7 +15199,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15752,7 +15749,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15802,7 +15799,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15852,7 +15849,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15902,7 +15899,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15952,7 +15949,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -16002,7 +15999,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16052,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16102,7 +16099,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16152,7 +16149,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16202,7 +16199,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16252,7 +16249,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16302,7 +16299,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16352,7 +16349,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16402,7 +16399,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16452,7 +16449,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16502,7 +16499,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16552,7 +16549,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16602,7 +16599,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16652,7 +16649,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16852,7 +16849,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16902,7 +16899,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16952,7 +16949,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17352,7 +17349,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17402,7 +17399,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17452,7 +17449,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17502,7 +17499,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17752,7 +17749,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17802,7 +17799,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17852,7 +17849,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17902,7 +17899,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18902,7 +18899,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18952,7 +18949,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19002,7 +18999,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19052,7 +19049,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19102,7 +19099,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19152,7 +19149,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19202,7 +19199,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19252,7 +19249,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19302,7 +19299,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19352,7 +19349,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19402,7 +19399,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19452,7 +19449,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19502,7 +19499,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19552,7 +19549,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19602,7 +19599,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19652,7 +19649,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19702,7 +19699,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -20002,7 +19999,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20052,7 +20049,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20102,7 +20099,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20152,7 +20149,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20202,7 +20199,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20252,7 +20249,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20302,7 +20299,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20352,7 +20349,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20402,7 +20399,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20452,7 +20449,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20502,7 +20499,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20552,7 +20549,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20602,7 +20599,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20652,7 +20649,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20952,7 +20949,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21002,7 +20999,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21052,7 +21049,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21102,7 +21099,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21152,7 +21149,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21202,7 +21199,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21252,7 +21249,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21302,7 +21299,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21552,7 +21549,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21602,7 +21599,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21652,7 +21649,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21702,7 +21699,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21752,7 +21749,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21802,7 +21799,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21852,7 +21849,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21902,7 +21899,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21952,7 +21949,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22002,7 +21999,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -24152,7 +24149,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24202,7 +24199,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24252,7 +24249,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24302,7 +24299,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24352,7 +24349,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24402,7 +24399,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24452,7 +24449,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24502,7 +24499,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -27602,7 +27599,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27652,7 +27649,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27702,7 +27699,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27752,7 +27749,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27802,7 +27799,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27852,7 +27849,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27902,7 +27899,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27952,7 +27949,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28002,7 +27999,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28052,7 +28049,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28102,7 +28099,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28152,7 +28149,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28202,7 +28199,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28252,7 +28249,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28302,7 +28299,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28752,7 +28749,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28802,7 +28799,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28852,7 +28849,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28902,7 +28899,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29102,7 +29099,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29152,7 +29149,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29202,7 +29199,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29252,7 +29249,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29302,7 +29299,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29352,7 +29349,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29402,7 +29399,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29452,7 +29449,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29502,7 +29499,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29552,7 +29549,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29602,7 +29599,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29652,7 +29649,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30152,7 +30149,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30202,7 +30199,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30252,7 +30249,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30302,7 +30299,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30352,7 +30349,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30402,7 +30399,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30452,7 +30449,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30502,7 +30499,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30552,7 +30549,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30602,7 +30599,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31202,7 +31199,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31252,7 +31249,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31302,7 +31299,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31352,7 +31349,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31402,7 +31399,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31452,7 +31449,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31502,7 +31499,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31952,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32002,7 +31999,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32152,7 +32149,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32202,7 +32199,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32252,7 +32249,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32302,7 +32299,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32352,7 +32349,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32402,7 +32399,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -35352,7 +35349,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35402,7 +35399,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35452,7 +35449,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35502,7 +35499,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35552,7 +35549,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35602,7 +35599,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35652,7 +35649,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35702,7 +35699,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35752,7 +35749,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35802,7 +35799,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35852,7 +35849,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35902,7 +35899,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35952,7 +35949,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36002,7 +35999,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36052,7 +36049,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36102,7 +36099,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36152,7 +36149,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36202,7 +36199,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36252,7 +36249,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36452,7 +36449,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36502,7 +36499,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36552,7 +36549,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36602,7 +36599,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36652,7 +36649,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36702,7 +36699,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36752,7 +36749,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36802,7 +36799,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36852,7 +36849,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36902,7 +36899,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36952,7 +36949,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37002,7 +36999,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37052,7 +37049,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37102,7 +37099,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37152,7 +37149,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37202,7 +37199,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37252,7 +37249,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37302,7 +37299,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37352,7 +37349,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37402,7 +37399,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37452,7 +37449,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37702,7 +37699,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37752,7 +37749,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37802,7 +37799,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37852,7 +37849,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37902,7 +37899,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37952,7 +37949,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38002,7 +37999,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38052,7 +38049,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38102,7 +38099,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38152,7 +38149,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38202,7 +38199,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38252,7 +38249,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38302,7 +38299,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38352,7 +38349,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38402,7 +38399,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38452,7 +38449,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38502,7 +38499,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38552,7 +38549,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38602,7 +38599,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38652,7 +38649,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38702,7 +38699,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38752,7 +38749,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38802,7 +38799,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38852,7 +38849,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38902,7 +38899,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38952,7 +38949,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39002,7 +38999,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39052,7 +39049,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39102,7 +39099,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39152,7 +39149,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39202,7 +39199,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39252,7 +39249,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39302,7 +39299,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39352,7 +39349,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39402,7 +39399,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39452,7 +39449,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39502,7 +39499,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39552,7 +39549,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39602,7 +39599,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39652,7 +39649,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39702,7 +39699,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39752,7 +39749,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39802,7 +39799,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39852,7 +39849,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39902,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39952,7 +39949,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40002,7 +39999,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40052,7 +40049,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40252,7 +40249,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40302,7 +40299,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40352,7 +40349,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40452,7 +40449,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40502,7 +40499,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40552,7 +40549,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40602,7 +40599,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40652,7 +40649,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40702,7 +40699,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -40752,7 +40749,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40802,7 +40799,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40852,7 +40849,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40902,7 +40899,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40952,7 +40949,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41002,7 +40999,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41052,7 +41049,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41102,7 +41099,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41152,7 +41149,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41202,7 +41199,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41252,7 +41249,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41302,7 +41299,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41352,7 +41349,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41402,7 +41399,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41452,7 +41449,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41502,7 +41499,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41552,7 +41549,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41602,7 +41599,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41652,7 +41649,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -41952,7 +41949,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42002,7 +41999,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42052,7 +42049,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42102,7 +42099,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42252,7 +42249,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42302,7 +42299,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42452,7 +42449,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42502,7 +42499,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42552,7 +42549,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42602,7 +42599,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42652,7 +42649,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42852,7 +42849,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42902,7 +42899,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42952,7 +42949,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43002,7 +42999,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43052,7 +43049,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43102,7 +43099,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43152,7 +43149,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43202,7 +43199,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43252,7 +43249,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43602,7 +43599,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43652,7 +43649,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43702,7 +43699,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43902,7 +43899,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43952,7 +43949,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44002,7 +43999,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44052,7 +44049,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44102,7 +44099,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44152,7 +44149,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44302,7 +44299,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44352,7 +44349,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44402,7 +44399,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44452,7 +44449,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44502,7 +44499,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44752,7 +44749,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44802,7 +44799,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44852,7 +44849,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44902,7 +44899,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45202,7 +45199,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45252,7 +45249,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45302,7 +45299,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45352,7 +45349,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45502,7 +45499,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45552,7 +45549,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45602,7 +45599,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45652,7 +45649,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46102,7 +46099,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46152,7 +46149,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46166,10 +46163,10 @@
         <v>0.011804494898219</v>
       </c>
       <c r="D888" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E888">
-        <v>-0.04474484839823045</v>
+        <v>-0.0116461618053334</v>
       </c>
       <c r="F888">
         <v>1</v>
@@ -46178,10 +46175,10 @@
         <v>0.01228819550510178</v>
       </c>
       <c r="H888">
-        <v>0.01216474484839823</v>
+        <v>0.01233164616180533</v>
       </c>
       <c r="I888">
-        <v>-0.05654934329644945</v>
+        <v>-0.0234506567035524</v>
       </c>
       <c r="J888">
         <v>1.672532835177597</v>
@@ -46193,10 +46190,10 @@
         <v>6.15</v>
       </c>
       <c r="M888">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="N888">
-        <v>6.06</v>
+        <v>6.16</v>
       </c>
       <c r="O888">
         <v>1</v>
@@ -46502,7 +46499,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46552,7 +46549,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46560,43 +46557,43 @@
         <v>0</v>
       </c>
       <c r="B896" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C896">
-        <v>1.339409495526739</v>
+        <v>1.135282743014287</v>
       </c>
       <c r="D896" t="s">
         <v>339</v>
       </c>
       <c r="E896">
-        <v>1.219290665046315</v>
+        <v>1.269330275206457</v>
       </c>
       <c r="F896">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G896">
-        <v>0.01050059050447326</v>
+        <v>0.01074471725698571</v>
       </c>
       <c r="H896">
-        <v>0.01080070933495368</v>
+        <v>0.01071066972479354</v>
       </c>
       <c r="I896">
-        <v>0.1201188304804246</v>
+        <v>0.1340475321921701</v>
       </c>
       <c r="J896">
         <v>1.400792203202832</v>
       </c>
       <c r="K896">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="L896">
-        <v>5.92</v>
+        <v>5.94</v>
       </c>
       <c r="M896">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="N896">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="O896">
         <v>1</v>
@@ -46610,43 +46607,43 @@
         <v>1</v>
       </c>
       <c r="B897" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C897">
-        <v>1.135282743014287</v>
+        <v>1.283298587078343</v>
       </c>
       <c r="D897" t="s">
         <v>340</v>
       </c>
       <c r="E897">
-        <v>1.269330275206457</v>
+        <v>1.209290665046315</v>
       </c>
       <c r="F897">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G897">
-        <v>0.01074471725698571</v>
+        <v>0.01083670141292166</v>
       </c>
       <c r="H897">
-        <v>0.01071066972479354</v>
+        <v>0.01079070933495369</v>
       </c>
       <c r="I897">
-        <v>0.1340475321921701</v>
+        <v>0.07400792203202755</v>
       </c>
       <c r="J897">
         <v>1.400792203202832</v>
       </c>
       <c r="K897">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="L897">
-        <v>5.94</v>
+        <v>6.06</v>
       </c>
       <c r="M897">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
       <c r="N897">
-        <v>5.99</v>
+        <v>6</v>
       </c>
       <c r="O897">
         <v>1</v>
@@ -46666,7 +46663,7 @@
         <v>1.05728794369645</v>
       </c>
       <c r="D898" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E898">
         <v>1.192699816401468</v>
@@ -46702,7 +46699,7 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -46716,7 +46713,7 @@
         <v>1.205758567931456</v>
       </c>
       <c r="D899" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E899">
         <v>1.131523255813954</v>
@@ -46752,7 +46749,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="478">
   <si>
     <t>trade_time</t>
   </si>
@@ -1031,6 +1031,9 @@
   </si>
   <si>
     <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-07-13</t>
   </si>
   <si>
     <t>2021-07-20</t>
@@ -1899,7 +1902,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1949,7 +1952,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1999,7 +2002,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2049,7 +2052,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2099,7 +2102,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2149,7 +2152,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2199,7 +2202,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2249,7 +2252,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2299,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2349,7 +2352,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2399,7 +2402,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2449,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2499,7 +2502,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2549,7 +2552,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2599,7 +2602,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2649,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2699,7 +2702,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2749,7 +2752,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2799,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2849,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2899,7 +2902,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2949,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2999,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3049,7 +3052,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3099,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3149,7 +3152,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3199,7 +3202,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3249,7 +3252,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3299,7 +3302,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3349,7 +3352,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3399,7 +3402,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3449,7 +3452,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3499,7 +3502,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3549,7 +3552,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3599,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3649,7 +3652,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3699,7 +3702,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3749,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3799,7 +3802,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3849,7 +3852,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3899,7 +3902,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3949,7 +3952,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3999,7 +4002,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4049,7 +4052,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4099,7 +4102,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4149,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4199,7 +4202,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4249,7 +4252,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4299,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4349,7 +4352,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4399,7 +4402,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4649,7 +4652,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4699,7 +4702,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4749,7 +4752,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4799,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4849,7 +4852,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4899,7 +4902,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5049,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5099,7 +5102,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5249,7 +5252,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5299,7 +5302,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5349,7 +5352,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5399,7 +5402,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5549,7 +5552,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5599,7 +5602,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5649,7 +5652,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5699,7 +5702,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5749,7 +5752,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5999,7 +6002,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6049,7 +6052,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6099,7 +6102,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6149,7 +6152,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6499,7 +6502,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6549,7 +6552,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6599,7 +6602,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6849,7 +6852,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6899,7 +6902,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6949,7 +6952,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6999,7 +7002,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7049,7 +7052,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7099,7 +7102,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7149,7 +7152,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7349,7 +7352,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7399,7 +7402,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7449,7 +7452,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7499,7 +7502,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7549,7 +7552,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7599,7 +7602,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7649,7 +7652,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7699,7 +7702,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7749,7 +7752,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7799,7 +7802,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7849,7 +7852,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7899,7 +7902,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7949,7 +7952,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7999,7 +8002,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8049,7 +8052,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8099,7 +8102,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8149,7 +8152,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8199,7 +8202,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8249,7 +8252,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8299,7 +8302,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8349,7 +8352,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8399,7 +8402,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8999,7 +9002,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9049,7 +9052,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9099,7 +9102,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9149,7 +9152,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9199,7 +9202,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9249,7 +9252,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9299,7 +9302,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9449,7 +9452,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10049,7 +10052,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10099,7 +10102,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10149,7 +10152,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10199,7 +10202,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10249,7 +10252,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10449,7 +10452,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10499,7 +10502,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10549,7 +10552,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10749,7 +10752,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10799,7 +10802,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10849,7 +10852,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10899,7 +10902,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10949,7 +10952,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10999,7 +11002,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11049,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11099,7 +11102,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11149,7 +11152,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11349,7 +11352,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11399,7 +11402,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11449,7 +11452,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11499,7 +11502,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11549,7 +11552,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11599,7 +11602,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11649,7 +11652,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11699,7 +11702,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11749,7 +11752,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11799,7 +11802,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11849,7 +11852,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11899,7 +11902,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12149,7 +12152,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12199,7 +12202,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12249,7 +12252,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12299,7 +12302,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12349,7 +12352,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12649,7 +12652,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12699,7 +12702,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12749,7 +12752,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12799,7 +12802,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12849,7 +12852,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12899,7 +12902,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12949,7 +12952,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12999,7 +13002,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -13049,7 +13052,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13099,7 +13102,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -13149,7 +13152,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13549,7 +13552,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13599,7 +13602,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13649,7 +13652,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13699,7 +13702,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -14199,7 +14202,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14249,7 +14252,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14299,7 +14302,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14349,7 +14352,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14399,7 +14402,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14449,7 +14452,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14499,7 +14502,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14549,7 +14552,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14599,7 +14602,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14649,7 +14652,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14699,7 +14702,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14749,7 +14752,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14799,7 +14802,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14849,7 +14852,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14899,7 +14902,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14949,7 +14952,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14999,7 +15002,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15049,7 +15052,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15099,7 +15102,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15149,7 +15152,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15199,7 +15202,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15749,7 +15752,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15799,7 +15802,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15849,7 +15852,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15899,7 +15902,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15949,7 +15952,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15999,7 +16002,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16049,7 +16052,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16099,7 +16102,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16149,7 +16152,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16199,7 +16202,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16249,7 +16252,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16299,7 +16302,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16349,7 +16352,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16399,7 +16402,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16449,7 +16452,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16499,7 +16502,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16549,7 +16552,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16599,7 +16602,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16649,7 +16652,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16849,7 +16852,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16899,7 +16902,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16949,7 +16952,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17349,7 +17352,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17399,7 +17402,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17449,7 +17452,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17499,7 +17502,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17749,7 +17752,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17799,7 +17802,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17849,7 +17852,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17899,7 +17902,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18899,7 +18902,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18949,7 +18952,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18999,7 +19002,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19049,7 +19052,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19099,7 +19102,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19149,7 +19152,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19199,7 +19202,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19249,7 +19252,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19299,7 +19302,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19349,7 +19352,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19399,7 +19402,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19449,7 +19452,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19499,7 +19502,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19549,7 +19552,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19599,7 +19602,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19649,7 +19652,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19699,7 +19702,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19999,7 +20002,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20049,7 +20052,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20099,7 +20102,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20149,7 +20152,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20199,7 +20202,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20249,7 +20252,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20299,7 +20302,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20349,7 +20352,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20399,7 +20402,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20449,7 +20452,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20499,7 +20502,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20549,7 +20552,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20599,7 +20602,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20649,7 +20652,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20949,7 +20952,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20999,7 +21002,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21049,7 +21052,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21099,7 +21102,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21149,7 +21152,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21199,7 +21202,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21249,7 +21252,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21299,7 +21302,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21549,7 +21552,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21599,7 +21602,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21649,7 +21652,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21699,7 +21702,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21749,7 +21752,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21799,7 +21802,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21849,7 +21852,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21899,7 +21902,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21949,7 +21952,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21999,7 +22002,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -24149,7 +24152,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24199,7 +24202,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24249,7 +24252,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24299,7 +24302,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24349,7 +24352,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24399,7 +24402,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24449,7 +24452,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24499,7 +24502,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -27599,7 +27602,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27649,7 +27652,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27699,7 +27702,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27749,7 +27752,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27799,7 +27802,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27849,7 +27852,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27899,7 +27902,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27949,7 +27952,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27999,7 +28002,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28049,7 +28052,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28099,7 +28102,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28149,7 +28152,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28199,7 +28202,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28249,7 +28252,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28299,7 +28302,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28749,7 +28752,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28799,7 +28802,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28849,7 +28852,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28899,7 +28902,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29099,7 +29102,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29149,7 +29152,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29199,7 +29202,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29249,7 +29252,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29299,7 +29302,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29349,7 +29352,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29399,7 +29402,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29449,7 +29452,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29499,7 +29502,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29549,7 +29552,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29599,7 +29602,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29649,7 +29652,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30149,7 +30152,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30199,7 +30202,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30249,7 +30252,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30299,7 +30302,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30349,7 +30352,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30399,7 +30402,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30449,7 +30452,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30499,7 +30502,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30549,7 +30552,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30599,7 +30602,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31199,7 +31202,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31249,7 +31252,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31299,7 +31302,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31349,7 +31352,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31399,7 +31402,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31449,7 +31452,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31499,7 +31502,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31949,7 +31952,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31999,7 +32002,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32149,7 +32152,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32199,7 +32202,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32249,7 +32252,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32299,7 +32302,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32349,7 +32352,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32399,7 +32402,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -35349,7 +35352,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35399,7 +35402,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35449,7 +35452,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35499,7 +35502,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35549,7 +35552,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35599,7 +35602,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35649,7 +35652,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35699,7 +35702,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35749,7 +35752,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35799,7 +35802,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35849,7 +35852,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35899,7 +35902,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35949,7 +35952,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35999,7 +36002,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36049,7 +36052,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36099,7 +36102,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36149,7 +36152,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36199,7 +36202,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36249,7 +36252,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36449,7 +36452,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36499,7 +36502,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36549,7 +36552,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36599,7 +36602,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36649,7 +36652,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36699,7 +36702,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36749,7 +36752,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36799,7 +36802,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36849,7 +36852,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36899,7 +36902,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36949,7 +36952,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36999,7 +37002,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37049,7 +37052,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37099,7 +37102,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37149,7 +37152,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37199,7 +37202,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37249,7 +37252,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37299,7 +37302,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37349,7 +37352,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37399,7 +37402,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37449,7 +37452,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37699,7 +37702,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37749,7 +37752,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37799,7 +37802,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37849,7 +37852,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37899,7 +37902,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37949,7 +37952,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37999,7 +38002,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38049,7 +38052,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38099,7 +38102,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38149,7 +38152,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38199,7 +38202,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38249,7 +38252,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38299,7 +38302,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38349,7 +38352,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38399,7 +38402,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38449,7 +38452,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38499,7 +38502,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38549,7 +38552,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38599,7 +38602,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38649,7 +38652,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38699,7 +38702,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38749,7 +38752,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38799,7 +38802,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38849,7 +38852,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38899,7 +38902,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38949,7 +38952,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38999,7 +39002,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39049,7 +39052,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39099,7 +39102,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39149,7 +39152,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39199,7 +39202,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39249,7 +39252,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39299,7 +39302,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39349,7 +39352,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39399,7 +39402,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39449,7 +39452,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39499,7 +39502,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39549,7 +39552,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39599,7 +39602,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39649,7 +39652,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39699,7 +39702,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39749,7 +39752,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39799,7 +39802,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39849,7 +39852,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39899,7 +39902,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39949,7 +39952,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -39999,7 +40002,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40049,7 +40052,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40249,7 +40252,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40299,7 +40302,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40349,7 +40352,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40449,7 +40452,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40499,7 +40502,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40549,7 +40552,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40599,7 +40602,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40649,7 +40652,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40699,7 +40702,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -40749,7 +40752,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40799,7 +40802,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40849,7 +40852,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40899,7 +40902,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40949,7 +40952,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40999,7 +41002,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41049,7 +41052,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41099,7 +41102,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41149,7 +41152,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41199,7 +41202,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41249,7 +41252,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41299,7 +41302,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41349,7 +41352,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41399,7 +41402,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41449,7 +41452,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41499,7 +41502,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41549,7 +41552,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41599,7 +41602,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41649,7 +41652,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -41949,7 +41952,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41999,7 +42002,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42049,7 +42052,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42099,7 +42102,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42249,7 +42252,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42299,7 +42302,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42449,7 +42452,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42499,7 +42502,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42549,7 +42552,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42599,7 +42602,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42649,7 +42652,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42849,7 +42852,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42899,7 +42902,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42949,7 +42952,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -42999,7 +43002,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43049,7 +43052,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43099,7 +43102,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43149,7 +43152,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43199,7 +43202,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43249,7 +43252,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43599,7 +43602,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43649,7 +43652,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43699,7 +43702,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43899,7 +43902,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43949,7 +43952,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43999,7 +44002,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44049,7 +44052,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44099,7 +44102,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44149,7 +44152,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44299,7 +44302,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44349,7 +44352,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44399,7 +44402,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44449,7 +44452,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44499,7 +44502,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44749,7 +44752,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44799,7 +44802,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44849,7 +44852,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44899,7 +44902,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45199,7 +45202,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45249,7 +45252,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45299,7 +45302,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45349,7 +45352,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45499,7 +45502,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45549,7 +45552,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45599,7 +45602,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45649,7 +45652,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46099,7 +46102,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46149,7 +46152,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46499,7 +46502,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46549,7 +46552,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46557,43 +46560,43 @@
         <v>0</v>
       </c>
       <c r="B896" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C896">
-        <v>1.135282743014287</v>
+        <v>1.339409495526739</v>
       </c>
       <c r="D896" t="s">
         <v>339</v>
       </c>
       <c r="E896">
-        <v>1.269330275206457</v>
+        <v>1.219290665046315</v>
       </c>
       <c r="F896">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G896">
-        <v>0.01074471725698571</v>
+        <v>0.01050059050447326</v>
       </c>
       <c r="H896">
-        <v>0.01071066972479354</v>
+        <v>0.01080070933495368</v>
       </c>
       <c r="I896">
-        <v>0.1340475321921701</v>
+        <v>0.1201188304804246</v>
       </c>
       <c r="J896">
         <v>1.400792203202832</v>
       </c>
       <c r="K896">
-        <v>3.43</v>
+        <v>3.27</v>
       </c>
       <c r="L896">
-        <v>5.94</v>
+        <v>5.92</v>
       </c>
       <c r="M896">
-        <v>3.37</v>
+        <v>3.42</v>
       </c>
       <c r="N896">
-        <v>5.99</v>
+        <v>6.01</v>
       </c>
       <c r="O896">
         <v>1</v>
@@ -46607,43 +46610,43 @@
         <v>1</v>
       </c>
       <c r="B897" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C897">
-        <v>1.283298587078343</v>
+        <v>1.135282743014287</v>
       </c>
       <c r="D897" t="s">
         <v>340</v>
       </c>
       <c r="E897">
-        <v>1.209290665046315</v>
+        <v>1.269330275206457</v>
       </c>
       <c r="F897">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G897">
-        <v>0.01083670141292166</v>
+        <v>0.01074471725698571</v>
       </c>
       <c r="H897">
-        <v>0.01079070933495369</v>
+        <v>0.01071066972479354</v>
       </c>
       <c r="I897">
-        <v>0.07400792203202755</v>
+        <v>0.1340475321921701</v>
       </c>
       <c r="J897">
         <v>1.400792203202832</v>
       </c>
       <c r="K897">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="L897">
-        <v>6.06</v>
+        <v>5.94</v>
       </c>
       <c r="M897">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="N897">
-        <v>6</v>
+        <v>5.99</v>
       </c>
       <c r="O897">
         <v>1</v>
@@ -46663,7 +46666,7 @@
         <v>1.05728794369645</v>
       </c>
       <c r="D898" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E898">
         <v>1.192699816401468</v>
@@ -46699,7 +46702,7 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -46713,7 +46716,7 @@
         <v>1.205758567931456</v>
       </c>
       <c r="D899" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E899">
         <v>1.131523255813954</v>
@@ -46749,7 +46752,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="476">
   <si>
     <t>trade_time</t>
   </si>
@@ -1034,9 +1034,6 @@
   </si>
   <si>
     <t>2021-08-12</t>
-  </si>
-  <si>
-    <t>2021-07-13</t>
   </si>
   <si>
     <t>2016-06-21</t>
@@ -1802,7 +1799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P900"/>
+  <dimension ref="A1:P899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1899,7 +1896,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1949,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1999,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2049,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2099,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2149,7 +2146,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2199,7 +2196,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2249,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2299,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2349,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2399,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2449,7 +2446,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2499,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2549,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2599,7 +2596,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2649,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2699,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2749,7 +2746,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2799,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2849,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2899,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2949,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2999,7 +2996,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3049,7 +3046,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3099,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3149,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3199,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3249,7 +3246,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3299,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3349,7 +3346,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3399,7 +3396,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3449,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3499,7 +3496,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3549,7 +3546,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3599,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3649,7 +3646,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3699,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3749,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3799,7 +3796,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3849,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3899,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3949,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3999,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4049,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4099,7 +4096,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4149,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4199,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4249,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4299,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4349,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4399,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4649,7 +4646,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4699,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4749,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4799,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4849,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4899,7 +4896,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5049,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5099,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5249,7 +5246,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5299,7 +5296,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5349,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5399,7 +5396,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5549,7 +5546,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5599,7 +5596,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5649,7 +5646,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5699,7 +5696,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5749,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5999,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6049,7 +6046,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6099,7 +6096,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6149,7 +6146,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6499,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6549,7 +6546,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6599,7 +6596,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6849,7 +6846,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6899,7 +6896,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6949,7 +6946,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6999,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7049,7 +7046,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7099,7 +7096,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7149,7 +7146,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7349,7 +7346,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7399,7 +7396,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7449,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7499,7 +7496,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7549,7 +7546,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7599,7 +7596,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7649,7 +7646,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7699,7 +7696,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7749,7 +7746,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7799,7 +7796,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7849,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7899,7 +7896,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7949,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7999,7 +7996,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8049,7 +8046,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8099,7 +8096,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8149,7 +8146,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8199,7 +8196,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8249,7 +8246,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8299,7 +8296,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8349,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8399,7 +8396,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8999,7 +8996,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9049,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9099,7 +9096,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9149,7 +9146,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9199,7 +9196,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9249,7 +9246,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9299,7 +9296,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9449,7 +9446,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10049,7 +10046,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10099,7 +10096,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10149,7 +10146,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10199,7 +10196,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10249,7 +10246,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10449,7 +10446,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10499,7 +10496,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10549,7 +10546,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10749,7 +10746,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10799,7 +10796,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10849,7 +10846,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10899,7 +10896,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10949,7 +10946,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10999,7 +10996,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11049,7 +11046,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11099,7 +11096,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11149,7 +11146,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11349,7 +11346,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11399,7 +11396,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11449,7 +11446,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11499,7 +11496,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11549,7 +11546,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11599,7 +11596,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11649,7 +11646,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11699,7 +11696,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11749,7 +11746,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11799,7 +11796,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11849,7 +11846,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11899,7 +11896,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12149,7 +12146,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12199,7 +12196,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12249,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12299,7 +12296,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12349,7 +12346,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12649,7 +12646,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12699,7 +12696,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12749,7 +12746,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12799,7 +12796,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12849,7 +12846,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12899,7 +12896,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12949,7 +12946,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12999,7 +12996,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -13049,7 +13046,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13099,7 +13096,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -13149,7 +13146,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13549,7 +13546,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13599,7 +13596,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13649,7 +13646,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13699,7 +13696,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -14199,7 +14196,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14249,7 +14246,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14299,7 +14296,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14349,7 +14346,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14399,7 +14396,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14449,7 +14446,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14499,7 +14496,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14549,7 +14546,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14599,7 +14596,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14649,7 +14646,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14699,7 +14696,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14749,7 +14746,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14799,7 +14796,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14849,7 +14846,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14899,7 +14896,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14949,7 +14946,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14999,7 +14996,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15049,7 +15046,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15099,7 +15096,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15149,7 +15146,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15199,7 +15196,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15749,7 +15746,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15799,7 +15796,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15849,7 +15846,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15899,7 +15896,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15949,7 +15946,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15999,7 +15996,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16049,7 +16046,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16099,7 +16096,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16149,7 +16146,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16199,7 +16196,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16249,7 +16246,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16299,7 +16296,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16349,7 +16346,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16399,7 +16396,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16449,7 +16446,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16499,7 +16496,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16549,7 +16546,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16599,7 +16596,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16649,7 +16646,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16849,7 +16846,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16899,7 +16896,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16949,7 +16946,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17349,7 +17346,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17399,7 +17396,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17449,7 +17446,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17499,7 +17496,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17749,7 +17746,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17799,7 +17796,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17849,7 +17846,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17899,7 +17896,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18899,7 +18896,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18949,7 +18946,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18999,7 +18996,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19049,7 +19046,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19099,7 +19096,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19149,7 +19146,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19199,7 +19196,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19249,7 +19246,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19299,7 +19296,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19349,7 +19346,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19399,7 +19396,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19449,7 +19446,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19499,7 +19496,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19549,7 +19546,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19599,7 +19596,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19649,7 +19646,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19699,7 +19696,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19999,7 +19996,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20049,7 +20046,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20099,7 +20096,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20149,7 +20146,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20199,7 +20196,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20249,7 +20246,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20299,7 +20296,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20349,7 +20346,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20399,7 +20396,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20449,7 +20446,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20499,7 +20496,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20549,7 +20546,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20599,7 +20596,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20649,7 +20646,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20949,7 +20946,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20999,7 +20996,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21049,7 +21046,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21099,7 +21096,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21149,7 +21146,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21199,7 +21196,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21249,7 +21246,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21299,7 +21296,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21549,7 +21546,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21599,7 +21596,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21649,7 +21646,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21699,7 +21696,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21749,7 +21746,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21799,7 +21796,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21849,7 +21846,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21899,7 +21896,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21949,7 +21946,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21999,7 +21996,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -24149,7 +24146,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24199,7 +24196,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24249,7 +24246,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24299,7 +24296,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24349,7 +24346,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24399,7 +24396,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24449,7 +24446,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24499,7 +24496,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -27599,7 +27596,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27649,7 +27646,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27699,7 +27696,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27749,7 +27746,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27799,7 +27796,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27849,7 +27846,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27899,7 +27896,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27949,7 +27946,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27999,7 +27996,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28049,7 +28046,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28099,7 +28096,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28149,7 +28146,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28199,7 +28196,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28249,7 +28246,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28299,7 +28296,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28749,7 +28746,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28799,7 +28796,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28849,7 +28846,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28899,7 +28896,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29099,7 +29096,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29149,7 +29146,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29199,7 +29196,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29249,7 +29246,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29299,7 +29296,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29349,7 +29346,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29399,7 +29396,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29449,7 +29446,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29499,7 +29496,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29549,7 +29546,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29599,7 +29596,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29649,7 +29646,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30149,7 +30146,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30199,7 +30196,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30249,7 +30246,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30299,7 +30296,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30349,7 +30346,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30399,7 +30396,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30449,7 +30446,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30499,7 +30496,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30549,7 +30546,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30599,7 +30596,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31199,7 +31196,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31249,7 +31246,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31299,7 +31296,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31349,7 +31346,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31399,7 +31396,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31449,7 +31446,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31499,7 +31496,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31949,7 +31946,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -31999,7 +31996,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32149,7 +32146,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32199,7 +32196,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32249,7 +32246,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32299,7 +32296,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32349,7 +32346,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32399,7 +32396,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -35349,7 +35346,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35399,7 +35396,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35449,7 +35446,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35499,7 +35496,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35549,7 +35546,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35599,7 +35596,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35649,7 +35646,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35699,7 +35696,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35749,7 +35746,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35799,7 +35796,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35849,7 +35846,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35899,7 +35896,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35949,7 +35946,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35999,7 +35996,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36049,7 +36046,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36099,7 +36096,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36149,7 +36146,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36199,7 +36196,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36249,7 +36246,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36449,7 +36446,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36499,7 +36496,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36549,7 +36546,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36599,7 +36596,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36649,7 +36646,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36699,7 +36696,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36749,7 +36746,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36799,7 +36796,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36849,7 +36846,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36899,7 +36896,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36949,7 +36946,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36999,7 +36996,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37049,7 +37046,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37099,7 +37096,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37149,7 +37146,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37199,7 +37196,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37249,7 +37246,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37299,7 +37296,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37349,7 +37346,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37399,7 +37396,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37449,7 +37446,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37699,7 +37696,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37749,7 +37746,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37799,7 +37796,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37849,7 +37846,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37899,7 +37896,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37949,7 +37946,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37999,7 +37996,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38049,7 +38046,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38099,7 +38096,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38149,7 +38146,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38199,7 +38196,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38249,7 +38246,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38299,7 +38296,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38349,7 +38346,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38399,7 +38396,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38449,7 +38446,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38499,7 +38496,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38549,7 +38546,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38599,7 +38596,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38649,7 +38646,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38699,7 +38696,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38749,7 +38746,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38799,7 +38796,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38849,7 +38846,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38899,7 +38896,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38949,7 +38946,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38999,7 +38996,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39049,7 +39046,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39099,7 +39096,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39149,7 +39146,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39199,7 +39196,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39249,7 +39246,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39299,7 +39296,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39349,7 +39346,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39399,7 +39396,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39449,7 +39446,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39499,7 +39496,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39549,7 +39546,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39599,7 +39596,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39649,7 +39646,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39699,7 +39696,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39749,7 +39746,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39799,7 +39796,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39849,7 +39846,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39899,7 +39896,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39949,7 +39946,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -39999,7 +39996,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40049,7 +40046,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40249,7 +40246,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40299,7 +40296,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40349,7 +40346,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40449,7 +40446,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40499,7 +40496,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40549,7 +40546,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40599,7 +40596,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40649,7 +40646,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40699,7 +40696,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -40749,7 +40746,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40799,7 +40796,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40849,7 +40846,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40899,7 +40896,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40949,7 +40946,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40999,7 +40996,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41049,7 +41046,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41099,7 +41096,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41149,7 +41146,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41199,7 +41196,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41249,7 +41246,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41299,7 +41296,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41349,7 +41346,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41399,7 +41396,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41449,7 +41446,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41499,7 +41496,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41549,7 +41546,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41599,7 +41596,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41649,7 +41646,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -41949,7 +41946,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -41999,7 +41996,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42049,7 +42046,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42099,7 +42096,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42249,7 +42246,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42299,7 +42296,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42449,7 +42446,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42499,7 +42496,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42549,7 +42546,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42599,7 +42596,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42649,7 +42646,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42849,7 +42846,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42899,7 +42896,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42949,7 +42946,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -42999,7 +42996,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43049,7 +43046,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43099,7 +43096,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43149,7 +43146,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43199,7 +43196,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43249,7 +43246,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43599,7 +43596,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43649,7 +43646,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43699,7 +43696,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43899,7 +43896,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43949,7 +43946,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43999,7 +43996,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44049,7 +44046,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44099,7 +44096,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44149,7 +44146,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44299,7 +44296,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44349,7 +44346,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44399,7 +44396,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44449,7 +44446,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44499,7 +44496,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44749,7 +44746,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -44799,7 +44796,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -44849,7 +44846,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -44899,7 +44896,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45199,7 +45196,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45249,7 +45246,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45299,7 +45296,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45349,7 +45346,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45499,7 +45496,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45549,7 +45546,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45599,7 +45596,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45649,7 +45646,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46099,7 +46096,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46149,7 +46146,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46499,7 +46496,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46549,7 +46546,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46657,49 +46654,49 @@
         <v>0</v>
       </c>
       <c r="B898" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C898">
-        <v>1.265052937576499</v>
+        <v>1.05728794369645</v>
       </c>
       <c r="D898" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E898">
-        <v>1.141523255813953</v>
+        <v>1.192699816401468</v>
       </c>
       <c r="F898">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G898">
-        <v>0.0105749470624235</v>
+        <v>0.01082271205630355</v>
       </c>
       <c r="H898">
-        <v>0.01087847674418605</v>
+        <v>0.01078730018359853</v>
       </c>
       <c r="I898">
-        <v>0.1235296817625455</v>
+        <v>0.135411872705018</v>
       </c>
       <c r="J898">
         <v>1.423531211750306</v>
       </c>
       <c r="K898">
-        <v>3.27</v>
+        <v>3.43</v>
       </c>
       <c r="L898">
-        <v>5.92</v>
+        <v>5.94</v>
       </c>
       <c r="M898">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="N898">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="O898">
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -46707,99 +46704,49 @@
         <v>1</v>
       </c>
       <c r="B899" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C899">
-        <v>1.05728794369645</v>
+        <v>1.231523255813953</v>
       </c>
       <c r="D899" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E899">
-        <v>1.192699816401468</v>
+        <v>1.284229192166463</v>
       </c>
       <c r="F899">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G899">
-        <v>0.01082271205630355</v>
+        <v>0.01096847674418605</v>
       </c>
       <c r="H899">
-        <v>0.01078730018359853</v>
+        <v>0.01093577080783354</v>
       </c>
       <c r="I899">
-        <v>0.135411872705018</v>
+        <v>-0.05270593635250975</v>
       </c>
       <c r="J899">
         <v>1.423531211750306</v>
       </c>
       <c r="K899">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="L899">
-        <v>5.94</v>
+        <v>6.1</v>
       </c>
       <c r="M899">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="N899">
-        <v>5.99</v>
+        <v>6.11</v>
       </c>
       <c r="O899">
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="900" spans="1:16">
-      <c r="A900" s="1">
-        <v>2</v>
-      </c>
-      <c r="B900" t="s">
-        <v>205</v>
-      </c>
-      <c r="C900">
-        <v>1.231523255813953</v>
-      </c>
-      <c r="D900" t="s">
-        <v>339</v>
-      </c>
-      <c r="E900">
-        <v>1.284229192166463</v>
-      </c>
-      <c r="F900">
-        <v>-1</v>
-      </c>
-      <c r="G900">
-        <v>0.01096847674418605</v>
-      </c>
-      <c r="H900">
-        <v>0.01093577080783354</v>
-      </c>
-      <c r="I900">
-        <v>-0.05270593635250975</v>
-      </c>
-      <c r="J900">
-        <v>1.423531211750306</v>
-      </c>
-      <c r="K900">
-        <v>3.42</v>
-      </c>
-      <c r="L900">
-        <v>6.1</v>
-      </c>
-      <c r="M900">
-        <v>3.39</v>
-      </c>
-      <c r="N900">
-        <v>6.11</v>
-      </c>
-      <c r="O900">
-        <v>1</v>
-      </c>
-      <c r="P900" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -634,7 +634,10 @@
     <t>2021-08-11</t>
   </si>
   <si>
-    <t>2021-08-18</t>
+    <t>2021-08-12</t>
+  </si>
+  <si>
+    <t>2021-08-20</t>
   </si>
   <si>
     <t>2016-07-25</t>
@@ -1039,10 +1042,7 @@
     <t>2021-08-13</t>
   </si>
   <si>
-    <t>2021-08-12</t>
-  </si>
-  <si>
-    <t>2021-08-19</t>
+    <t>2021-08-23</t>
   </si>
   <si>
     <t>2016-06-21</t>
@@ -1869,7 +1869,7 @@
         <v>3.243101562510338</v>
       </c>
       <c r="D2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E2">
         <v>2.811523862602873</v>
@@ -1919,7 +1919,7 @@
         <v>3.289636006444374</v>
       </c>
       <c r="D3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E3">
         <v>2.811523862602873</v>
@@ -1969,7 +1969,7 @@
         <v>2.642153147989039</v>
       </c>
       <c r="D4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E4">
         <v>2.397506560213501</v>
@@ -2019,7 +2019,7 @@
         <v>2.634437672345428</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E5">
         <v>2.397506560213501</v>
@@ -2069,7 +2069,7 @@
         <v>2.551523862602873</v>
       </c>
       <c r="D6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E6">
         <v>2.397506560213501</v>
@@ -2119,7 +2119,7 @@
         <v>3.51273100348791</v>
       </c>
       <c r="D7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E7">
         <v>3.28358785697468</v>
@@ -2169,7 +2169,7 @@
         <v>3.487126941772404</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E8">
         <v>3.28358785697468</v>
@@ -2219,7 +2219,7 @@
         <v>3.411368566458607</v>
       </c>
       <c r="D9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E9">
         <v>3.28358785697468</v>
@@ -2269,7 +2269,7 @@
         <v>4.114907651256331</v>
       </c>
       <c r="D10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E10">
         <v>3.865258921200569</v>
@@ -2319,7 +2319,7 @@
         <v>4.017281255370698</v>
       </c>
       <c r="D11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E11">
         <v>3.865258921200569</v>
@@ -2369,7 +2369,7 @@
         <v>3.250435096360468</v>
       </c>
       <c r="D12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E12">
         <v>3.016620926843599</v>
@@ -2419,7 +2419,7 @@
         <v>3.230220676572238</v>
       </c>
       <c r="D13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E13">
         <v>3.016620926843599</v>
@@ -2469,7 +2469,7 @@
         <v>3.152306444487531</v>
       </c>
       <c r="D14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E14">
         <v>3.016620926843599</v>
@@ -2519,7 +2519,7 @@
         <v>3.865906194216171</v>
       </c>
       <c r="D15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E15">
         <v>3.550292149834982</v>
@@ -2569,7 +2569,7 @@
         <v>3.767920488868719</v>
       </c>
       <c r="D16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E16">
         <v>3.550292149834982</v>
@@ -2619,7 +2619,7 @@
         <v>3.172782159400292</v>
       </c>
       <c r="D17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E17">
         <v>2.937585129362215</v>
@@ -2669,7 +2669,7 @@
         <v>3.154163347905764</v>
       </c>
       <c r="D18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E18">
         <v>2.937585129362215</v>
@@ -2719,7 +2719,7 @@
         <v>3.075610872503576</v>
       </c>
       <c r="D19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E19">
         <v>2.937585129362215</v>
@@ -2769,7 +2769,7 @@
         <v>3.792189091047127</v>
       </c>
       <c r="D20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E20">
         <v>3.524163347905765</v>
@@ -2819,7 +2819,7 @@
         <v>3.694097011813428</v>
       </c>
       <c r="D21" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E21">
         <v>3.524163347905765</v>
@@ -2869,7 +2869,7 @@
         <v>3.131337540570926</v>
       </c>
       <c r="D22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E22">
         <v>2.895402455676983</v>
@@ -2919,7 +2919,7 @@
         <v>3.113570330833166</v>
       </c>
       <c r="D23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E23">
         <v>2.895402455676983</v>
@@ -2969,7 +2969,7 @@
         <v>3.034677214728271</v>
       </c>
       <c r="D24" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E24">
         <v>2.895402455676983</v>
@@ -3019,7 +3019,7 @@
         <v>3.752845089884454</v>
       </c>
       <c r="D25" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E25">
         <v>3.419123772780718</v>
@@ -3069,7 +3069,7 @@
         <v>3.654696237200305</v>
       </c>
       <c r="D26" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E26">
         <v>3.419123772780718</v>
@@ -3119,7 +3119,7 @@
         <v>2.917985536997794</v>
       </c>
       <c r="D27" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E27">
         <v>2.678251032862137</v>
@@ -3169,7 +3169,7 @@
         <v>2.904602272538934</v>
       </c>
       <c r="D28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E28">
         <v>2.678251032862137</v>
@@ -3219,7 +3219,7 @@
         <v>2.823955578322479</v>
       </c>
       <c r="D29" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E29">
         <v>2.678251032862137</v>
@@ -3269,7 +3269,7 @@
         <v>3.550306817999275</v>
       </c>
       <c r="D30" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E30">
         <v>3.171749999808766</v>
@@ -3319,7 +3319,7 @@
         <v>3.451865702296533</v>
       </c>
       <c r="D31" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E31">
         <v>3.171749999808766</v>
@@ -3369,7 +3369,7 @@
         <v>2.695092590325597</v>
       </c>
       <c r="D32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E32">
         <v>2.451388759742354</v>
@@ -3419,7 +3419,7 @@
         <v>2.686289317921646</v>
       </c>
       <c r="D33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E33">
         <v>2.451388759742354</v>
@@ -3469,7 +3469,7 @@
         <v>2.603810626883227</v>
       </c>
       <c r="D34" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E34">
         <v>2.451388759742354</v>
@@ -3519,7 +3519,7 @@
         <v>3.33871118506252</v>
       </c>
       <c r="D35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E35">
         <v>3.111246699998485</v>
@@ -3569,7 +3569,7 @@
         <v>2.573608795274185</v>
       </c>
       <c r="D36" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E36">
         <v>2.327741554642081</v>
@@ -3619,7 +3619,7 @@
         <v>2.567301765234304</v>
       </c>
       <c r="D37" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E37">
         <v>2.327741554642081</v>
@@ -3669,7 +3669,7 @@
         <v>2.483824577250257</v>
       </c>
       <c r="D38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E38">
         <v>2.327741554642081</v>
@@ -3719,7 +3719,7 @@
         <v>3.22338478784248</v>
       </c>
       <c r="D39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E39">
         <v>3.00338478784248</v>
@@ -3769,7 +3769,7 @@
         <v>3.124471923178472</v>
       </c>
       <c r="D40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E40">
         <v>3.00338478784248</v>
@@ -3819,7 +3819,7 @@
         <v>2.525023995746672</v>
       </c>
       <c r="D41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E41">
         <v>2.278291546355859</v>
@@ -3869,7 +3869,7 @@
         <v>2.519715283505301</v>
       </c>
       <c r="D42" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E42">
         <v>2.278291546355859</v>
@@ -3919,7 +3919,7 @@
         <v>2.43583876840185</v>
       </c>
       <c r="D43" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E43">
         <v>2.278291546355859</v>
@@ -3969,7 +3969,7 @@
         <v>3.177262505551293</v>
       </c>
       <c r="D44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E44">
         <v>2.878283086367383</v>
@@ -4019,7 +4019,7 @@
         <v>2.49367544506272</v>
       </c>
       <c r="D45" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E45">
         <v>2.246384733810411</v>
@@ -4069,7 +4069,7 @@
         <v>2.489010881123074</v>
       </c>
       <c r="D46" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E46">
         <v>2.246384733810411</v>
@@ -4119,7 +4119,7 @@
         <v>2.404876706698933</v>
       </c>
       <c r="D47" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E47">
         <v>2.246384733810411</v>
@@ -4169,7 +4169,7 @@
         <v>3.147502854011596</v>
       </c>
       <c r="D48" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E48">
         <v>2.81434631718343</v>
@@ -4219,7 +4219,7 @@
         <v>2.435576766372018</v>
       </c>
       <c r="D49" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E49">
         <v>2.187251421115628</v>
@@ -4269,7 +4269,7 @@
         <v>2.432106010898619</v>
       </c>
       <c r="D50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E50">
         <v>2.187251421115628</v>
@@ -4319,7 +4319,7 @@
         <v>2.347494313087979</v>
       </c>
       <c r="D51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E51">
         <v>2.187251421115628</v>
@@ -4369,7 +4369,7 @@
         <v>3.092348902870971</v>
       </c>
       <c r="D52" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E52">
         <v>2.737737205060329</v>
@@ -4419,7 +4419,7 @@
         <v>2.371772059045239</v>
       </c>
       <c r="D53" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E53">
         <v>2.122310465576181</v>
@@ -4455,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4469,7 +4469,7 @@
         <v>2.369612359201843</v>
       </c>
       <c r="D54" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E54">
         <v>2.122310465576181</v>
@@ -4505,7 +4505,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4519,7 +4519,7 @@
         <v>2.284476239139202</v>
       </c>
       <c r="D55" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E55">
         <v>2.122310465576181</v>
@@ -4555,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4569,7 +4569,7 @@
         <v>3.031778132764864</v>
       </c>
       <c r="D56" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E56">
         <v>2.649073952670901</v>
@@ -4605,7 +4605,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4619,7 +4619,7 @@
         <v>2.321868001707651</v>
       </c>
       <c r="D57" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E57">
         <v>2.07151770584765</v>
@@ -4669,7 +4669,7 @@
         <v>2.320733727699959</v>
       </c>
       <c r="D58" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E58">
         <v>2.07151770584765</v>
@@ -4719,7 +4719,7 @@
         <v>2.235187437303036</v>
       </c>
       <c r="D59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E59">
         <v>2.07151770584765</v>
@@ -4819,7 +4819,7 @@
         <v>2.151512527619126</v>
       </c>
       <c r="D61" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E61">
         <v>2.792784685035415</v>
@@ -4919,7 +4919,7 @@
         <v>2.060915719062437</v>
       </c>
       <c r="D63" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E63">
         <v>2.69992609762433</v>
@@ -5019,7 +5019,7 @@
         <v>1.929841637735545</v>
       </c>
       <c r="D65" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E65">
         <v>2.565579709135323</v>
@@ -5119,7 +5119,7 @@
         <v>1.724822206455505</v>
       </c>
       <c r="D67" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E67">
         <v>2.355441900930122</v>
@@ -5219,7 +5219,7 @@
         <v>1.674034425134113</v>
       </c>
       <c r="D69" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E69">
         <v>2.303386186094466</v>
@@ -5319,7 +5319,7 @@
         <v>1.623841162955755</v>
       </c>
       <c r="D71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E71">
         <v>2.251939832766024</v>
@@ -5469,7 +5469,7 @@
         <v>2.333284107344603</v>
       </c>
       <c r="D74" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E74">
         <v>1.896773826741966</v>
@@ -5505,7 +5505,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5519,7 +5519,7 @@
         <v>2.326740023309851</v>
       </c>
       <c r="D75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E75">
         <v>1.889918119657939</v>
@@ -5569,7 +5569,7 @@
         <v>1.672605536248085</v>
       </c>
       <c r="D76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E76">
         <v>2.015292952838233</v>
@@ -5619,7 +5619,7 @@
         <v>2.422236961918112</v>
       </c>
       <c r="D77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E77">
         <v>2.050376064330505</v>
@@ -5669,7 +5669,7 @@
         <v>2.322168039785237</v>
       </c>
       <c r="D78" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E78">
         <v>2.050376064330505</v>
@@ -5719,7 +5719,7 @@
         <v>2.400031453666133</v>
       </c>
       <c r="D79" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E79">
         <v>2.26996253153326</v>
@@ -5769,7 +5769,7 @@
         <v>2.452252719470961</v>
       </c>
       <c r="D80" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E80">
         <v>2.081561266982816</v>
@@ -5805,7 +5805,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5819,7 +5819,7 @@
         <v>2.36235515687661</v>
       </c>
       <c r="D81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E81">
         <v>2.081561266982816</v>
@@ -5855,7 +5855,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5869,7 +5869,7 @@
         <v>2.352227110119547</v>
       </c>
       <c r="D82" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E82">
         <v>2.081561266982816</v>
@@ -5905,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5919,7 +5919,7 @@
         <v>2.431433220225751</v>
       </c>
       <c r="D83" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E83">
         <v>2.311714923091293</v>
@@ -5955,7 +5955,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5969,7 +5969,7 @@
         <v>2.454094657085679</v>
       </c>
       <c r="D84" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E84">
         <v>2.083474968400705</v>
@@ -6019,7 +6019,7 @@
         <v>2.364186462816786</v>
       </c>
       <c r="D85" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E85">
         <v>2.083474968400705</v>
@@ -6069,7 +6069,7 @@
         <v>2.354071705652902</v>
       </c>
       <c r="D86" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E86">
         <v>2.083474968400705</v>
@@ -6169,7 +6169,7 @@
         <v>2.339781007767745</v>
       </c>
       <c r="D88" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E88">
         <v>2.057971444982259</v>
@@ -6219,7 +6219,7 @@
         <v>2.329489142802344</v>
       </c>
       <c r="D89" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E89">
         <v>2.057971444982259</v>
@@ -6269,7 +6269,7 @@
         <v>2.407679580016858</v>
       </c>
       <c r="D90" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E90">
         <v>2.25849680191998</v>
@@ -6319,7 +6319,7 @@
         <v>2.36826330994766</v>
       </c>
       <c r="D91" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E91">
         <v>2.25849680191998</v>
@@ -6369,7 +6369,7 @@
         <v>3.548245528330676</v>
       </c>
       <c r="D92" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E92">
         <v>4.061344787936081</v>
@@ -6405,7 +6405,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6419,7 +6419,7 @@
         <v>4.409079280825154</v>
       </c>
       <c r="D93" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E93">
         <v>4.814235609417867</v>
@@ -6455,7 +6455,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6469,7 +6469,7 @@
         <v>5.769925742504288</v>
       </c>
       <c r="D94" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E94">
         <v>6.769399637973693</v>
@@ -6519,7 +6519,7 @@
         <v>7.229395624055007</v>
       </c>
       <c r="D95" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E95">
         <v>8.109917714666915</v>
@@ -6569,7 +6569,7 @@
         <v>5.828616664074527</v>
       </c>
       <c r="D96" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E96">
         <v>6.827923586794087</v>
@@ -6619,7 +6619,7 @@
         <v>6.627254795247419</v>
       </c>
       <c r="D97" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E97">
         <v>7.429368904817279</v>
@@ -6655,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6669,7 +6669,7 @@
         <v>6.647982466464144</v>
       </c>
       <c r="D98" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E98">
         <v>7.429368904817279</v>
@@ -6705,7 +6705,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6719,7 +6719,7 @@
         <v>6.738850879729914</v>
       </c>
       <c r="D99" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E99">
         <v>7.519850094731065</v>
@@ -6769,7 +6769,7 @@
         <v>6.79484616973682</v>
       </c>
       <c r="D100" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E100">
         <v>7.519850094731065</v>
@@ -6819,7 +6819,7 @@
         <v>7.382736713736916</v>
       </c>
       <c r="D101" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E101">
         <v>6.823146636869726</v>
@@ -6869,7 +6869,7 @@
         <v>4.077630001836678</v>
       </c>
       <c r="D102" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E102">
         <v>4.295890041790149</v>
@@ -6919,7 +6919,7 @@
         <v>4.085204721856269</v>
       </c>
       <c r="D103" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E103">
         <v>4.295890041790149</v>
@@ -6969,7 +6969,7 @@
         <v>0.2559344762264057</v>
       </c>
       <c r="D104" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E104">
         <v>0.4288461810550128</v>
@@ -7069,7 +7069,7 @@
         <v>0.3089776058983933</v>
       </c>
       <c r="D106" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E106">
         <v>0.07644783487002726</v>
@@ -7119,7 +7119,7 @@
         <v>0.2660659010697888</v>
       </c>
       <c r="D107" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E107">
         <v>-0.001905345815551129</v>
@@ -7219,7 +7219,7 @@
         <v>0.2889545424481916</v>
       </c>
       <c r="D109" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E109">
         <v>0.05610354580297638</v>
@@ -7269,7 +7269,7 @@
         <v>0.246096375222395</v>
       </c>
       <c r="D110" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E110">
         <v>-0.02246378529383364</v>
@@ -7369,7 +7369,7 @@
         <v>-1.630207146872417</v>
       </c>
       <c r="D112" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E112">
         <v>-1.215938554569574</v>
@@ -7419,7 +7419,7 @@
         <v>-1.036774334908403</v>
       </c>
       <c r="D113" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E113">
         <v>-1.383639958836433</v>
@@ -7469,7 +7469,7 @@
         <v>-1.076087772515599</v>
       </c>
       <c r="D114" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E114">
         <v>-1.383639958836433</v>
@@ -7519,7 +7519,7 @@
         <v>-1.110744491319196</v>
       </c>
       <c r="D115" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E115">
         <v>-1.383639958836433</v>
@@ -7569,7 +7569,7 @@
         <v>-1.598983240032837</v>
       </c>
       <c r="D116" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E116">
         <v>-1.755699646014843</v>
@@ -7619,7 +7619,7 @@
         <v>-2.012129891907831</v>
       </c>
       <c r="D117" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E117">
         <v>-1.639595934646165</v>
@@ -7669,7 +7669,7 @@
         <v>-2.069512610754847</v>
       </c>
       <c r="D118" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E118">
         <v>-1.639595934646165</v>
@@ -7719,7 +7719,7 @@
         <v>-1.470284212196077</v>
       </c>
       <c r="D119" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E119">
         <v>-1.828741009313617</v>
@@ -7769,7 +7769,7 @@
         <v>-1.508438532484321</v>
       </c>
       <c r="D120" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E120">
         <v>-1.828741009313617</v>
@@ -7819,7 +7819,7 @@
         <v>-1.542515692628445</v>
       </c>
       <c r="D121" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E121">
         <v>-1.828741009313617</v>
@@ -7869,7 +7869,7 @@
         <v>-2.044663849169496</v>
       </c>
       <c r="D122" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E122">
         <v>-2.204278048448881</v>
@@ -7919,7 +7919,7 @@
         <v>-2.572474789015972</v>
       </c>
       <c r="D123" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E123">
         <v>-2.124642573576088</v>
@@ -7969,7 +7969,7 @@
         <v>-1.96661100551972</v>
       </c>
       <c r="D124" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E124">
         <v>-2.338338572512225</v>
@@ -8019,7 +8019,7 @@
         <v>-2.003438248820469</v>
       </c>
       <c r="D125" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E125">
         <v>-2.338338572512225</v>
@@ -8069,7 +8069,7 @@
         <v>-2.036851870470842</v>
       </c>
       <c r="D126" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E126">
         <v>-2.338338572512225</v>
@@ -8119,7 +8119,7 @@
         <v>-3.407338082790915</v>
       </c>
       <c r="D127" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E127">
         <v>-2.849979157056712</v>
@@ -8169,7 +8169,7 @@
         <v>-3.324602190217494</v>
       </c>
       <c r="D128" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E128">
         <v>-2.849979157056712</v>
@@ -8219,7 +8219,7 @@
         <v>-2.794507371909873</v>
       </c>
       <c r="D129" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E129">
         <v>-3.10038849879556</v>
@@ -8269,7 +8269,7 @@
         <v>-2.708815881639428</v>
       </c>
       <c r="D130" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E130">
         <v>-3.10038849879556</v>
@@ -8319,7 +8319,7 @@
         <v>-2.743658619923814</v>
       </c>
       <c r="D131" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E131">
         <v>-3.10038849879556</v>
@@ -8369,7 +8369,7 @@
         <v>-2.776079989066007</v>
       </c>
       <c r="D132" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E132">
         <v>-3.10038849879556</v>
@@ -8419,7 +8419,7 @@
         <v>-4.198122324411599</v>
       </c>
       <c r="D133" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E133">
         <v>-3.609589249861864</v>
@@ -8469,7 +8469,7 @@
         <v>-4.112269016956628</v>
       </c>
       <c r="D134" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E134">
         <v>-3.609589249861864</v>
@@ -8519,7 +8519,7 @@
         <v>-3.54788263495192</v>
       </c>
       <c r="D135" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E135">
         <v>-3.898446708473204</v>
@@ -8569,7 +8569,7 @@
         <v>-3.48609132544005</v>
       </c>
       <c r="D136" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E136">
         <v>-3.898446708473204</v>
@@ -8619,7 +8619,7 @@
         <v>-3.518855787136733</v>
       </c>
       <c r="D137" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E137">
         <v>-3.898446708473204</v>
@@ -8669,7 +8669,7 @@
         <v>-3.550238017985075</v>
       </c>
       <c r="D138" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E138">
         <v>-3.898446708473204</v>
@@ -8719,7 +8719,7 @@
         <v>-4.300984707980247</v>
       </c>
       <c r="D139" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E139">
         <v>-3.791582878012612</v>
@@ -8769,7 +8769,7 @@
         <v>-3.728382471353138</v>
       </c>
       <c r="D140" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E140">
         <v>-4.089652052412703</v>
@@ -8819,7 +8819,7 @@
         <v>-3.672317363547791</v>
       </c>
       <c r="D141" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E141">
         <v>-4.089652052412703</v>
@@ -8869,7 +8869,7 @@
         <v>-3.704583894661299</v>
       </c>
       <c r="D142" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E142">
         <v>-4.089652052412703</v>
@@ -8919,7 +8919,7 @@
         <v>-3.735717160218051</v>
       </c>
       <c r="D143" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E143">
         <v>-4.089652052412703</v>
@@ -8969,7 +8969,7 @@
         <v>3.441688870966403</v>
       </c>
       <c r="D144" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E144">
         <v>3.651560048451251</v>
@@ -9069,7 +9069,7 @@
         <v>3.8022990056297</v>
       </c>
       <c r="D146" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E146">
         <v>3.836671882010169</v>
@@ -9119,7 +9119,7 @@
         <v>3.779869630048473</v>
       </c>
       <c r="D147" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E147">
         <v>3.98562223265952</v>
@@ -9419,7 +9419,7 @@
         <v>4.373222703065367</v>
       </c>
       <c r="D153" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E153">
         <v>4.431458212414677</v>
@@ -9469,7 +9469,7 @@
         <v>4.083529379419559</v>
       </c>
       <c r="D154" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E154">
         <v>4.233778249441884</v>
@@ -9505,7 +9505,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9519,7 +9519,7 @@
         <v>4.082413509772715</v>
       </c>
       <c r="D155" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E155">
         <v>4.233778249441884</v>
@@ -9555,7 +9555,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9569,7 +9569,7 @@
         <v>4.052868422995772</v>
       </c>
       <c r="D156" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E156">
         <v>4.233778249441884</v>
@@ -9605,7 +9605,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9619,7 +9619,7 @@
         <v>4.043984292642614</v>
       </c>
       <c r="D157" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E157">
         <v>4.233778249441884</v>
@@ -9655,7 +9655,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9669,7 +9669,7 @@
         <v>4.389563640876833</v>
       </c>
       <c r="D158" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E158">
         <v>4.179769684077565</v>
@@ -9705,7 +9705,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9719,7 +9719,7 @@
         <v>4.401546510148196</v>
       </c>
       <c r="D159" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E159">
         <v>4.411340466947465</v>
@@ -9755,7 +9755,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9769,7 +9769,7 @@
         <v>4.094971814749398</v>
       </c>
       <c r="D160" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E160">
         <v>4.264780591105191</v>
@@ -9819,7 +9819,7 @@
         <v>4.064216552539926</v>
       </c>
       <c r="D161" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E161">
         <v>4.264780591105191</v>
@@ -9869,7 +9869,7 @@
         <v>4.055253834032031</v>
       </c>
       <c r="D162" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E162">
         <v>4.264780591105191</v>
@@ -9919,7 +9919,7 @@
         <v>4.40044024149256</v>
       </c>
       <c r="D163" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E163">
         <v>4.1909134844194</v>
@@ -9969,7 +9969,7 @@
         <v>4.412706028120979</v>
       </c>
       <c r="D164" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E164">
         <v>4.40044024149256</v>
@@ -10019,7 +10019,7 @@
         <v>4.043749044780681</v>
       </c>
       <c r="D165" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E165">
         <v>4.215527927673731</v>
@@ -10069,7 +10069,7 @@
         <v>4.013415948257763</v>
       </c>
       <c r="D166" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E166">
         <v>4.215527927673731</v>
@@ -10119,7 +10119,7 @@
         <v>4.004805034488664</v>
       </c>
       <c r="D167" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E167">
         <v>4.215527927673731</v>
@@ -10169,7 +10169,7 @@
         <v>4.351750465643174</v>
       </c>
       <c r="D168" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E168">
         <v>4.141027572458107</v>
@@ -10219,7 +10219,7 @@
         <v>4.362749755211928</v>
       </c>
       <c r="D169" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E169">
         <v>4.328639196658452</v>
@@ -10269,7 +10269,7 @@
         <v>3.837290479346144</v>
       </c>
       <c r="D170" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E170">
         <v>4.04476916280097</v>
@@ -10319,7 +10319,7 @@
         <v>4.182943229511817</v>
       </c>
       <c r="D171" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E171">
         <v>3.968073337751268</v>
@@ -10419,7 +10419,7 @@
         <v>4.005765648245287</v>
       </c>
       <c r="D173" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E173">
         <v>3.78654312804322</v>
@@ -10469,7 +10469,7 @@
         <v>4.007765332737217</v>
       </c>
       <c r="D174" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E174">
         <v>3.953098876409263</v>
@@ -10519,7 +10519,7 @@
         <v>4.02454344355129</v>
       </c>
       <c r="D175" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E175">
         <v>3.953098876409263</v>
@@ -10569,7 +10569,7 @@
         <v>3.953616152889737</v>
       </c>
       <c r="D176" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E176">
         <v>3.677108955456802</v>
@@ -10619,7 +10619,7 @@
         <v>3.903905391470386</v>
       </c>
       <c r="D177" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E177">
         <v>3.812837536808245</v>
@@ -10669,7 +10669,7 @@
         <v>3.917887571538293</v>
       </c>
       <c r="D178" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E178">
         <v>3.812837536808245</v>
@@ -10719,7 +10719,7 @@
         <v>3.902034725100593</v>
       </c>
       <c r="D179" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E179">
         <v>3.623875720664222</v>
@@ -10769,7 +10769,7 @@
         <v>3.886926312984887</v>
       </c>
       <c r="D180" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E180">
         <v>3.769904630561744</v>
@@ -10819,7 +10819,7 @@
         <v>3.866005815203071</v>
       </c>
       <c r="D181" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E181">
         <v>3.769904630561744</v>
@@ -10869,7 +10869,7 @@
         <v>3.848331413478074</v>
       </c>
       <c r="D182" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E182">
         <v>3.568452652337633</v>
@@ -10919,7 +10919,7 @@
         <v>3.832050439973229</v>
       </c>
       <c r="D183" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E183">
         <v>3.65479424527226</v>
@@ -10969,7 +10969,7 @@
         <v>3.811989820543448</v>
       </c>
       <c r="D184" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E184">
         <v>3.65479424527226</v>
@@ -11019,7 +11019,7 @@
         <v>3.782176954997707</v>
       </c>
       <c r="D185" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E185">
         <v>3.500179710470706</v>
@@ -11069,7 +11069,7 @@
         <v>3.764451561002026</v>
       </c>
       <c r="D186" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E186">
         <v>3.586906482202889</v>
@@ -11119,7 +11119,7 @@
         <v>3.745450183265525</v>
       </c>
       <c r="D187" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E187">
         <v>3.586906482202889</v>
@@ -11169,7 +11169,7 @@
         <v>3.771581102618217</v>
       </c>
       <c r="D188" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E188">
         <v>3.489244544041217</v>
@@ -11219,7 +11219,7 @@
         <v>3.753624358133901</v>
       </c>
       <c r="D189" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E189">
         <v>3.576033009237036</v>
@@ -11269,7 +11269,7 @@
         <v>3.734792637422399</v>
       </c>
       <c r="D190" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E190">
         <v>3.576033009237036</v>
@@ -11319,7 +11319,7 @@
         <v>3.801691864414723</v>
       </c>
       <c r="D191" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E191">
         <v>3.520319551484772</v>
@@ -11369,7 +11369,7 @@
         <v>3.784392560144303</v>
       </c>
       <c r="D192" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E192">
         <v>3.606932699290218</v>
@@ -11419,7 +11419,7 @@
         <v>3.765078716609277</v>
       </c>
       <c r="D193" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E193">
         <v>3.606932699290218</v>
@@ -11469,7 +11469,7 @@
         <v>3.757917937598063</v>
       </c>
       <c r="D194" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E194">
         <v>3.593577848445167</v>
@@ -11519,7 +11519,7 @@
         <v>3.739662870733393</v>
       </c>
       <c r="D195" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E195">
         <v>3.562011857360458</v>
@@ -11569,7 +11569,7 @@
         <v>3.721049919767484</v>
       </c>
       <c r="D196" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E196">
         <v>3.562011857360458</v>
@@ -11619,7 +11619,7 @@
         <v>3.654060057628653</v>
       </c>
       <c r="D197" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E197">
         <v>3.486696449408235</v>
@@ -11669,7 +11669,7 @@
         <v>3.633537351463342</v>
       </c>
       <c r="D198" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E198">
         <v>3.455432810230278</v>
@@ -11719,7 +11719,7 @@
         <v>3.63416917105232</v>
       </c>
       <c r="D199" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E199">
         <v>3.680378253518446</v>
@@ -11769,7 +11769,7 @@
         <v>3.663638628212444</v>
       </c>
       <c r="D200" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E200">
         <v>3.496553872119646</v>
@@ -11819,7 +11819,7 @@
         <v>3.643325061142847</v>
       </c>
       <c r="D201" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E201">
         <v>3.515262347728926</v>
@@ -11869,7 +11869,7 @@
         <v>3.643970823338207</v>
       </c>
       <c r="D202" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E202">
         <v>3.346221676993885</v>
@@ -11969,7 +11969,7 @@
         <v>3.732518473414919</v>
       </c>
       <c r="D204" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E204">
         <v>3.567438952990316</v>
@@ -12019,7 +12019,7 @@
         <v>3.713708833096469</v>
       </c>
       <c r="D205" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E205">
         <v>3.585946905032777</v>
@@ -12069,7 +12069,7 @@
         <v>3.714454857075237</v>
       </c>
       <c r="D206" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E206">
         <v>3.415502569329999</v>
@@ -12169,7 +12169,7 @@
         <v>3.805132584430824</v>
       </c>
       <c r="D208" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E208">
         <v>3.642167011925171</v>
@@ -12219,7 +12219,7 @@
         <v>3.787908405051586</v>
       </c>
       <c r="D209" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E209">
         <v>3.660463569175736</v>
@@ -12269,7 +12269,7 @@
         <v>3.768539469929693</v>
       </c>
       <c r="D210" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E210">
         <v>3.660463569175736</v>
@@ -12319,7 +12319,7 @@
         <v>3.788760126426302</v>
       </c>
       <c r="D211" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E211">
         <v>3.488539469929694</v>
@@ -12405,7 +12405,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12419,7 +12419,7 @@
         <v>3.860377371854645</v>
       </c>
       <c r="D213" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E213">
         <v>3.699020090103688</v>
@@ -12455,7 +12455,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12469,7 +12469,7 @@
         <v>3.844359410541429</v>
       </c>
       <c r="D214" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E214">
         <v>3.717155818278784</v>
@@ -12505,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12519,7 +12519,7 @@
         <v>3.824105915504454</v>
       </c>
       <c r="D215" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E215">
         <v>3.717155818278784</v>
@@ -12555,7 +12555,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12569,7 +12569,7 @@
         <v>3.597834459154263</v>
       </c>
       <c r="D216" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E216">
         <v>3.522495138716523</v>
@@ -12605,7 +12605,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12619,7 +12619,7 @@
         <v>0.625943177311898</v>
       </c>
       <c r="D217" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E217">
         <v>0.1379206150209047</v>
@@ -12669,7 +12669,7 @@
         <v>0.7658867715844124</v>
       </c>
       <c r="D218" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E218">
         <v>0.1379206150209047</v>
@@ -12719,7 +12719,7 @@
         <v>0.5858867715844109</v>
       </c>
       <c r="D219" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E219">
         <v>0.1379206150209047</v>
@@ -12869,7 +12869,7 @@
         <v>0.663525902861652</v>
       </c>
       <c r="D222" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E222">
         <v>0.175066966398818</v>
@@ -12919,7 +12919,7 @@
         <v>0.5877553710930705</v>
       </c>
       <c r="D223" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E223">
         <v>0.175066966398818</v>
@@ -12969,7 +12969,7 @@
         <v>0.8023785617045647</v>
       </c>
       <c r="D224" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E224">
         <v>0.175066966398818</v>
@@ -13019,7 +13019,7 @@
         <v>0.6223785617045632</v>
       </c>
       <c r="D225" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E225">
         <v>0.175066966398818</v>
@@ -13169,7 +13169,7 @@
         <v>0.4716402043713206</v>
       </c>
       <c r="D228" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E228">
         <v>0.03601049292784353</v>
@@ -13219,7 +13219,7 @@
         <v>0.4737683280770817</v>
       </c>
       <c r="D229" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E229">
         <v>0.03601049292784353</v>
@@ -13269,7 +13269,7 @@
         <v>-0.4038754659271504</v>
       </c>
       <c r="D230" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E230">
         <v>-0.7248363937203361</v>
@@ -13319,7 +13319,7 @@
         <v>-0.3805801463088194</v>
       </c>
       <c r="D231" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E231">
         <v>-0.7248363937203361</v>
@@ -13369,7 +13369,7 @@
         <v>-0.4605801463088195</v>
       </c>
       <c r="D232" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E232">
         <v>-0.7248363937203361</v>
@@ -13419,7 +13419,7 @@
         <v>-1.654646533801483</v>
       </c>
       <c r="D233" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E233">
         <v>-1.429234276956707</v>
@@ -13455,7 +13455,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13469,7 +13469,7 @@
         <v>-1.787765390147543</v>
       </c>
       <c r="D234" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E234">
         <v>-1.429234276956707</v>
@@ -13505,7 +13505,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13519,7 +13519,7 @@
         <v>-1.544731674061682</v>
       </c>
       <c r="D235" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E235">
         <v>-1.809837684076546</v>
@@ -13569,7 +13569,7 @@
         <v>-1.469054674516903</v>
       </c>
       <c r="D236" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E236">
         <v>-1.809837684076546</v>
@@ -13619,7 +13619,7 @@
         <v>-1.543638678158672</v>
       </c>
       <c r="D237" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E237">
         <v>-1.809837684076546</v>
@@ -13669,7 +13669,7 @@
         <v>-2.073377674972123</v>
       </c>
       <c r="D238" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E238">
         <v>-1.780881696822737</v>
@@ -13719,7 +13719,7 @@
         <v>-1.652132987219185</v>
       </c>
       <c r="D239" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E239">
         <v>-1.934727966537217</v>
@@ -13769,7 +13769,7 @@
         <v>-1.649689974810006</v>
       </c>
       <c r="D240" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E240">
         <v>-1.934727966537217</v>
@@ -13819,7 +13819,7 @@
         <v>-2.180478984461589</v>
       </c>
       <c r="D241" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E241">
         <v>-1.915592959643229</v>
@@ -13869,7 +13869,7 @@
         <v>-1.737604814589712</v>
       </c>
       <c r="D242" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E242">
         <v>-2.018409182999145</v>
@@ -13919,7 +13919,7 @@
         <v>-2.26571206371097</v>
       </c>
       <c r="D243" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E243">
         <v>-1.998677305802289</v>
@@ -13969,7 +13969,7 @@
         <v>-1.819533600394442</v>
       </c>
       <c r="D244" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E244">
         <v>-2.22286478809788</v>
@@ -14019,7 +14019,7 @@
         <v>-2.347411998158703</v>
       </c>
       <c r="D245" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E245">
         <v>-2.078317578037055</v>
@@ -14069,7 +14069,7 @@
         <v>-2.415714139279594</v>
       </c>
       <c r="D246" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E246">
         <v>-2.144897816440613</v>
@@ -14119,7 +14119,7 @@
         <v>-2.436972664625649</v>
       </c>
       <c r="D247" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E247">
         <v>-2.200816202245704</v>
@@ -14169,7 +14169,7 @@
         <v>-2.516890282739048</v>
       </c>
       <c r="D248" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E248">
         <v>-2.243523300821257</v>
@@ -14219,7 +14219,7 @@
         <v>-2.522986556894401</v>
       </c>
       <c r="D249" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E249">
         <v>-2.3355828882186</v>
@@ -14269,7 +14269,7 @@
         <v>-3.131557245685132</v>
       </c>
       <c r="D250" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E250">
         <v>-3.347513294796991</v>
@@ -14319,7 +14319,7 @@
         <v>-3.047779776380045</v>
       </c>
       <c r="D251" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E251">
         <v>-3.377200086071589</v>
@@ -14369,7 +14369,7 @@
         <v>-3.069378665878359</v>
       </c>
       <c r="D252" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E252">
         <v>-3.377200086071589</v>
@@ -14419,7 +14419,7 @@
         <v>-3.163756593478626</v>
       </c>
       <c r="D253" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E253">
         <v>-3.379340932947848</v>
@@ -14469,7 +14469,7 @@
         <v>-3.07974680564689</v>
       </c>
       <c r="D254" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E254">
         <v>-3.410607490203656</v>
@@ -14519,7 +14519,7 @@
         <v>-3.102182041841141</v>
       </c>
       <c r="D255" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E255">
         <v>-3.410607490203656</v>
@@ -14569,7 +14569,7 @@
         <v>-3.524211405336349</v>
       </c>
       <c r="D256" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E256">
         <v>-3.577409447770004</v>
@@ -14619,7 +14619,7 @@
         <v>0.6985619802361995</v>
       </c>
       <c r="D257" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E257">
         <v>0.4443773057352942</v>
@@ -14669,7 +14669,7 @@
         <v>0.2116110986844824</v>
       </c>
       <c r="D258" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E258">
         <v>0.5643773057352952</v>
@@ -14719,7 +14719,7 @@
         <v>0.2545187614340296</v>
       </c>
       <c r="D259" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E259">
         <v>0.5643773057352952</v>
@@ -14769,7 +14769,7 @@
         <v>0.2430295661345721</v>
       </c>
       <c r="D260" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E260">
         <v>0.4588448916336674</v>
@@ -14819,7 +14819,7 @@
         <v>0.6450845842289681</v>
       </c>
       <c r="D261" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E261">
         <v>0.3235953889295118</v>
@@ -14919,7 +14919,7 @@
         <v>0.7941490617311544</v>
       </c>
       <c r="D263" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E263">
         <v>0.5413183118973173</v>
@@ -14969,7 +14969,7 @@
         <v>0.3097706370468654</v>
       </c>
       <c r="D264" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E264">
         <v>0.6613183118973183</v>
@@ -15019,7 +15019,7 @@
         <v>0.3533552621299467</v>
       </c>
       <c r="D265" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E265">
         <v>0.6613183118973183</v>
@@ -15069,7 +15069,7 @@
         <v>0.3410537120302486</v>
       </c>
       <c r="D266" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E266">
         <v>0.5582229621964121</v>
@@ -15119,7 +15119,7 @@
         <v>0.7515030630604631</v>
       </c>
       <c r="D267" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E267">
         <v>0.4292015129607663</v>
@@ -15219,7 +15219,7 @@
         <v>0.4166051310402512</v>
       </c>
       <c r="D269" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E269">
         <v>0.7668265845859583</v>
@@ -15269,7 +15269,7 @@
         <v>0.460926545737081</v>
       </c>
       <c r="D270" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E270">
         <v>0.7668265845859583</v>
@@ -15319,7 +15319,7 @@
         <v>0.4477408481008851</v>
       </c>
       <c r="D271" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E271">
         <v>0.6663836774945437</v>
@@ -15369,7 +15369,7 @@
         <v>0.8673263903415673</v>
       </c>
       <c r="D272" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E272">
         <v>0.5441406927053745</v>
@@ -15469,7 +15469,7 @@
         <v>0.4961745637454023</v>
       </c>
       <c r="D274" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E274">
         <v>0.8454082588161489</v>
@@ -15505,7 +15505,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15519,7 +15519,7 @@
         <v>0.5410447331505424</v>
       </c>
       <c r="D275" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E275">
         <v>0.8454082588161489</v>
@@ -15555,7 +15555,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15569,7 +15569,7 @@
         <v>0.5272005298643734</v>
       </c>
       <c r="D276" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E276">
         <v>0.7469408686746544</v>
@@ -15605,7 +15605,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15619,7 +15619,7 @@
         <v>0.953590630488117</v>
       </c>
       <c r="D277" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E277">
         <v>0.6297464272019511</v>
@@ -15655,7 +15655,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15705,7 +15705,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15719,7 +15719,7 @@
         <v>0.7398405907582468</v>
       </c>
       <c r="D279" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E279">
         <v>1.086049466183317</v>
@@ -15769,7 +15769,7 @@
         <v>0.7863912155220971</v>
       </c>
       <c r="D280" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E280">
         <v>1.086049466183317</v>
@@ -15819,7 +15819,7 @@
         <v>0.7705304658054768</v>
       </c>
       <c r="D281" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E281">
         <v>0.9936317153331773</v>
@@ -15869,7 +15869,7 @@
         <v>1.217758212877216</v>
       </c>
       <c r="D282" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E282">
         <v>0.891897463160598</v>
@@ -15969,7 +15969,7 @@
         <v>0.8404768364070323</v>
       </c>
       <c r="D284" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E284">
         <v>1.185436434299911</v>
@@ -16019,7 +16019,7 @@
         <v>0.8771704378117802</v>
       </c>
       <c r="D285" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E285">
         <v>1.185436434299911</v>
@@ -16069,7 +16069,7 @@
         <v>0.8710279028395735</v>
       </c>
       <c r="D286" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E286">
         <v>1.095517238514154</v>
@@ -16119,7 +16119,7 @@
         <v>1.326861784021968</v>
       </c>
       <c r="D287" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E287">
         <v>1.000168182617221</v>
@@ -16269,7 +16269,7 @@
         <v>0.9191467676646941</v>
       </c>
       <c r="D290" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E290">
         <v>1.263129773307477</v>
@@ -16319,7 +16319,7 @@
         <v>1.412150840530273</v>
       </c>
       <c r="D291" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E291">
         <v>1.084806177625463</v>
@@ -16419,7 +16419,7 @@
         <v>0.9146273854272415</v>
       </c>
       <c r="D293" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E293">
         <v>0.8634785090778685</v>
@@ -16469,7 +16469,7 @@
         <v>0.9881745201758667</v>
       </c>
       <c r="D294" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E294">
         <v>1.331300629580579</v>
@@ -16519,7 +16519,7 @@
         <v>1.486986445321696</v>
       </c>
       <c r="D295" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E295">
         <v>1.159070518258174</v>
@@ -16569,7 +16569,7 @@
         <v>1.384628046088775</v>
       </c>
       <c r="D296" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E296">
         <v>1.159070518258174</v>
@@ -16669,7 +16669,7 @@
         <v>1.568515655101596</v>
       </c>
       <c r="D298" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E298">
         <v>1.239977367658073</v>
@@ -16719,7 +16719,7 @@
         <v>1.463875267808676</v>
       </c>
       <c r="D299" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E299">
         <v>1.239977367658073</v>
@@ -16769,7 +16769,7 @@
         <v>0.9955922299886435</v>
       </c>
       <c r="D300" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E300">
         <v>0.9990028926204211</v>
@@ -16819,7 +16819,7 @@
         <v>1.677993157711763</v>
       </c>
       <c r="D301" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E301">
         <v>1.348619164141446</v>
@@ -16869,7 +16869,7 @@
         <v>1.570288514620596</v>
       </c>
       <c r="D302" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E302">
         <v>1.348619164141446</v>
@@ -16919,7 +16919,7 @@
         <v>1.106741144852402</v>
       </c>
       <c r="D303" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E303">
         <v>1.107784488901872</v>
@@ -16969,7 +16969,7 @@
         <v>1.742513494588377</v>
       </c>
       <c r="D304" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E304">
         <v>1.412646979362513</v>
@@ -17019,7 +17019,7 @@
         <v>1.633002938760204</v>
       </c>
       <c r="D305" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E305">
         <v>1.412646979362513</v>
@@ -17119,7 +17119,7 @@
         <v>1.805034484116738</v>
       </c>
       <c r="D307" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E307">
         <v>1.474690709428826</v>
@@ -17169,7 +17169,7 @@
         <v>1.69377397692772</v>
       </c>
       <c r="D308" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E308">
         <v>1.474690709428826</v>
@@ -17219,7 +17219,7 @@
         <v>1.722914540207936</v>
       </c>
       <c r="D309" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E309">
         <v>1.39274265286398</v>
@@ -17269,7 +17269,7 @@
         <v>1.235722033492567</v>
       </c>
       <c r="D310" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E310">
         <v>1.194518822084868</v>
@@ -17319,7 +17319,7 @@
         <v>1.870945052560478</v>
       </c>
       <c r="D311" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E311">
         <v>1.540098143762307</v>
@@ -17369,7 +17369,7 @@
         <v>1.757839720300515</v>
       </c>
       <c r="D312" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E312">
         <v>1.540098143762307</v>
@@ -17419,7 +17419,7 @@
         <v>1.785722448305086</v>
       </c>
       <c r="D313" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E313">
         <v>1.455298993906002</v>
@@ -17519,7 +17519,7 @@
         <v>1.899125582028087</v>
       </c>
       <c r="D315" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E315">
         <v>1.568063554684362</v>
@@ -17555,7 +17555,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17569,7 +17569,7 @@
         <v>1.785231481767759</v>
       </c>
       <c r="D316" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E316">
         <v>1.568063554684362</v>
@@ -17605,7 +17605,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17619,7 +17619,7 @@
         <v>1.812576413408444</v>
       </c>
       <c r="D317" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E317">
         <v>1.482045399736583</v>
@@ -17655,7 +17655,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17669,7 +17669,7 @@
         <v>1.331249636715539</v>
       </c>
       <c r="D318" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E318">
         <v>1.415762495439622</v>
@@ -17705,7 +17705,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17819,7 +17819,7 @@
         <v>1.822704074329991</v>
       </c>
       <c r="D321" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E321">
         <v>1.492132495928136</v>
@@ -18019,7 +18019,7 @@
         <v>1.844747253622594</v>
       </c>
       <c r="D325" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E325">
         <v>1.514087384782985</v>
@@ -18255,7 +18255,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18305,7 +18305,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18319,7 +18319,7 @@
         <v>1.905060827919813</v>
       </c>
       <c r="D331" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E331">
         <v>1.574159382681151</v>
@@ -18355,7 +18355,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18405,7 +18405,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18455,7 +18455,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18505,7 +18505,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18519,7 +18519,7 @@
         <v>2.171983384191653</v>
       </c>
       <c r="D335" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E335">
         <v>2.204898359259156</v>
@@ -18669,7 +18669,7 @@
         <v>1.952914540694782</v>
       </c>
       <c r="D338" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E338">
         <v>1.62182142504447</v>
@@ -18869,7 +18869,7 @@
         <v>2.179252235816775</v>
       </c>
       <c r="D342" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E342">
         <v>2.212248088231984</v>
@@ -19019,7 +19019,7 @@
         <v>1.960486682373803</v>
       </c>
       <c r="D345" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E345">
         <v>1.629363237718101</v>
@@ -19169,7 +19169,7 @@
         <v>2.154780197587645</v>
       </c>
       <c r="D348" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E348">
         <v>2.187503760286814</v>
@@ -19319,7 +19319,7 @@
         <v>1.934993557709523</v>
       </c>
       <c r="D351" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E351">
         <v>1.603972221697336</v>
@@ -19619,7 +19619,7 @@
         <v>1.929708178794847</v>
       </c>
       <c r="D357" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E357">
         <v>1.580374956308318</v>
@@ -19669,7 +19669,7 @@
         <v>1.188709675226703</v>
       </c>
       <c r="D358" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E358">
         <v>0.9637105065777352</v>
@@ -19755,7 +19755,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19805,7 +19805,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19855,7 +19855,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19905,7 +19905,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19919,7 +19919,7 @@
         <v>1.195364511122933</v>
       </c>
       <c r="D363" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E363">
         <v>0.9294680860372049</v>
@@ -19955,7 +19955,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20169,7 +20169,7 @@
         <v>1.196880596489463</v>
       </c>
       <c r="D368" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E368">
         <v>1.117568433078354</v>
@@ -20419,7 +20419,7 @@
         <v>1.214608625915525</v>
       </c>
       <c r="D373" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E373">
         <v>1.283141571142766</v>
@@ -20619,7 +20619,7 @@
         <v>1.186887430408948</v>
       </c>
       <c r="D377" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E377">
         <v>1.285894308899635</v>
@@ -20769,7 +20769,7 @@
         <v>1.153653122665109</v>
       </c>
       <c r="D380" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E380">
         <v>1.257399888895324</v>
@@ -20855,7 +20855,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20905,7 +20905,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21019,7 +21019,7 @@
         <v>0.8759988973248651</v>
       </c>
       <c r="D385" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E385">
         <v>0.9501238499442906</v>
@@ -21069,7 +21069,7 @@
         <v>0.9307488427654169</v>
       </c>
       <c r="D386" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E386">
         <v>0.9501238499442906</v>
@@ -21219,7 +21219,7 @@
         <v>0.7617642371331348</v>
       </c>
       <c r="D389" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E389">
         <v>1.020980669197449</v>
@@ -21269,7 +21269,7 @@
         <v>0.8108619467829499</v>
       </c>
       <c r="D390" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E390">
         <v>1.020980669197449</v>
@@ -21419,7 +21419,7 @@
         <v>0.6948350874985758</v>
       </c>
       <c r="D393" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E393">
         <v>0.7907320904119164</v>
@@ -21469,7 +21469,7 @@
         <v>0.740621198598765</v>
       </c>
       <c r="D394" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E394">
         <v>0.7907320904119164</v>
@@ -21869,7 +21869,7 @@
         <v>0.6646904187964902</v>
       </c>
       <c r="D402" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E402">
         <v>0.5071832846035527</v>
@@ -21919,7 +21919,7 @@
         <v>0.7089849968098569</v>
       </c>
       <c r="D403" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E403">
         <v>0.5071832846035527</v>
@@ -21969,7 +21969,7 @@
         <v>0.6682342833905643</v>
       </c>
       <c r="D404" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E404">
         <v>0.5071832846035527</v>
@@ -22169,7 +22169,7 @@
         <v>0.7432347119479275</v>
       </c>
       <c r="D408" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E408">
         <v>0.6707453955694014</v>
@@ -22219,7 +22219,7 @@
         <v>0.7820857966962995</v>
       </c>
       <c r="D409" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E409">
         <v>0.6707453955694014</v>
@@ -22269,7 +22269,7 @@
         <v>0.7511762387887622</v>
       </c>
       <c r="D410" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E410">
         <v>0.6707453955694014</v>
@@ -22355,7 +22355,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22405,7 +22405,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22455,7 +22455,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22469,7 +22469,7 @@
         <v>0.8216522553499699</v>
       </c>
       <c r="D414" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E414">
         <v>1.394472460139291</v>
@@ -22505,7 +22505,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22519,7 +22519,7 @@
         <v>0.8629538883296561</v>
       </c>
       <c r="D415" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E415">
         <v>1.394472460139291</v>
@@ -22555,7 +22555,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22569,7 +22569,7 @@
         <v>0.8339843477719082</v>
       </c>
       <c r="D416" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E416">
         <v>1.394472460139291</v>
@@ -22605,7 +22605,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22769,7 +22769,7 @@
         <v>0.9101672579802429</v>
       </c>
       <c r="D420" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E420">
         <v>1.488980666072655</v>
@@ -22819,7 +22819,7 @@
         <v>0.9542349847921239</v>
       </c>
       <c r="D421" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E421">
         <v>1.488980666072655</v>
@@ -22869,7 +22869,7 @@
         <v>0.9274552685181989</v>
       </c>
       <c r="D422" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E422">
         <v>1.488980666072655</v>
@@ -23019,7 +23019,7 @@
         <v>0.9657431826212832</v>
       </c>
       <c r="D425" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E425">
         <v>1.548319543944599</v>
@@ -23069,7 +23069,7 @@
         <v>1.011547657078197</v>
       </c>
       <c r="D426" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E426">
         <v>1.548319543944599</v>
@@ -23119,7 +23119,7 @@
         <v>0.9861428660232558</v>
       </c>
       <c r="D427" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E427">
         <v>1.548319543944599</v>
@@ -23219,7 +23219,7 @@
         <v>0.8844661762798571</v>
       </c>
       <c r="D429" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E429">
         <v>1.461539406965473</v>
@@ -23269,7 +23269,7 @@
         <v>0.9277307442886018</v>
       </c>
       <c r="D430" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E430">
         <v>1.461539406965473</v>
@@ -23319,7 +23319,7 @@
         <v>0.9003151939621921</v>
       </c>
       <c r="D431" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E431">
         <v>1.461539406965473</v>
@@ -23369,7 +23369,7 @@
         <v>0.7931634996038204</v>
       </c>
       <c r="D432" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E432">
         <v>1.36405477822283</v>
@@ -23405,7 +23405,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23419,7 +23419,7 @@
         <v>0.8335748589664389</v>
       </c>
       <c r="D433" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E433">
         <v>1.36405477822283</v>
@@ -23455,7 +23455,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23469,7 +23469,7 @@
         <v>0.8039005184618464</v>
       </c>
       <c r="D434" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E434">
         <v>1.36405477822283</v>
@@ -23505,7 +23505,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23519,7 +23519,7 @@
         <v>0.8355917364899295</v>
       </c>
       <c r="D435" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E435">
         <v>1.409355760314769</v>
@@ -23569,7 +23569,7 @@
         <v>0.8773289782552389</v>
       </c>
       <c r="D436" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E436">
         <v>1.409355760314769</v>
@@ -23619,7 +23619,7 @@
         <v>0.8487042946527765</v>
       </c>
       <c r="D437" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E437">
         <v>1.409355760314769</v>
@@ -23705,7 +23705,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23719,7 +23719,7 @@
         <v>0.8424985093805963</v>
       </c>
       <c r="D439" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E439">
         <v>1.416730179286574</v>
@@ -23755,7 +23755,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23769,7 +23769,7 @@
         <v>0.8844515877987398</v>
       </c>
       <c r="D440" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E440">
         <v>1.416730179286574</v>
@@ -23805,7 +23805,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23819,7 +23819,7 @@
         <v>0.8559977748797696</v>
       </c>
       <c r="D441" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E441">
         <v>1.416730179286574</v>
@@ -23855,7 +23855,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23869,7 +23869,7 @@
         <v>1.3975439619608</v>
       </c>
       <c r="D442" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E442">
         <v>1.517299827158533</v>
@@ -23905,7 +23905,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23919,7 +23919,7 @@
         <v>0.884482412735685</v>
       </c>
       <c r="D443" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E443">
         <v>1.461556742764664</v>
@@ -23969,7 +23969,7 @@
         <v>0.927747488133674</v>
       </c>
       <c r="D444" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E444">
         <v>1.461556742764664</v>
@@ -24019,7 +24019,7 @@
         <v>0.9003323394904168</v>
       </c>
       <c r="D445" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E445">
         <v>1.461556742764664</v>
@@ -24069,7 +24069,7 @@
         <v>1.442917190847158</v>
       </c>
       <c r="D446" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E446">
         <v>1.680876518723414</v>
@@ -24119,7 +24119,7 @@
         <v>0.9079753490611466</v>
       </c>
       <c r="D447" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E447">
         <v>1.486640346653829</v>
@@ -24169,7 +24169,7 @@
         <v>0.9519745787193061</v>
       </c>
       <c r="D448" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E448">
         <v>1.486640346653829</v>
@@ -24219,7 +24219,7 @@
         <v>0.925140635532018</v>
       </c>
       <c r="D449" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E449">
         <v>1.486640346653829</v>
@@ -24269,7 +24269,7 @@
         <v>1.468306692344727</v>
       </c>
       <c r="D450" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E450">
         <v>1.705807173808378</v>
@@ -24319,7 +24319,7 @@
         <v>0.9564160406795352</v>
       </c>
       <c r="D451" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E451">
         <v>1.538360876767213</v>
@@ -24369,7 +24369,7 @@
         <v>1.00192904195077</v>
       </c>
       <c r="D452" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E452">
         <v>1.538360876767213</v>
@@ -24419,7 +24419,7 @@
         <v>0.976293501290499</v>
       </c>
       <c r="D453" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E453">
         <v>1.538360876767213</v>
@@ -24469,7 +24469,7 @@
         <v>1.520657960630226</v>
       </c>
       <c r="D454" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E454">
         <v>1.757212334835704</v>
@@ -24519,7 +24519,7 @@
         <v>1.001796159074114</v>
       </c>
       <c r="D455" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E455">
         <v>1.586813607344758</v>
@@ -24569,7 +24569,7 @@
         <v>1.04872728904518</v>
       </c>
       <c r="D456" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E456">
         <v>1.586813607344758</v>
@@ -24619,7 +24619,7 @@
         <v>1.024214433605608</v>
       </c>
       <c r="D457" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E457">
         <v>1.586813607344758</v>
@@ -24669,7 +24669,7 @@
         <v>1.569701578166034</v>
       </c>
       <c r="D458" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E458">
         <v>1.805369621934118</v>
@@ -24719,7 +24719,7 @@
         <v>1.131375070810735</v>
       </c>
       <c r="D459" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E459">
         <v>1.725166091230212</v>
@@ -24769,7 +24769,7 @@
         <v>1.182355541773569</v>
       </c>
       <c r="D460" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E460">
         <v>1.725166091230212</v>
@@ -24819,7 +24819,7 @@
         <v>1.161048414619149</v>
       </c>
       <c r="D461" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E461">
         <v>1.725166091230212</v>
@@ -24869,7 +24869,7 @@
         <v>1.709741287464726</v>
       </c>
       <c r="D462" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E462">
         <v>1.942878493112953</v>
@@ -24919,7 +24919,7 @@
         <v>1.720982982903215</v>
       </c>
       <c r="D463" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E463">
         <v>1.513336012736406</v>
@@ -24969,7 +24969,7 @@
         <v>1.281563945976974</v>
       </c>
       <c r="D464" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E464">
         <v>1.885524004819166</v>
@@ -25005,7 +25005,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25019,7 +25019,7 @@
         <v>1.337237819288754</v>
       </c>
       <c r="D465" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E465">
         <v>1.885524004819166</v>
@@ -25055,7 +25055,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25069,7 +25069,7 @@
         <v>1.319646302327247</v>
       </c>
       <c r="D466" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E466">
         <v>1.885524004819166</v>
@@ -25105,7 +25105,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25119,7 +25119,7 @@
         <v>1.87205478536574</v>
       </c>
       <c r="D467" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E467">
         <v>2.102258614545877</v>
@@ -25155,7 +25155,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25205,7 +25205,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25219,7 +25219,7 @@
         <v>1.349426747936501</v>
       </c>
       <c r="D469" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E469">
         <v>1.957981683994701</v>
@@ -25269,7 +25269,7 @@
         <v>1.407221333809515</v>
       </c>
       <c r="D470" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E470">
         <v>1.957981683994701</v>
@@ -25319,7 +25319,7 @@
         <v>1.391308714292319</v>
       </c>
       <c r="D471" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E471">
         <v>1.957981683994701</v>
@@ -25369,7 +25369,7 @@
         <v>1.945396094775123</v>
       </c>
       <c r="D472" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E472">
         <v>2.174274478604488</v>
@@ -25419,7 +25419,7 @@
         <v>1.944997010575388</v>
       </c>
       <c r="D473" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E473">
         <v>1.762411421355811</v>
@@ -25469,7 +25469,7 @@
         <v>1.948704215965599</v>
       </c>
       <c r="D474" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E474">
         <v>1.762411421355811</v>
@@ -25519,7 +25519,7 @@
         <v>1.477021972447642</v>
       </c>
       <c r="D475" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E475">
         <v>2.094216168498784</v>
@@ -25555,7 +25555,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25569,7 +25569,7 @@
         <v>1.53880390908663</v>
       </c>
       <c r="D476" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E476">
         <v>2.094216168498784</v>
@@ -25605,7 +25605,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25619,7 +25619,7 @@
         <v>1.526047942259163</v>
       </c>
       <c r="D477" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E477">
         <v>2.094216168498784</v>
@@ -25655,7 +25655,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25669,7 +25669,7 @@
         <v>2.083291975431695</v>
       </c>
       <c r="D478" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E478">
         <v>2.309678265032328</v>
@@ -25705,7 +25705,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25719,7 +25719,7 @@
         <v>2.076081167006756</v>
       </c>
       <c r="D479" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E479">
         <v>1.963341812553087</v>
@@ -25755,7 +25755,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25769,7 +25769,7 @@
         <v>2.080619070473213</v>
       </c>
       <c r="D480" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E480">
         <v>1.963341812553087</v>
@@ -25805,7 +25805,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25819,7 +25819,7 @@
         <v>1.550026715673766</v>
       </c>
       <c r="D481" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E481">
         <v>2.172163941214178</v>
@@ -25855,7 +25855,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25869,7 +25869,7 @@
         <v>1.614090050538571</v>
       </c>
       <c r="D482" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E482">
         <v>2.172163941214178</v>
@@ -25905,7 +25905,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25919,7 +25919,7 @@
         <v>1.603140190639875</v>
       </c>
       <c r="D483" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E483">
         <v>2.172163941214178</v>
@@ -25955,7 +25955,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26005,7 +26005,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26055,7 +26055,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26105,7 +26105,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26119,7 +26119,7 @@
         <v>1.623258385611686</v>
       </c>
       <c r="D487" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E487">
         <v>2.25035400547081</v>
@@ -26169,7 +26169,7 @@
         <v>1.68961021016205</v>
       </c>
       <c r="D488" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E488">
         <v>2.25035400547081</v>
@@ -26219,7 +26219,7 @@
         <v>1.680472071264423</v>
       </c>
       <c r="D489" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E489">
         <v>2.25035400547081</v>
@@ -26469,7 +26469,7 @@
         <v>1.762765525787095</v>
       </c>
       <c r="D494" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E494">
         <v>2.399306941595595</v>
@@ -26505,7 +26505,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26519,7 +26519,7 @@
         <v>1.83347694846794</v>
       </c>
       <c r="D495" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E495">
         <v>2.399306941595595</v>
@@ -26555,7 +26555,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26569,7 +26569,7 @@
         <v>1.827790158090278</v>
       </c>
       <c r="D496" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E496">
         <v>2.399306941595595</v>
@@ -26605,7 +26605,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26619,7 +26619,7 @@
         <v>2.392103367712614</v>
       </c>
       <c r="D497" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E497">
         <v>2.445799092797729</v>
@@ -26655,7 +26655,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26669,7 +26669,7 @@
         <v>2.418595518914747</v>
       </c>
       <c r="D498" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E498">
         <v>2.445799092797729</v>
@@ -26705,7 +26705,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26719,7 +26719,7 @@
         <v>1.833848033537286</v>
       </c>
       <c r="D499" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E499">
         <v>2.475202327474705</v>
@@ -26769,7 +26769,7 @@
         <v>1.90285254583169</v>
       </c>
       <c r="D500" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E500">
         <v>2.475202327474705</v>
@@ -26819,7 +26819,7 @@
         <v>2.468924307078055</v>
       </c>
       <c r="D501" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E501">
         <v>2.423641774387</v>
@@ -26869,7 +26869,7 @@
         <v>2.492269576426664</v>
       </c>
       <c r="D502" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E502">
         <v>2.423641774387</v>
@@ -26919,7 +26919,7 @@
         <v>1.851549056007959</v>
       </c>
       <c r="D503" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E503">
         <v>2.494101856675164</v>
@@ -26955,7 +26955,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26969,7 +26969,7 @@
         <v>1.92154464117507</v>
       </c>
       <c r="D504" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E504">
         <v>2.494101856675164</v>
@@ -27005,7 +27005,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27019,7 +27019,7 @@
         <v>2.488054318341933</v>
       </c>
       <c r="D505" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E505">
         <v>2.382011194841591</v>
@@ -27055,7 +27055,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27069,7 +27069,7 @@
         <v>2.510615948674913</v>
       </c>
       <c r="D506" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E506">
         <v>2.382011194841591</v>
@@ -27105,7 +27105,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27119,7 +27119,7 @@
         <v>1.864147259392827</v>
       </c>
       <c r="D507" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E507">
         <v>2.507553063414217</v>
@@ -27169,7 +27169,7 @@
         <v>1.934848212718206</v>
       </c>
       <c r="D508" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E508">
         <v>2.507553063414217</v>
@@ -27219,7 +27219,7 @@
         <v>2.501669564187559</v>
       </c>
       <c r="D509" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E509">
         <v>2.253673461558189</v>
@@ -27269,7 +27269,7 @@
         <v>2.523673461558189</v>
       </c>
       <c r="D510" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E510">
         <v>2.253673461558189</v>
@@ -27319,7 +27319,7 @@
         <v>1.945845237918145</v>
       </c>
       <c r="D511" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E511">
         <v>2.594782675902186</v>
@@ -27369,7 +27369,7 @@
         <v>2.022277901603086</v>
       </c>
       <c r="D512" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E512">
         <v>2.594782675902186</v>
@@ -27419,7 +27419,7 @@
         <v>2.021120427020333</v>
       </c>
       <c r="D513" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E513">
         <v>2.594782675902186</v>
@@ -27469,7 +27469,7 @@
         <v>2.589962952437578</v>
       </c>
       <c r="D514" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E514">
         <v>2.297723818642469</v>
@@ -27519,7 +27519,7 @@
         <v>2.608350012217243</v>
       </c>
       <c r="D515" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E515">
         <v>2.297723818642469</v>
@@ -27569,7 +27569,7 @@
         <v>2.266279845688224</v>
       </c>
       <c r="D516" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E516">
         <v>2.483614796034592</v>
@@ -27619,7 +27619,7 @@
         <v>2.307068900485583</v>
       </c>
       <c r="D517" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E517">
         <v>2.574468278923365</v>
@@ -27669,7 +27669,7 @@
         <v>2.687922383374356</v>
       </c>
       <c r="D518" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E518">
         <v>2.779436064877657</v>
@@ -27719,7 +27719,7 @@
         <v>2.719073751524686</v>
       </c>
       <c r="D519" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E519">
         <v>2.779436064877657</v>
@@ -27769,7 +27769,7 @@
         <v>2.661312059733931</v>
       </c>
       <c r="D520" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E520">
         <v>2.452036686439876</v>
@@ -27819,7 +27819,7 @@
         <v>2.178065180993424</v>
       </c>
       <c r="D521" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E521">
         <v>2.397102519605832</v>
@@ -27869,7 +27869,7 @@
         <v>2.220092336347903</v>
       </c>
       <c r="D522" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E522">
         <v>2.493217929862364</v>
@@ -27919,7 +27919,7 @@
         <v>2.606207746604436</v>
       </c>
       <c r="D523" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E523">
         <v>2.696173802411337</v>
@@ -27969,7 +27969,7 @@
         <v>2.637204352185126</v>
       </c>
       <c r="D524" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E524">
         <v>2.696173802411337</v>
@@ -28019,7 +28019,7 @@
         <v>2.575109308444452</v>
       </c>
       <c r="D525" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E525">
         <v>2.363048208896876</v>
@@ -28069,7 +28069,7 @@
         <v>2.12088326409676</v>
       </c>
       <c r="D526" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E526">
         <v>2.286141940050999</v>
@@ -28119,7 +28119,7 @@
         <v>2.130930583414695</v>
       </c>
       <c r="D527" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E527">
         <v>2.389006294323388</v>
@@ -28169,7 +28169,7 @@
         <v>2.501400616005236</v>
       </c>
       <c r="D528" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E528">
         <v>2.589381688278063</v>
@@ -28219,7 +28219,7 @@
         <v>2.532198723232519</v>
       </c>
       <c r="D529" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E529">
         <v>2.589381688278063</v>
@@ -28269,7 +28269,7 @@
         <v>2.464545725596433</v>
       </c>
       <c r="D530" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E530">
         <v>2.248911655687521</v>
@@ -28319,7 +28319,7 @@
         <v>2.140747071531653</v>
       </c>
       <c r="D531" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E531">
         <v>1.952012635521896</v>
@@ -28355,7 +28355,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28369,7 +28369,7 @@
         <v>2.120862122803493</v>
       </c>
       <c r="D532" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E532">
         <v>1.952012635521896</v>
@@ -28405,7 +28405,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28455,7 +28455,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28469,7 +28469,7 @@
         <v>2.111322327890854</v>
       </c>
       <c r="D534" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E534">
         <v>1.971667481706374</v>
@@ -28505,7 +28505,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28519,7 +28519,7 @@
         <v>2.100113320360155</v>
       </c>
       <c r="D535" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E535">
         <v>1.93087160618927</v>
@@ -28619,7 +28619,7 @@
         <v>2.090416634691801</v>
       </c>
       <c r="D537" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E537">
         <v>1.950644120440534</v>
@@ -28669,7 +28669,7 @@
         <v>1.821174920520916</v>
       </c>
       <c r="D538" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E538">
         <v>1.870719949023447</v>
@@ -28719,7 +28719,7 @@
         <v>3.677672300021996</v>
       </c>
       <c r="D539" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E539">
         <v>3.541994244446075</v>
@@ -29319,7 +29319,7 @@
         <v>3.978801242489368</v>
       </c>
       <c r="D551" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E551">
         <v>4.001638601163368</v>
@@ -29369,7 +29369,7 @@
         <v>3.972496123834499</v>
       </c>
       <c r="D552" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E552">
         <v>4.001638601163368</v>
@@ -29419,7 +29419,7 @@
         <v>3.880251497171022</v>
       </c>
       <c r="D553" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E553">
         <v>4.001638601163368</v>
@@ -29719,7 +29719,7 @@
         <v>4.022199580117016</v>
       </c>
       <c r="D559" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E559">
         <v>4.091206258231424</v>
@@ -29769,7 +29769,7 @@
         <v>4.065709597288629</v>
       </c>
       <c r="D560" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E560">
         <v>4.091206258231424</v>
@@ -29819,7 +29819,7 @@
         <v>4.074716275403038</v>
       </c>
       <c r="D561" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E561">
         <v>4.091206258231424</v>
@@ -30219,7 +30219,7 @@
         <v>4.048036218160957</v>
       </c>
       <c r="D569" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E569">
         <v>4.122590316821391</v>
@@ -30269,7 +30269,7 @@
         <v>4.091698514142259</v>
       </c>
       <c r="D570" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E570">
         <v>4.122590316821391</v>
@@ -30319,7 +30319,7 @@
         <v>4.100806711463127</v>
       </c>
       <c r="D571" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E571">
         <v>4.122590316821391</v>
@@ -30655,7 +30655,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30705,7 +30705,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30755,7 +30755,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -30805,7 +30805,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30855,7 +30855,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30905,7 +30905,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31019,7 +31019,7 @@
         <v>3.994175842561082</v>
       </c>
       <c r="D585" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E585">
         <v>3.987624320511637</v>
@@ -31069,7 +31069,7 @@
         <v>4.031968972954489</v>
       </c>
       <c r="D586" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E586">
         <v>3.987624320511637</v>
@@ -31119,7 +31119,7 @@
         <v>4.029762103347897</v>
       </c>
       <c r="D587" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E587">
         <v>3.987624320511637</v>
@@ -31269,7 +31269,7 @@
         <v>3.974502457741278</v>
       </c>
       <c r="D590" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E590">
         <v>4.02356250952716</v>
@@ -31319,7 +31319,7 @@
         <v>4.00977951012228</v>
       </c>
       <c r="D591" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E591">
         <v>4.02356250952716</v>
@@ -31619,7 +31619,7 @@
         <v>3.831405330516851</v>
       </c>
       <c r="D597" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E597">
         <v>3.850567996970952</v>
@@ -31669,7 +31669,7 @@
         <v>3.880964530341485</v>
       </c>
       <c r="D598" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E598">
         <v>3.850567996970952</v>
@@ -31855,7 +31855,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -31905,7 +31905,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32619,7 +32619,7 @@
         <v>3.560372125976119</v>
       </c>
       <c r="D617" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E617">
         <v>3.5580450644216</v>
@@ -32819,7 +32819,7 @@
         <v>3.537985937044418</v>
       </c>
       <c r="D621" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E621">
         <v>3.543795194274905</v>
@@ -33319,7 +33319,7 @@
         <v>3.513407764343196</v>
       </c>
       <c r="D631" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E631">
         <v>3.432185734163389</v>
@@ -34469,7 +34469,7 @@
         <v>3.300340269867909</v>
       </c>
       <c r="D654" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E654">
         <v>3.32717886940423</v>
@@ -34519,7 +34519,7 @@
         <v>3.355120178326529</v>
       </c>
       <c r="D655" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E655">
         <v>3.32717886940423</v>
@@ -34569,7 +34569,7 @@
         <v>3.319715551327793</v>
       </c>
       <c r="D656" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E656">
         <v>3.32717886940423</v>
@@ -34769,7 +34769,7 @@
         <v>3.177869947980192</v>
       </c>
       <c r="D660" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E660">
         <v>3.00684994632877</v>
@@ -34819,7 +34819,7 @@
         <v>3.163573279753848</v>
       </c>
       <c r="D661" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E661">
         <v>3.00684994632877</v>
@@ -34869,7 +34869,7 @@
         <v>3.116679946053533</v>
       </c>
       <c r="D662" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E662">
         <v>3.00684994632877</v>
@@ -34969,7 +34969,7 @@
         <v>3.087400375663595</v>
       </c>
       <c r="D664" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E664">
         <v>3.241716253711907</v>
@@ -35019,7 +35019,7 @@
         <v>3.081905443957313</v>
       </c>
       <c r="D665" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E665">
         <v>2.925042268347651</v>
@@ -35069,7 +35069,7 @@
         <v>3.034452741518665</v>
       </c>
       <c r="D666" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E666">
         <v>2.925042268347651</v>
@@ -35169,7 +35169,7 @@
         <v>2.989312133043864</v>
       </c>
       <c r="D668" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E668">
         <v>2.907291204027289</v>
@@ -35219,7 +35219,7 @@
         <v>2.476500577738507</v>
       </c>
       <c r="D669" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E669">
         <v>2.193477149265671</v>
@@ -35269,7 +35269,7 @@
         <v>2.451590863540431</v>
       </c>
       <c r="D670" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E670">
         <v>2.193477149265671</v>
@@ -35319,7 +35319,7 @@
         <v>4.277467356934507</v>
       </c>
       <c r="D671" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E671">
         <v>4.250019035921865</v>
@@ -35369,7 +35369,7 @@
         <v>4.312388090974894</v>
       </c>
       <c r="D672" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E672">
         <v>4.250019035921865</v>
@@ -35419,7 +35419,7 @@
         <v>4.328265072623884</v>
       </c>
       <c r="D673" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E673">
         <v>4.250019035921865</v>
@@ -35469,7 +35469,7 @@
         <v>4.111896806998631</v>
       </c>
       <c r="D674" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E674">
         <v>4.346549444666274</v>
@@ -35519,7 +35519,7 @@
         <v>4.117244169330988</v>
       </c>
       <c r="D675" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E675">
         <v>4.346549444666274</v>
@@ -35569,7 +35569,7 @@
         <v>3.834254835686777</v>
       </c>
       <c r="D676" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E676">
         <v>4.016549444666274</v>
@@ -35619,7 +35619,7 @@
         <v>3.867454604316342</v>
       </c>
       <c r="D677" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E677">
         <v>3.899538778310484</v>
@@ -35669,7 +35669,7 @@
         <v>3.847454604316343</v>
       </c>
       <c r="D678" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E678">
         <v>3.899538778310484</v>
@@ -35719,7 +35719,7 @@
         <v>4.09540978178439</v>
       </c>
       <c r="D679" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E679">
         <v>4.330013928201403</v>
@@ -35769,7 +35769,7 @@
         <v>4.100805635367377</v>
       </c>
       <c r="D680" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E680">
         <v>4.330013928201403</v>
@@ -35819,7 +35819,7 @@
         <v>3.816701002958673</v>
       </c>
       <c r="D681" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E681">
         <v>4.000013928201403</v>
@@ -35869,7 +35869,7 @@
         <v>3.851743439112183</v>
       </c>
       <c r="D682" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E682">
         <v>3.891097828525042</v>
@@ -35919,7 +35919,7 @@
         <v>3.831743439112183</v>
       </c>
       <c r="D683" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E683">
         <v>3.891097828525042</v>
@@ -36019,7 +36019,7 @@
         <v>3.072514803912405</v>
       </c>
       <c r="D685" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E685">
         <v>3.774449448295682</v>
@@ -36069,7 +36069,7 @@
         <v>2.371533691899383</v>
       </c>
       <c r="D686" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E686">
         <v>2.931507151748597</v>
@@ -36119,7 +36119,7 @@
         <v>3.00124175024074</v>
       </c>
       <c r="D687" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E687">
         <v>3.689569720741245</v>
@@ -36169,7 +36169,7 @@
         <v>2.318595131284202</v>
       </c>
       <c r="D688" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E688">
         <v>2.868371291570359</v>
@@ -36219,7 +36219,7 @@
         <v>2.936132894431933</v>
       </c>
       <c r="D689" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E689">
         <v>3.612030992459847</v>
@@ -36269,7 +36269,7 @@
         <v>2.879002435988074</v>
       </c>
       <c r="D690" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E690">
         <v>3.543993810131251</v>
@@ -36319,7 +36319,7 @@
         <v>3.039849598930484</v>
       </c>
       <c r="D691" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E691">
         <v>3.542642379679147</v>
@@ -36369,7 +36369,7 @@
         <v>2.977447192513372</v>
       </c>
       <c r="D692" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E692">
         <v>2.899058823529414</v>
@@ -36419,7 +36419,7 @@
         <v>3.042101740294511</v>
       </c>
       <c r="D693" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E693">
         <v>3.545002623828647</v>
@@ -36519,7 +36519,7 @@
         <v>3.050868993661444</v>
       </c>
       <c r="D695" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E695">
         <v>3.554190705357193</v>
@@ -36669,7 +36669,7 @@
         <v>3.089396271713036</v>
       </c>
       <c r="D698" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E698">
         <v>3.594567292755261</v>
@@ -36719,7 +36719,7 @@
         <v>3.027786612060444</v>
       </c>
       <c r="D699" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E699">
         <v>3.145566633714636</v>
@@ -36769,7 +36769,7 @@
         <v>2.996371463540931</v>
       </c>
       <c r="D700" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E700">
         <v>3.145566633714636</v>
@@ -36819,7 +36819,7 @@
         <v>2.416022659343419</v>
       </c>
       <c r="D701" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E701">
         <v>2.867912855598218</v>
@@ -36869,7 +36869,7 @@
         <v>3.105522877654162</v>
       </c>
       <c r="D702" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E702">
         <v>3.611467975781562</v>
@@ -36919,7 +36919,7 @@
         <v>3.044171243696629</v>
       </c>
       <c r="D703" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E703">
         <v>3.05430849837813</v>
@@ -36969,7 +36969,7 @@
         <v>3.083632681399362</v>
       </c>
       <c r="D704" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E704">
         <v>3.05430849837813</v>
@@ -37019,7 +37019,7 @@
         <v>2.442409140573988</v>
       </c>
       <c r="D705" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E705">
         <v>2.897644102055196</v>
@@ -37069,7 +37069,7 @@
         <v>3.140364182095934</v>
       </c>
       <c r="D706" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E706">
         <v>3.647981662836538</v>
@@ -37119,7 +37119,7 @@
         <v>3.079570009009469</v>
       </c>
       <c r="D707" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E707">
         <v>2.916452842425499</v>
@@ -37169,7 +37169,7 @@
         <v>3.115129220614724</v>
       </c>
       <c r="D708" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E708">
         <v>2.916452842425499</v>
@@ -37219,7 +37219,7 @@
         <v>2.506084679240175</v>
       </c>
       <c r="D709" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E709">
         <v>2.946342336667283</v>
@@ -37269,7 +37269,7 @@
         <v>2.485628823792214</v>
       </c>
       <c r="D710" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E710">
         <v>2.946342336667283</v>
@@ -37319,7 +37319,7 @@
         <v>3.197432425781973</v>
       </c>
       <c r="D711" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E711">
         <v>3.707789182219507</v>
@@ -37369,7 +37369,7 @@
         <v>3.137551344594485</v>
       </c>
       <c r="D712" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E712">
         <v>2.906599994094392</v>
@@ -37419,7 +37419,7 @@
         <v>3.166718912906903</v>
       </c>
       <c r="D713" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E713">
         <v>2.906599994094392</v>
@@ -37469,7 +37469,7 @@
         <v>2.548771137606324</v>
       </c>
       <c r="D714" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E714">
         <v>3.017488605753604</v>
@@ -37519,7 +37519,7 @@
         <v>3.280806959867506</v>
       </c>
       <c r="D715" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E715">
         <v>3.795165693941145</v>
@@ -37569,7 +37569,7 @@
         <v>3.222259871225385</v>
       </c>
       <c r="D716" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E716">
         <v>2.962089491720224</v>
@@ -37619,7 +37619,7 @@
         <v>3.242089491720225</v>
       </c>
       <c r="D717" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E717">
         <v>2.962089491720224</v>
@@ -37669,7 +37669,7 @@
         <v>2.653191076884793</v>
       </c>
       <c r="D718" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E718">
         <v>3.092218373582619</v>
@@ -37719,7 +37719,7 @@
         <v>3.368380906542133</v>
       </c>
       <c r="D719" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E719">
         <v>3.886943190056155</v>
@@ -37769,7 +37769,7 @@
         <v>3.311235001046807</v>
       </c>
       <c r="D720" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E720">
         <v>2.886023832922186</v>
@@ -37819,7 +37819,7 @@
         <v>3.321256339514088</v>
       </c>
       <c r="D721" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E721">
         <v>2.886023832922186</v>
@@ -37869,7 +37869,7 @@
         <v>2.738191997996943</v>
       </c>
       <c r="D722" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E722">
         <v>3.189362283425077</v>
@@ -37919,7 +37919,7 @@
         <v>3.482221425888762</v>
       </c>
       <c r="D723" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E723">
         <v>4.006248054331422</v>
@@ -37969,7 +37969,7 @@
         <v>3.426896968702983</v>
       </c>
       <c r="D724" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E724">
         <v>2.985596340510704</v>
@@ -38019,7 +38019,7 @@
         <v>3.424168169003441</v>
       </c>
       <c r="D725" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E725">
         <v>2.985596340510704</v>
@@ -38069,7 +38069,7 @@
         <v>2.804657363903828</v>
       </c>
       <c r="D726" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E726">
         <v>3.265322701604374</v>
@@ -38119,7 +38119,7 @@
         <v>3.571237540942626</v>
       </c>
       <c r="D727" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E727">
         <v>4.099536942907871</v>
@@ -38169,7 +38169,7 @@
         <v>3.517337341597708</v>
       </c>
       <c r="D728" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E728">
         <v>3.063455769144483</v>
@@ -38219,7 +38219,7 @@
         <v>3.504638737012133</v>
       </c>
       <c r="D729" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E729">
         <v>3.063455769144483</v>
@@ -38269,7 +38269,7 @@
         <v>0.5561171847256032</v>
       </c>
       <c r="D730" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E730">
         <v>0.4330335026282048</v>
@@ -38319,7 +38319,7 @@
         <v>0.5838703236021816</v>
       </c>
       <c r="D731" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E731">
         <v>0.4330335026282048</v>
@@ -38469,7 +38469,7 @@
         <v>0.551213907254529</v>
       </c>
       <c r="D734" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E734">
         <v>0.4281448182448422</v>
@@ -38519,7 +38519,7 @@
         <v>0.5788357083417033</v>
       </c>
       <c r="D735" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E735">
         <v>0.4281448182448422</v>
@@ -38669,7 +38669,7 @@
         <v>0.5518269121620083</v>
       </c>
       <c r="D738" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E738">
         <v>0.4287559987329539</v>
@@ -38719,7 +38719,7 @@
         <v>0.5794651330234899</v>
       </c>
       <c r="D739" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E739">
         <v>0.4287559987329539</v>
@@ -38869,7 +38869,7 @@
         <v>0.555190648483161</v>
       </c>
       <c r="D742" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E742">
         <v>0.4321097239341025</v>
@@ -38919,7 +38919,7 @@
         <v>0.5829189694246733</v>
       </c>
       <c r="D743" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E743">
         <v>0.4321097239341025</v>
@@ -39069,7 +39069,7 @@
         <v>0.5690756953603548</v>
       </c>
       <c r="D746" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E746">
         <v>0.4459534462670192</v>
@@ -39119,7 +39119,7 @@
         <v>0.5971759372003635</v>
       </c>
       <c r="D747" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E747">
         <v>0.4459534462670192</v>
@@ -39269,7 +39269,7 @@
         <v>0.5772648724003702</v>
       </c>
       <c r="D750" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E750">
         <v>0.4541182507563208</v>
@@ -39319,7 +39319,7 @@
         <v>0.6055844671968078</v>
       </c>
       <c r="D751" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E751">
         <v>0.4541182507563208</v>
@@ -39469,7 +39469,7 @@
         <v>0.5864399744245681</v>
       </c>
       <c r="D754" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E754">
         <v>0.4632660459292559</v>
@@ -39519,7 +39519,7 @@
         <v>0.6150053308823686</v>
       </c>
       <c r="D755" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E755">
         <v>0.4632660459292559</v>
@@ -39669,7 +39669,7 @@
         <v>0.595932369726385</v>
       </c>
       <c r="D758" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E758">
         <v>0.4727301900545786</v>
@@ -39719,7 +39719,7 @@
         <v>0.6247519867726261</v>
       </c>
       <c r="D759" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E759">
         <v>0.4727301900545786</v>
@@ -39869,7 +39869,7 @@
         <v>0.608430208081792</v>
       </c>
       <c r="D762" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E762">
         <v>0.4851908324625001</v>
@@ -39919,7 +39919,7 @@
         <v>0.637584588655411</v>
       </c>
       <c r="D763" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E763">
         <v>0.4851908324625001</v>
@@ -40069,7 +40069,7 @@
         <v>0.6487552402128216</v>
       </c>
       <c r="D766" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E766">
         <v>0.496037697018247</v>
@@ -40219,7 +40219,7 @@
         <v>0.660243576041168</v>
       </c>
       <c r="D769" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E769">
         <v>0.5071930376051919</v>
@@ -40419,7 +40419,7 @@
         <v>0.6200014950680988</v>
       </c>
       <c r="D773" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E773">
         <v>0.5032178605940176</v>
@@ -40519,7 +40519,7 @@
         <v>0.6162587744088102</v>
       </c>
       <c r="D775" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E775">
         <v>0.5028669571717694</v>
@@ -40569,7 +40569,7 @@
         <v>0.6375579856807025</v>
       </c>
       <c r="D776" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E776">
         <v>0.5206716816708736</v>
@@ -40669,7 +40669,7 @@
         <v>0.6334559216463012</v>
       </c>
       <c r="D778" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E778">
         <v>0.5200127696413874</v>
@@ -40769,7 +40769,7 @@
         <v>0.6569511874884277</v>
       </c>
       <c r="D780" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E780">
         <v>0.5399514729417119</v>
@@ -41705,7 +41705,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -41755,7 +41755,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41805,7 +41805,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41855,7 +41855,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41905,7 +41905,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42169,7 +42169,7 @@
         <v>0.270836261272378</v>
       </c>
       <c r="D808" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E808">
         <v>0.09124596707246546</v>
@@ -42269,7 +42269,7 @@
         <v>0.2794126519714268</v>
       </c>
       <c r="D810" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E810">
         <v>0.06592505104991719</v>
@@ -42355,7 +42355,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42369,7 +42369,7 @@
         <v>0.1298112530385671</v>
       </c>
       <c r="D812" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E812">
         <v>0.07261882114189877</v>
@@ -42405,7 +42405,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42469,7 +42469,7 @@
         <v>0.1409299212154549</v>
       </c>
       <c r="D814" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E814">
         <v>0.08367689712163706</v>
@@ -42619,7 +42619,7 @@
         <v>0.1597535501777907</v>
       </c>
       <c r="D817" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E817">
         <v>0.1023979449997094</v>
@@ -42769,7 +42769,7 @@
         <v>0.1800760542101028</v>
       </c>
       <c r="D820" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E820">
         <v>0.122609699691246</v>
@@ -42919,7 +42919,7 @@
         <v>0.1921206757259357</v>
       </c>
       <c r="D823" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E823">
         <v>0.1345886829426881</v>
@@ -43069,7 +43069,7 @@
         <v>0.207445501992245</v>
       </c>
       <c r="D826" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E826">
         <v>0.149829995169398</v>
@@ -43219,7 +43219,7 @@
         <v>0.2264355115310135</v>
       </c>
       <c r="D829" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E829">
         <v>0.1687165169177645</v>
@@ -43369,7 +43369,7 @@
         <v>0.247602885402646</v>
       </c>
       <c r="D832" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E832">
         <v>0.189768537253312</v>
@@ -43519,7 +43519,7 @@
         <v>0.2658141232074192</v>
       </c>
       <c r="D835" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E835">
         <v>0.2078805312553342</v>
@@ -43669,7 +43669,7 @@
         <v>0.2841622296762241</v>
       </c>
       <c r="D838" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E838">
         <v>0.2261286480431108</v>
@@ -43819,7 +43819,7 @@
         <v>0.3008602884138671</v>
       </c>
       <c r="D841" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E841">
         <v>0.2427357091854532</v>
@@ -43969,7 +43969,7 @@
         <v>0.3157253050058326</v>
       </c>
       <c r="D844" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E844">
         <v>0.2575197175126123</v>
@@ -44119,7 +44119,7 @@
         <v>0.3256535453070422</v>
       </c>
       <c r="D847" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E847">
         <v>0.2673938529620443</v>
@@ -44219,7 +44219,7 @@
         <v>0.3356173056739165</v>
       </c>
       <c r="D849" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E849">
         <v>0.2773033149073001</v>
@@ -44319,7 +44319,7 @@
         <v>0.3554042853652533</v>
       </c>
       <c r="D851" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E851">
         <v>0.2969824636466409</v>
@@ -44469,7 +44469,7 @@
         <v>0.36895891007521</v>
       </c>
       <c r="D854" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E854">
         <v>0.3104632211919656</v>
@@ -44569,7 +44569,7 @@
         <v>0.3786093045418983</v>
       </c>
       <c r="D856" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E856">
         <v>0.3200610249531142</v>
@@ -44655,7 +44655,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44669,7 +44669,7 @@
         <v>0.37775626876864</v>
       </c>
       <c r="D858" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E858">
         <v>0.3192126378761673</v>
@@ -44705,7 +44705,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -44769,7 +44769,7 @@
         <v>0.3789042474925317</v>
       </c>
       <c r="D860" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E860">
         <v>0.3203543605852142</v>
@@ -44869,7 +44869,7 @@
         <v>0.3814658379638036</v>
       </c>
       <c r="D862" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E862">
         <v>0.3229019914353897</v>
@@ -44969,7 +44969,7 @@
         <v>0.3806182450080593</v>
       </c>
       <c r="D864" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E864">
         <v>0.3220590175148264</v>
@@ -45069,7 +45069,7 @@
         <v>0.3721749196184598</v>
       </c>
       <c r="D866" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E866">
         <v>0.3136617047976493</v>
@@ -45169,7 +45169,7 @@
         <v>0.3561949085063132</v>
       </c>
       <c r="D868" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E868">
         <v>0.2977687782147251</v>
@@ -45269,7 +45269,7 @@
         <v>0.3203941118255811</v>
       </c>
       <c r="D870" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E870">
         <v>0.2621630812434246</v>
@@ -45369,7 +45369,7 @@
         <v>0.3042852051995242</v>
       </c>
       <c r="D872" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E872">
         <v>0.246141961574458</v>
@@ -45469,7 +45469,7 @@
         <v>0.2827161083084606</v>
       </c>
       <c r="D874" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E874">
         <v>0.2246904074457436</v>
@@ -45569,7 +45569,7 @@
         <v>0.2629830094488543</v>
       </c>
       <c r="D876" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E876">
         <v>0.2050648459096225</v>
@@ -45669,7 +45669,7 @@
         <v>0.2531682602441148</v>
       </c>
       <c r="D878" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E878">
         <v>0.195303583076571</v>
@@ -45769,7 +45769,7 @@
         <v>0.264044594240807</v>
       </c>
       <c r="D880" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E880">
         <v>0.2061206454983502</v>
@@ -45919,7 +45919,7 @@
         <v>0.2246564252284724</v>
       </c>
       <c r="D883" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E883">
         <v>0.1669471259084254</v>
@@ -46069,7 +46069,7 @@
         <v>0.1598063964288423</v>
       </c>
       <c r="D886" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E886">
         <v>0.1371622895973914</v>
@@ -46169,7 +46169,7 @@
         <v>0.011804494898219</v>
       </c>
       <c r="D888" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E888">
         <v>-0.0116461618053334</v>
@@ -46355,7 +46355,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -46405,7 +46405,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46419,7 +46419,7 @@
         <v>0.1619145765582886</v>
       </c>
       <c r="D893" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E893">
         <v>0.3617858655291597</v>
@@ -46455,7 +46455,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46519,7 +46519,7 @@
         <v>0.2077085108365813</v>
       </c>
       <c r="D895" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E895">
         <v>0.4045012159904244</v>
@@ -46569,7 +46569,7 @@
         <v>1.135282743014287</v>
       </c>
       <c r="D896" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E896">
         <v>1.269330275206457</v>
@@ -46619,7 +46619,7 @@
         <v>1.309290665046315</v>
       </c>
       <c r="D897" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E897">
         <v>1.223338197238484</v>
@@ -46669,7 +46669,7 @@
         <v>1.05728794369645</v>
       </c>
       <c r="D898" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E898">
         <v>1.192699816401468</v>
@@ -46713,43 +46713,43 @@
         <v>1</v>
       </c>
       <c r="B899" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C899">
-        <v>1.231523255813953</v>
+        <v>1.284229192166463</v>
       </c>
       <c r="D899" t="s">
         <v>341</v>
       </c>
       <c r="E899">
-        <v>1.284229192166463</v>
+        <v>1.146935128518972</v>
       </c>
       <c r="F899">
         <v>-1</v>
       </c>
       <c r="G899">
-        <v>0.01096847674418605</v>
+        <v>0.01093577080783354</v>
       </c>
       <c r="H899">
-        <v>0.01093577080783354</v>
+        <v>0.01071306487148103</v>
       </c>
       <c r="I899">
-        <v>-0.05270593635250975</v>
+        <v>0.1372940636474915</v>
       </c>
       <c r="J899">
         <v>1.423531211750306</v>
       </c>
       <c r="K899">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="L899">
-        <v>6.1</v>
+        <v>6.11</v>
       </c>
       <c r="M899">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="N899">
-        <v>6.11</v>
+        <v>5.93</v>
       </c>
       <c r="O899">
         <v>1</v>
@@ -46763,43 +46763,43 @@
         <v>2</v>
       </c>
       <c r="B900" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C900">
-        <v>1.281170440636474</v>
+        <v>1.279288249694003</v>
       </c>
       <c r="D900" t="s">
         <v>342</v>
       </c>
       <c r="E900">
-        <v>1.23234700122399</v>
+        <v>1.309288249694003</v>
       </c>
       <c r="F900">
         <v>-1</v>
       </c>
       <c r="G900">
-        <v>0.01081882955936353</v>
+        <v>0.010560711750306</v>
       </c>
       <c r="H900">
-        <v>0.01062765299877601</v>
+        <v>0.010590711750306</v>
       </c>
       <c r="I900">
-        <v>0.04882343941248468</v>
+        <v>-0.03000000000000025</v>
       </c>
       <c r="J900">
         <v>1.423531211750306</v>
       </c>
       <c r="K900">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="L900">
-        <v>6.05</v>
+        <v>5.92</v>
       </c>
       <c r="M900">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="N900">
-        <v>5.93</v>
+        <v>5.95</v>
       </c>
       <c r="O900">
         <v>1</v>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -634,12 +634,12 @@
     <t>2021-08-20</t>
   </si>
   <si>
+    <t>2021-10-08</t>
+  </si>
+  <si>
     <t>2021-09-28</t>
   </si>
   <si>
-    <t>2021-10-08</t>
-  </si>
-  <si>
     <t>2016-08-08</t>
   </si>
   <si>
@@ -1042,10 +1042,7 @@
     <t>2021-08-23</t>
   </si>
   <si>
-    <t>2021-09-30</t>
-  </si>
-  <si>
-    <t>2021-10-11</t>
+    <t>2021-10-12</t>
   </si>
   <si>
     <t>2016-07-11</t>
@@ -1454,6 +1451,9 @@
   </si>
   <si>
     <t>2021-06-28</t>
+  </si>
+  <si>
+    <t>2021-09-10</t>
   </si>
   <si>
     <t>2021-09-24</t>
@@ -1914,7 +1914,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1964,7 +1964,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2014,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2064,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2114,7 +2114,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2164,7 +2164,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2214,7 +2214,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2264,7 +2264,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2314,7 +2314,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2364,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2414,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2464,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2514,7 +2514,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2564,7 +2564,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2614,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2664,7 +2664,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2714,7 +2714,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2764,7 +2764,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2814,7 +2814,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2864,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2914,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2964,7 +2964,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3014,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3114,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3164,7 +3164,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3214,7 +3214,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3264,7 +3264,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3314,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3364,7 +3364,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3414,7 +3414,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3464,7 +3464,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3514,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3564,7 +3564,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3614,7 +3614,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3664,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3714,7 +3714,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3764,7 +3764,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3814,7 +3814,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3864,7 +3864,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3914,7 +3914,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3964,7 +3964,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4014,7 +4014,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4064,7 +4064,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4114,7 +4114,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4164,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4214,7 +4214,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4264,7 +4264,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4314,7 +4314,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4364,7 +4364,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4414,7 +4414,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4464,7 +4464,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4514,7 +4514,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4564,7 +4564,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4614,7 +4614,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4664,7 +4664,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4814,7 +4814,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4864,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5014,7 +5014,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5064,7 +5064,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5114,7 +5114,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5164,7 +5164,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5314,7 +5314,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5364,7 +5364,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5414,7 +5414,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5464,7 +5464,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5514,7 +5514,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5764,7 +5764,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5814,7 +5814,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5864,7 +5864,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5914,7 +5914,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6264,7 +6264,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6314,7 +6314,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6364,7 +6364,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6614,7 +6614,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6664,7 +6664,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6714,7 +6714,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6764,7 +6764,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6814,7 +6814,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6864,7 +6864,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6914,7 +6914,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7114,7 +7114,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7164,7 +7164,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7214,7 +7214,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7264,7 +7264,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7314,7 +7314,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7364,7 +7364,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7414,7 +7414,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7464,7 +7464,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7514,7 +7514,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7564,7 +7564,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7614,7 +7614,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7664,7 +7664,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7714,7 +7714,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7764,7 +7764,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7814,7 +7814,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7864,7 +7864,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7914,7 +7914,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7964,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8014,7 +8014,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8064,7 +8064,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8114,7 +8114,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8164,7 +8164,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8764,7 +8764,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8814,7 +8814,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8864,7 +8864,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8914,7 +8914,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8964,7 +8964,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9014,7 +9014,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9064,7 +9064,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9214,7 +9214,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9814,7 +9814,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9864,7 +9864,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9914,7 +9914,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9964,7 +9964,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10014,7 +10014,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10214,7 +10214,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10264,7 +10264,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10314,7 +10314,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10514,7 +10514,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10564,7 +10564,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10614,7 +10614,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10664,7 +10664,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10714,7 +10714,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10764,7 +10764,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10814,7 +10814,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10864,7 +10864,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10914,7 +10914,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11114,7 +11114,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11164,7 +11164,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11214,7 +11214,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11264,7 +11264,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11314,7 +11314,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11364,7 +11364,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11414,7 +11414,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11464,7 +11464,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11514,7 +11514,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11564,7 +11564,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11614,7 +11614,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11664,7 +11664,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11914,7 +11914,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11964,7 +11964,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12014,7 +12014,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12064,7 +12064,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12114,7 +12114,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12414,7 +12414,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12464,7 +12464,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12514,7 +12514,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12564,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12614,7 +12614,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12664,7 +12664,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12714,7 +12714,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12764,7 +12764,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12814,7 +12814,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12864,7 +12864,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12914,7 +12914,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -13314,7 +13314,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13364,7 +13364,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13414,7 +13414,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13464,7 +13464,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13964,7 +13964,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14014,7 +14014,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14064,7 +14064,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14114,7 +14114,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14164,7 +14164,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14214,7 +14214,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14264,7 +14264,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14314,7 +14314,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14364,7 +14364,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14414,7 +14414,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14464,7 +14464,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14514,7 +14514,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14564,7 +14564,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14614,7 +14614,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14714,7 +14714,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14764,7 +14764,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14814,7 +14814,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14864,7 +14864,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14914,7 +14914,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14964,7 +14964,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15514,7 +15514,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15564,7 +15564,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15614,7 +15614,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15664,7 +15664,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15714,7 +15714,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15764,7 +15764,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15814,7 +15814,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15864,7 +15864,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15914,7 +15914,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15964,7 +15964,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -16014,7 +16014,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16064,7 +16064,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16114,7 +16114,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16164,7 +16164,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16214,7 +16214,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16264,7 +16264,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16314,7 +16314,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16364,7 +16364,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16414,7 +16414,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16614,7 +16614,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16664,7 +16664,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16714,7 +16714,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -17114,7 +17114,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17164,7 +17164,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17214,7 +17214,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17264,7 +17264,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17514,7 +17514,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17564,7 +17564,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17614,7 +17614,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17664,7 +17664,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -18664,7 +18664,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18714,7 +18714,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18764,7 +18764,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18814,7 +18814,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18864,7 +18864,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18914,7 +18914,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18964,7 +18964,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19014,7 +19014,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19064,7 +19064,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19114,7 +19114,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19164,7 +19164,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19214,7 +19214,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19264,7 +19264,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19314,7 +19314,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19364,7 +19364,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19414,7 +19414,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19464,7 +19464,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19764,7 +19764,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19814,7 +19814,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19864,7 +19864,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19914,7 +19914,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19964,7 +19964,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20014,7 +20014,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20064,7 +20064,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20114,7 +20114,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20164,7 +20164,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20214,7 +20214,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20264,7 +20264,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20314,7 +20314,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20364,7 +20364,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20414,7 +20414,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20714,7 +20714,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20764,7 +20764,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20814,7 +20814,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20864,7 +20864,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20914,7 +20914,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20964,7 +20964,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21014,7 +21014,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21064,7 +21064,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21314,7 +21314,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21364,7 +21364,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21414,7 +21414,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21464,7 +21464,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21514,7 +21514,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21564,7 +21564,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21664,7 +21664,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21714,7 +21714,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21764,7 +21764,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -23914,7 +23914,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23964,7 +23964,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24014,7 +24014,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24064,7 +24064,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24114,7 +24114,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24164,7 +24164,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24214,7 +24214,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24264,7 +24264,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -27364,7 +27364,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27414,7 +27414,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27464,7 +27464,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27514,7 +27514,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27564,7 +27564,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27614,7 +27614,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27664,7 +27664,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27714,7 +27714,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27764,7 +27764,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27814,7 +27814,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27864,7 +27864,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27914,7 +27914,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27964,7 +27964,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28014,7 +28014,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28064,7 +28064,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28514,7 +28514,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28564,7 +28564,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28614,7 +28614,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28664,7 +28664,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28864,7 +28864,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28914,7 +28914,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28964,7 +28964,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29014,7 +29014,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29064,7 +29064,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29114,7 +29114,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29164,7 +29164,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29214,7 +29214,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29264,7 +29264,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29314,7 +29314,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29364,7 +29364,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29414,7 +29414,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29914,7 +29914,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -29964,7 +29964,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30014,7 +30014,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30064,7 +30064,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30114,7 +30114,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30164,7 +30164,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30214,7 +30214,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30264,7 +30264,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30314,7 +30314,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30364,7 +30364,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30964,7 +30964,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31014,7 +31014,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31064,7 +31064,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31114,7 +31114,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31164,7 +31164,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31214,7 +31214,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31264,7 +31264,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31714,7 +31714,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -31764,7 +31764,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -31914,7 +31914,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -31964,7 +31964,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32014,7 +32014,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32064,7 +32064,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32114,7 +32114,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32164,7 +32164,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -35114,7 +35114,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35164,7 +35164,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35214,7 +35214,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35264,7 +35264,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35314,7 +35314,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35364,7 +35364,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35414,7 +35414,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35464,7 +35464,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35514,7 +35514,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35564,7 +35564,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35614,7 +35614,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35664,7 +35664,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35714,7 +35714,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35764,7 +35764,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35814,7 +35814,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35864,7 +35864,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35914,7 +35914,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35964,7 +35964,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36014,7 +36014,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36214,7 +36214,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36264,7 +36264,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36314,7 +36314,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36364,7 +36364,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36414,7 +36414,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36464,7 +36464,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36514,7 +36514,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36564,7 +36564,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36614,7 +36614,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36664,7 +36664,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36714,7 +36714,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36764,7 +36764,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36814,7 +36814,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36864,7 +36864,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36914,7 +36914,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36964,7 +36964,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37014,7 +37014,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37064,7 +37064,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37114,7 +37114,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37164,7 +37164,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37214,7 +37214,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37464,7 +37464,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37564,7 +37564,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37614,7 +37614,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37664,7 +37664,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37714,7 +37714,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37764,7 +37764,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37814,7 +37814,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37864,7 +37864,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37914,7 +37914,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37964,7 +37964,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38014,7 +38014,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38064,7 +38064,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38114,7 +38114,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38164,7 +38164,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38214,7 +38214,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38264,7 +38264,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38314,7 +38314,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38364,7 +38364,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38414,7 +38414,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38464,7 +38464,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38514,7 +38514,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38564,7 +38564,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38614,7 +38614,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38664,7 +38664,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38714,7 +38714,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38764,7 +38764,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38814,7 +38814,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38864,7 +38864,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38914,7 +38914,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38964,7 +38964,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39014,7 +39014,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39064,7 +39064,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39114,7 +39114,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39164,7 +39164,7 @@
         <v>1</v>
       </c>
       <c r="P747" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39214,7 +39214,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39264,7 +39264,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39314,7 +39314,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39364,7 +39364,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39414,7 +39414,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39464,7 +39464,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39514,7 +39514,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39564,7 +39564,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39614,7 +39614,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39664,7 +39664,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39714,7 +39714,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39764,7 +39764,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39814,7 +39814,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40014,7 +40014,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40064,7 +40064,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40114,7 +40114,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -40214,7 +40214,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40264,7 +40264,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40314,7 +40314,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40364,7 +40364,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40414,7 +40414,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40464,7 +40464,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40514,7 +40514,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40564,7 +40564,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40614,7 +40614,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40664,7 +40664,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40714,7 +40714,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -40764,7 +40764,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -40814,7 +40814,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -40864,7 +40864,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40914,7 +40914,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40964,7 +40964,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41014,7 +41014,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41064,7 +41064,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41114,7 +41114,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41164,7 +41164,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41214,7 +41214,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41264,7 +41264,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41314,7 +41314,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41364,7 +41364,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41414,7 +41414,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41714,7 +41714,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -41764,7 +41764,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41814,7 +41814,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41864,7 +41864,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42014,7 +42014,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42064,7 +42064,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42214,7 +42214,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42264,7 +42264,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42314,7 +42314,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42364,7 +42364,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42414,7 +42414,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42614,7 +42614,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42664,7 +42664,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42714,7 +42714,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -42764,7 +42764,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -42814,7 +42814,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -42864,7 +42864,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -42914,7 +42914,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42964,7 +42964,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43014,7 +43014,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43364,7 +43364,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43414,7 +43414,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43464,7 +43464,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43664,7 +43664,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43714,7 +43714,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43764,7 +43764,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43814,7 +43814,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43864,7 +43864,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43914,7 +43914,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44064,7 +44064,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44114,7 +44114,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44164,7 +44164,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44214,7 +44214,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44264,7 +44264,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44514,7 +44514,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44564,7 +44564,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44614,7 +44614,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44664,7 +44664,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44964,7 +44964,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45014,7 +45014,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45064,7 +45064,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45114,7 +45114,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45264,7 +45264,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45314,7 +45314,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45364,7 +45364,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45414,7 +45414,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45864,7 +45864,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -45914,7 +45914,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46264,7 +46264,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -46314,7 +46314,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46464,7 +46464,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46514,7 +46514,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46564,7 +46564,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46575,90 +46575,90 @@
         <v>206</v>
       </c>
       <c r="C896">
-        <v>1.635010114276823</v>
+        <v>1.490242187015885</v>
       </c>
       <c r="D896" t="s">
         <v>342</v>
       </c>
       <c r="E896">
-        <v>1.535619265389657</v>
+        <v>1.481117416809536</v>
       </c>
       <c r="F896">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G896">
-        <v>0.01090498988572318</v>
+        <v>0.01106975781298412</v>
       </c>
       <c r="H896">
-        <v>0.01088438073461034</v>
+        <v>0.01077888258319046</v>
       </c>
       <c r="I896">
-        <v>0.09939084888716643</v>
+        <v>-0.009124770206349275</v>
       </c>
       <c r="J896">
-        <v>1.31302829623886</v>
+        <v>1.280683907215004</v>
       </c>
       <c r="K896">
-        <v>3.53</v>
+        <v>3.74</v>
       </c>
       <c r="L896">
-        <v>6.27</v>
+        <v>6.28</v>
       </c>
       <c r="M896">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="N896">
-        <v>6.21</v>
+        <v>6.13</v>
       </c>
       <c r="O896">
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="897" spans="1:16">
       <c r="A897" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B897" t="s">
         <v>207</v>
       </c>
       <c r="C897">
+        <v>1.635010114276823</v>
+      </c>
+      <c r="D897" t="s">
+        <v>206</v>
+      </c>
+      <c r="E897">
         <v>1.369274172066662</v>
       </c>
-      <c r="D897" t="s">
-        <v>343</v>
-      </c>
-      <c r="E897">
-        <v>1.454316435765771</v>
-      </c>
       <c r="F897">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G897">
+        <v>0.01090498988572318</v>
+      </c>
+      <c r="H897">
         <v>0.01119072582793334</v>
       </c>
-      <c r="H897">
-        <v>0.01106568356423423</v>
-      </c>
       <c r="I897">
-        <v>0.08504226369910839</v>
+        <v>0.2657359422101608</v>
       </c>
       <c r="J897">
         <v>1.31302829623886</v>
       </c>
       <c r="K897">
+        <v>3.53</v>
+      </c>
+      <c r="L897">
+        <v>6.27</v>
+      </c>
+      <c r="M897">
         <v>3.74</v>
       </c>
-      <c r="L897">
+      <c r="N897">
         <v>6.28</v>
-      </c>
-      <c r="M897">
-        <v>3.66</v>
-      </c>
-      <c r="N897">
-        <v>6.26</v>
       </c>
       <c r="O897">
         <v>1</v>
@@ -46672,13 +46672,13 @@
         <v>0</v>
       </c>
       <c r="B898" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C898">
         <v>1.631068392352668</v>
       </c>
       <c r="D898" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E898">
         <v>1.365097956770249</v>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2715" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="483">
   <si>
     <t>trade_time</t>
   </si>
@@ -634,418 +634,418 @@
     <t>2021-08-20</t>
   </si>
   <si>
+    <t>2021-10-12</t>
+  </si>
+  <si>
+    <t>2021-09-28</t>
+  </si>
+  <si>
+    <t>2016-08-08</t>
+  </si>
+  <si>
+    <t>2016-09-05</t>
+  </si>
+  <si>
+    <t>2016-09-06</t>
+  </si>
+  <si>
+    <t>2016-09-07</t>
+  </si>
+  <si>
+    <t>2016-09-08</t>
+  </si>
+  <si>
+    <t>2016-09-09</t>
+  </si>
+  <si>
+    <t>2016-09-12</t>
+  </si>
+  <si>
+    <t>2016-09-13</t>
+  </si>
+  <si>
+    <t>2016-09-14</t>
+  </si>
+  <si>
+    <t>2016-09-19</t>
+  </si>
+  <si>
+    <t>2016-09-20</t>
+  </si>
+  <si>
+    <t>2016-09-21</t>
+  </si>
+  <si>
+    <t>2016-08-19</t>
+  </si>
+  <si>
+    <t>2016-10-13</t>
+  </si>
+  <si>
+    <t>2016-10-25</t>
+  </si>
+  <si>
+    <t>2016-10-26</t>
+  </si>
+  <si>
+    <t>2016-10-28</t>
+  </si>
+  <si>
+    <t>2016-10-18</t>
+  </si>
+  <si>
+    <t>2016-11-14</t>
+  </si>
+  <si>
+    <t>2016-11-29</t>
+  </si>
+  <si>
+    <t>2016-12-12</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-02-15</t>
+  </si>
+  <si>
+    <t>2017-03-01</t>
+  </si>
+  <si>
+    <t>2017-03-17</t>
+  </si>
+  <si>
+    <t>2017-05-31</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-07-11</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-07-17</t>
+  </si>
+  <si>
+    <t>2017-07-25</t>
+  </si>
+  <si>
+    <t>2017-06-23</t>
+  </si>
+  <si>
+    <t>2017-07-26</t>
+  </si>
+  <si>
+    <t>2017-07-27</t>
+  </si>
+  <si>
+    <t>2017-07-31</t>
+  </si>
+  <si>
+    <t>2017-08-01</t>
+  </si>
+  <si>
+    <t>2017-08-02</t>
+  </si>
+  <si>
+    <t>2017-08-03</t>
+  </si>
+  <si>
+    <t>2017-07-13</t>
+  </si>
+  <si>
+    <t>2017-08-10</t>
+  </si>
+  <si>
+    <t>2017-08-11</t>
+  </si>
+  <si>
+    <t>2017-08-16</t>
+  </si>
+  <si>
+    <t>2018-04-27</t>
+  </si>
+  <si>
+    <t>2018-05-02</t>
+  </si>
+  <si>
+    <t>2018-06-01</t>
+  </si>
+  <si>
+    <t>2018-06-27</t>
+  </si>
+  <si>
+    <t>2018-05-30</t>
+  </si>
+  <si>
+    <t>2018-06-15</t>
+  </si>
+  <si>
+    <t>2018-05-31</t>
+  </si>
+  <si>
+    <t>2018-06-05</t>
+  </si>
+  <si>
+    <t>2018-07-12</t>
+  </si>
+  <si>
+    <t>2018-07-13</t>
+  </si>
+  <si>
+    <t>2018-10-29</t>
+  </si>
+  <si>
+    <t>2018-11-06</t>
+  </si>
+  <si>
+    <t>2018-11-26</t>
+  </si>
+  <si>
+    <t>2018-11-07</t>
+  </si>
+  <si>
+    <t>2018-11-21</t>
+  </si>
+  <si>
+    <t>2018-12-03</t>
+  </si>
+  <si>
+    <t>2018-12-19</t>
+  </si>
+  <si>
+    <t>2019-01-10</t>
+  </si>
+  <si>
+    <t>2019-01-14</t>
+  </si>
+  <si>
+    <t>2019-01-15</t>
+  </si>
+  <si>
+    <t>2018-12-27</t>
+  </si>
+  <si>
+    <t>2019-01-17</t>
+  </si>
+  <si>
+    <t>2019-01-21</t>
+  </si>
+  <si>
+    <t>2018-12-10</t>
+  </si>
+  <si>
+    <t>2019-01-02</t>
+  </si>
+  <si>
+    <t>2019-01-30</t>
+  </si>
+  <si>
+    <t>2019-01-31</t>
+  </si>
+  <si>
+    <t>2019-02-01</t>
+  </si>
+  <si>
+    <t>2019-02-11</t>
+  </si>
+  <si>
+    <t>2019-02-12</t>
+  </si>
+  <si>
+    <t>2019-02-13</t>
+  </si>
+  <si>
+    <t>2019-02-15</t>
+  </si>
+  <si>
+    <t>2019-02-18</t>
+  </si>
+  <si>
+    <t>2019-02-19</t>
+  </si>
+  <si>
+    <t>2019-02-21</t>
+  </si>
+  <si>
+    <t>2019-02-22</t>
+  </si>
+  <si>
+    <t>2019-02-25</t>
+  </si>
+  <si>
+    <t>2019-03-05</t>
+  </si>
+  <si>
+    <t>2019-03-06</t>
+  </si>
+  <si>
+    <t>2019-03-12</t>
+  </si>
+  <si>
+    <t>2019-03-14</t>
+  </si>
+  <si>
+    <t>2019-03-15</t>
+  </si>
+  <si>
+    <t>2019-03-20</t>
+  </si>
+  <si>
+    <t>2019-03-21</t>
+  </si>
+  <si>
+    <t>2019-03-22</t>
+  </si>
+  <si>
+    <t>2019-03-25</t>
+  </si>
+  <si>
+    <t>2019-03-26</t>
+  </si>
+  <si>
+    <t>2019-08-13</t>
+  </si>
+  <si>
+    <t>2019-08-26</t>
+  </si>
+  <si>
+    <t>2019-09-04</t>
+  </si>
+  <si>
+    <t>2019-09-17</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-10-18</t>
+  </si>
+  <si>
+    <t>2019-10-29</t>
+  </si>
+  <si>
+    <t>2019-09-30</t>
+  </si>
+  <si>
+    <t>2019-11-26</t>
+  </si>
+  <si>
+    <t>2019-12-06</t>
+  </si>
+  <si>
+    <t>2019-12-10</t>
+  </si>
+  <si>
+    <t>2019-12-13</t>
+  </si>
+  <si>
+    <t>2019-12-16</t>
+  </si>
+  <si>
+    <t>2019-12-19</t>
+  </si>
+  <si>
+    <t>2020-01-03</t>
+  </si>
+  <si>
+    <t>2020-01-06</t>
+  </si>
+  <si>
+    <t>2019-12-24</t>
+  </si>
+  <si>
+    <t>2020-01-14</t>
+  </si>
+  <si>
+    <t>2020-01-17</t>
+  </si>
+  <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
+    <t>2020-01-22</t>
+  </si>
+  <si>
+    <t>2020-09-11</t>
+  </si>
+  <si>
+    <t>2020-08-10</t>
+  </si>
+  <si>
+    <t>2020-09-01</t>
+  </si>
+  <si>
+    <t>2020-09-22</t>
+  </si>
+  <si>
+    <t>2020-09-23</t>
+  </si>
+  <si>
+    <t>2021-01-14</t>
+  </si>
+  <si>
+    <t>2021-01-07</t>
+  </si>
+  <si>
+    <t>2021-01-22</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-02-02</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-05-20</t>
+  </si>
+  <si>
+    <t>2021-06-11</t>
+  </si>
+  <si>
+    <t>2021-06-15</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-07-20</t>
+  </si>
+  <si>
+    <t>2021-08-13</t>
+  </si>
+  <si>
+    <t>2021-08-23</t>
+  </si>
+  <si>
+    <t>2021-10-19</t>
+  </si>
+  <si>
     <t>2021-10-08</t>
-  </si>
-  <si>
-    <t>2021-10-12</t>
-  </si>
-  <si>
-    <t>2021-09-28</t>
-  </si>
-  <si>
-    <t>2016-08-08</t>
-  </si>
-  <si>
-    <t>2016-09-05</t>
-  </si>
-  <si>
-    <t>2016-09-06</t>
-  </si>
-  <si>
-    <t>2016-09-07</t>
-  </si>
-  <si>
-    <t>2016-09-08</t>
-  </si>
-  <si>
-    <t>2016-09-09</t>
-  </si>
-  <si>
-    <t>2016-09-12</t>
-  </si>
-  <si>
-    <t>2016-09-13</t>
-  </si>
-  <si>
-    <t>2016-09-14</t>
-  </si>
-  <si>
-    <t>2016-09-19</t>
-  </si>
-  <si>
-    <t>2016-09-20</t>
-  </si>
-  <si>
-    <t>2016-09-21</t>
-  </si>
-  <si>
-    <t>2016-08-19</t>
-  </si>
-  <si>
-    <t>2016-10-13</t>
-  </si>
-  <si>
-    <t>2016-10-25</t>
-  </si>
-  <si>
-    <t>2016-10-26</t>
-  </si>
-  <si>
-    <t>2016-10-28</t>
-  </si>
-  <si>
-    <t>2016-10-18</t>
-  </si>
-  <si>
-    <t>2016-11-14</t>
-  </si>
-  <si>
-    <t>2016-11-29</t>
-  </si>
-  <si>
-    <t>2016-12-12</t>
-  </si>
-  <si>
-    <t>2017-02-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-02-15</t>
-  </si>
-  <si>
-    <t>2017-03-01</t>
-  </si>
-  <si>
-    <t>2017-03-17</t>
-  </si>
-  <si>
-    <t>2017-05-31</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-07-11</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-07-17</t>
-  </si>
-  <si>
-    <t>2017-07-25</t>
-  </si>
-  <si>
-    <t>2017-06-23</t>
-  </si>
-  <si>
-    <t>2017-07-26</t>
-  </si>
-  <si>
-    <t>2017-07-27</t>
-  </si>
-  <si>
-    <t>2017-07-31</t>
-  </si>
-  <si>
-    <t>2017-08-01</t>
-  </si>
-  <si>
-    <t>2017-08-02</t>
-  </si>
-  <si>
-    <t>2017-08-03</t>
-  </si>
-  <si>
-    <t>2017-07-13</t>
-  </si>
-  <si>
-    <t>2017-08-10</t>
-  </si>
-  <si>
-    <t>2017-08-11</t>
-  </si>
-  <si>
-    <t>2017-08-16</t>
-  </si>
-  <si>
-    <t>2018-04-27</t>
-  </si>
-  <si>
-    <t>2018-05-02</t>
-  </si>
-  <si>
-    <t>2018-06-01</t>
-  </si>
-  <si>
-    <t>2018-06-27</t>
-  </si>
-  <si>
-    <t>2018-05-30</t>
-  </si>
-  <si>
-    <t>2018-06-15</t>
-  </si>
-  <si>
-    <t>2018-05-31</t>
-  </si>
-  <si>
-    <t>2018-06-05</t>
-  </si>
-  <si>
-    <t>2018-07-12</t>
-  </si>
-  <si>
-    <t>2018-07-13</t>
-  </si>
-  <si>
-    <t>2018-10-29</t>
-  </si>
-  <si>
-    <t>2018-11-06</t>
-  </si>
-  <si>
-    <t>2018-11-26</t>
-  </si>
-  <si>
-    <t>2018-11-07</t>
-  </si>
-  <si>
-    <t>2018-11-21</t>
-  </si>
-  <si>
-    <t>2018-12-03</t>
-  </si>
-  <si>
-    <t>2018-12-19</t>
-  </si>
-  <si>
-    <t>2019-01-10</t>
-  </si>
-  <si>
-    <t>2019-01-14</t>
-  </si>
-  <si>
-    <t>2019-01-15</t>
-  </si>
-  <si>
-    <t>2018-12-27</t>
-  </si>
-  <si>
-    <t>2019-01-17</t>
-  </si>
-  <si>
-    <t>2019-01-21</t>
-  </si>
-  <si>
-    <t>2018-12-10</t>
-  </si>
-  <si>
-    <t>2019-01-02</t>
-  </si>
-  <si>
-    <t>2019-01-30</t>
-  </si>
-  <si>
-    <t>2019-01-31</t>
-  </si>
-  <si>
-    <t>2019-02-01</t>
-  </si>
-  <si>
-    <t>2019-02-11</t>
-  </si>
-  <si>
-    <t>2019-02-12</t>
-  </si>
-  <si>
-    <t>2019-02-13</t>
-  </si>
-  <si>
-    <t>2019-02-15</t>
-  </si>
-  <si>
-    <t>2019-02-18</t>
-  </si>
-  <si>
-    <t>2019-02-19</t>
-  </si>
-  <si>
-    <t>2019-02-21</t>
-  </si>
-  <si>
-    <t>2019-02-22</t>
-  </si>
-  <si>
-    <t>2019-02-25</t>
-  </si>
-  <si>
-    <t>2019-03-05</t>
-  </si>
-  <si>
-    <t>2019-03-06</t>
-  </si>
-  <si>
-    <t>2019-03-12</t>
-  </si>
-  <si>
-    <t>2019-03-14</t>
-  </si>
-  <si>
-    <t>2019-03-15</t>
-  </si>
-  <si>
-    <t>2019-03-20</t>
-  </si>
-  <si>
-    <t>2019-03-21</t>
-  </si>
-  <si>
-    <t>2019-03-22</t>
-  </si>
-  <si>
-    <t>2019-03-25</t>
-  </si>
-  <si>
-    <t>2019-03-26</t>
-  </si>
-  <si>
-    <t>2019-08-13</t>
-  </si>
-  <si>
-    <t>2019-08-26</t>
-  </si>
-  <si>
-    <t>2019-09-04</t>
-  </si>
-  <si>
-    <t>2019-09-17</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-10-18</t>
-  </si>
-  <si>
-    <t>2019-10-29</t>
-  </si>
-  <si>
-    <t>2019-09-30</t>
-  </si>
-  <si>
-    <t>2019-11-26</t>
-  </si>
-  <si>
-    <t>2019-12-06</t>
-  </si>
-  <si>
-    <t>2019-12-10</t>
-  </si>
-  <si>
-    <t>2019-12-13</t>
-  </si>
-  <si>
-    <t>2019-12-16</t>
-  </si>
-  <si>
-    <t>2019-12-19</t>
-  </si>
-  <si>
-    <t>2020-01-03</t>
-  </si>
-  <si>
-    <t>2020-01-06</t>
-  </si>
-  <si>
-    <t>2019-12-24</t>
-  </si>
-  <si>
-    <t>2020-01-14</t>
-  </si>
-  <si>
-    <t>2020-01-17</t>
-  </si>
-  <si>
-    <t>2019-12-31</t>
-  </si>
-  <si>
-    <t>2020-01-22</t>
-  </si>
-  <si>
-    <t>2020-09-11</t>
-  </si>
-  <si>
-    <t>2020-08-10</t>
-  </si>
-  <si>
-    <t>2020-09-01</t>
-  </si>
-  <si>
-    <t>2020-09-22</t>
-  </si>
-  <si>
-    <t>2020-09-23</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-22</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-05-20</t>
-  </si>
-  <si>
-    <t>2021-06-11</t>
-  </si>
-  <si>
-    <t>2021-06-15</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-07-20</t>
-  </si>
-  <si>
-    <t>2021-08-13</t>
-  </si>
-  <si>
-    <t>2021-08-23</t>
-  </si>
-  <si>
-    <t>2021-10-18</t>
   </si>
   <si>
     <t>2016-07-11</t>
@@ -1820,7 +1820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P901"/>
+  <dimension ref="A1:P899"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1881,7 +1881,7 @@
         <v>3.51273100348791</v>
       </c>
       <c r="D2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E2">
         <v>3.28358785697468</v>
@@ -1931,7 +1931,7 @@
         <v>3.487126941772404</v>
       </c>
       <c r="D3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E3">
         <v>3.28358785697468</v>
@@ -1981,7 +1981,7 @@
         <v>3.411368566458607</v>
       </c>
       <c r="D4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E4">
         <v>3.28358785697468</v>
@@ -2031,7 +2031,7 @@
         <v>4.114907651256331</v>
       </c>
       <c r="D5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E5">
         <v>3.865258921200569</v>
@@ -2081,7 +2081,7 @@
         <v>4.017281255370698</v>
       </c>
       <c r="D6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E6">
         <v>3.865258921200569</v>
@@ -2131,7 +2131,7 @@
         <v>3.250435096360468</v>
       </c>
       <c r="D7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E7">
         <v>3.016620926843599</v>
@@ -2181,7 +2181,7 @@
         <v>3.230220676572238</v>
       </c>
       <c r="D8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E8">
         <v>3.016620926843599</v>
@@ -2231,7 +2231,7 @@
         <v>3.152306444487531</v>
       </c>
       <c r="D9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E9">
         <v>3.016620926843599</v>
@@ -2281,7 +2281,7 @@
         <v>3.865906194216171</v>
       </c>
       <c r="D10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E10">
         <v>3.550292149834982</v>
@@ -2331,7 +2331,7 @@
         <v>3.767920488868719</v>
       </c>
       <c r="D11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E11">
         <v>3.550292149834982</v>
@@ -2381,7 +2381,7 @@
         <v>3.172782159400292</v>
       </c>
       <c r="D12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E12">
         <v>2.937585129362215</v>
@@ -2431,7 +2431,7 @@
         <v>3.154163347905764</v>
       </c>
       <c r="D13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E13">
         <v>2.937585129362215</v>
@@ -2481,7 +2481,7 @@
         <v>3.075610872503576</v>
       </c>
       <c r="D14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E14">
         <v>2.937585129362215</v>
@@ -2531,7 +2531,7 @@
         <v>3.792189091047127</v>
       </c>
       <c r="D15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E15">
         <v>3.524163347905765</v>
@@ -2581,7 +2581,7 @@
         <v>3.694097011813428</v>
       </c>
       <c r="D16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E16">
         <v>3.524163347905765</v>
@@ -2631,7 +2631,7 @@
         <v>3.131337540570926</v>
       </c>
       <c r="D17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E17">
         <v>2.895402455676983</v>
@@ -2681,7 +2681,7 @@
         <v>3.113570330833166</v>
       </c>
       <c r="D18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E18">
         <v>2.895402455676983</v>
@@ -2731,7 +2731,7 @@
         <v>3.034677214728271</v>
       </c>
       <c r="D19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E19">
         <v>2.895402455676983</v>
@@ -2781,7 +2781,7 @@
         <v>3.752845089884454</v>
       </c>
       <c r="D20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E20">
         <v>3.419123772780718</v>
@@ -2831,7 +2831,7 @@
         <v>3.654696237200305</v>
       </c>
       <c r="D21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E21">
         <v>3.419123772780718</v>
@@ -2881,7 +2881,7 @@
         <v>2.917985536997794</v>
       </c>
       <c r="D22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E22">
         <v>2.678251032862137</v>
@@ -2931,7 +2931,7 @@
         <v>2.904602272538934</v>
       </c>
       <c r="D23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E23">
         <v>2.678251032862137</v>
@@ -2981,7 +2981,7 @@
         <v>2.823955578322479</v>
       </c>
       <c r="D24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E24">
         <v>2.678251032862137</v>
@@ -3031,7 +3031,7 @@
         <v>3.550306817999275</v>
       </c>
       <c r="D25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E25">
         <v>3.171749999808766</v>
@@ -3081,7 +3081,7 @@
         <v>3.451865702296533</v>
       </c>
       <c r="D26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E26">
         <v>3.171749999808766</v>
@@ -3131,7 +3131,7 @@
         <v>2.695092590325597</v>
       </c>
       <c r="D27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E27">
         <v>2.451388759742354</v>
@@ -3181,7 +3181,7 @@
         <v>2.686289317921646</v>
       </c>
       <c r="D28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E28">
         <v>2.451388759742354</v>
@@ -3231,7 +3231,7 @@
         <v>2.603810626883227</v>
       </c>
       <c r="D29" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E29">
         <v>2.451388759742354</v>
@@ -3281,7 +3281,7 @@
         <v>3.33871118506252</v>
       </c>
       <c r="D30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E30">
         <v>3.111246699998485</v>
@@ -3331,7 +3331,7 @@
         <v>2.573608795274185</v>
       </c>
       <c r="D31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E31">
         <v>2.327741554642081</v>
@@ -3381,7 +3381,7 @@
         <v>2.567301765234304</v>
       </c>
       <c r="D32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E32">
         <v>2.327741554642081</v>
@@ -3431,7 +3431,7 @@
         <v>2.483824577250257</v>
       </c>
       <c r="D33" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E33">
         <v>2.327741554642081</v>
@@ -3481,7 +3481,7 @@
         <v>3.22338478784248</v>
       </c>
       <c r="D34" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E34">
         <v>3.00338478784248</v>
@@ -3531,7 +3531,7 @@
         <v>3.124471923178472</v>
       </c>
       <c r="D35" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E35">
         <v>3.00338478784248</v>
@@ -3581,7 +3581,7 @@
         <v>2.525023995746672</v>
       </c>
       <c r="D36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E36">
         <v>2.278291546355859</v>
@@ -3631,7 +3631,7 @@
         <v>2.519715283505301</v>
       </c>
       <c r="D37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E37">
         <v>2.278291546355859</v>
@@ -3681,7 +3681,7 @@
         <v>2.43583876840185</v>
       </c>
       <c r="D38" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E38">
         <v>2.278291546355859</v>
@@ -3731,7 +3731,7 @@
         <v>3.177262505551293</v>
       </c>
       <c r="D39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E39">
         <v>2.878283086367383</v>
@@ -3781,7 +3781,7 @@
         <v>2.49367544506272</v>
       </c>
       <c r="D40" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E40">
         <v>2.246384733810411</v>
@@ -3831,7 +3831,7 @@
         <v>2.489010881123074</v>
       </c>
       <c r="D41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E41">
         <v>2.246384733810411</v>
@@ -3881,7 +3881,7 @@
         <v>2.404876706698933</v>
       </c>
       <c r="D42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E42">
         <v>2.246384733810411</v>
@@ -3931,7 +3931,7 @@
         <v>3.147502854011596</v>
       </c>
       <c r="D43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E43">
         <v>2.81434631718343</v>
@@ -3981,7 +3981,7 @@
         <v>2.435576766372018</v>
       </c>
       <c r="D44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E44">
         <v>2.187251421115628</v>
@@ -4031,7 +4031,7 @@
         <v>2.432106010898619</v>
       </c>
       <c r="D45" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E45">
         <v>2.187251421115628</v>
@@ -4081,7 +4081,7 @@
         <v>2.347494313087979</v>
       </c>
       <c r="D46" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E46">
         <v>2.187251421115628</v>
@@ -4131,7 +4131,7 @@
         <v>3.092348902870971</v>
       </c>
       <c r="D47" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E47">
         <v>2.737737205060329</v>
@@ -4181,7 +4181,7 @@
         <v>2.371772059045239</v>
       </c>
       <c r="D48" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E48">
         <v>2.122310465576181</v>
@@ -4231,7 +4231,7 @@
         <v>2.369612359201843</v>
       </c>
       <c r="D49" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E49">
         <v>2.122310465576181</v>
@@ -4281,7 +4281,7 @@
         <v>2.284476239139202</v>
       </c>
       <c r="D50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E50">
         <v>2.122310465576181</v>
@@ -4331,7 +4331,7 @@
         <v>3.031778132764864</v>
       </c>
       <c r="D51" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E51">
         <v>2.649073952670901</v>
@@ -4381,7 +4381,7 @@
         <v>2.321868001707651</v>
       </c>
       <c r="D52" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E52">
         <v>2.07151770584765</v>
@@ -4431,7 +4431,7 @@
         <v>2.320733727699959</v>
       </c>
       <c r="D53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E53">
         <v>2.07151770584765</v>
@@ -4481,7 +4481,7 @@
         <v>2.235187437303036</v>
       </c>
       <c r="D54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E54">
         <v>2.07151770584765</v>
@@ -4581,7 +4581,7 @@
         <v>2.151512527619126</v>
       </c>
       <c r="D56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E56">
         <v>2.792784685035415</v>
@@ -4681,7 +4681,7 @@
         <v>2.060915719062437</v>
       </c>
       <c r="D58" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E58">
         <v>2.69992609762433</v>
@@ -4781,7 +4781,7 @@
         <v>1.929841637735545</v>
       </c>
       <c r="D60" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E60">
         <v>2.565579709135323</v>
@@ -4881,7 +4881,7 @@
         <v>1.724822206455505</v>
       </c>
       <c r="D62" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E62">
         <v>2.355441900930122</v>
@@ -4981,7 +4981,7 @@
         <v>1.674034425134113</v>
       </c>
       <c r="D64" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E64">
         <v>2.303386186094466</v>
@@ -5081,7 +5081,7 @@
         <v>1.623841162955755</v>
       </c>
       <c r="D66" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E66">
         <v>2.251939832766024</v>
@@ -5231,7 +5231,7 @@
         <v>2.333284107344603</v>
       </c>
       <c r="D69" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E69">
         <v>1.896773826741966</v>
@@ -5267,7 +5267,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5281,7 +5281,7 @@
         <v>2.326740023309851</v>
       </c>
       <c r="D70" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E70">
         <v>1.889918119657939</v>
@@ -5331,7 +5331,7 @@
         <v>1.672605536248085</v>
       </c>
       <c r="D71" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E71">
         <v>2.015292952838233</v>
@@ -5381,7 +5381,7 @@
         <v>2.422236961918112</v>
       </c>
       <c r="D72" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E72">
         <v>2.050376064330505</v>
@@ -5431,7 +5431,7 @@
         <v>2.322168039785237</v>
       </c>
       <c r="D73" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E73">
         <v>2.050376064330505</v>
@@ -5481,7 +5481,7 @@
         <v>2.400031453666133</v>
       </c>
       <c r="D74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E74">
         <v>2.26996253153326</v>
@@ -5531,7 +5531,7 @@
         <v>2.452252719470961</v>
       </c>
       <c r="D75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E75">
         <v>2.081561266982816</v>
@@ -5567,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5581,7 +5581,7 @@
         <v>2.36235515687661</v>
       </c>
       <c r="D76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E76">
         <v>2.081561266982816</v>
@@ -5617,7 +5617,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5631,7 +5631,7 @@
         <v>2.352227110119547</v>
       </c>
       <c r="D77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E77">
         <v>2.081561266982816</v>
@@ -5667,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5681,7 +5681,7 @@
         <v>2.431433220225751</v>
       </c>
       <c r="D78" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E78">
         <v>2.311714923091293</v>
@@ -5717,7 +5717,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5731,7 +5731,7 @@
         <v>2.454094657085679</v>
       </c>
       <c r="D79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E79">
         <v>2.083474968400705</v>
@@ -5781,7 +5781,7 @@
         <v>2.364186462816786</v>
       </c>
       <c r="D80" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E80">
         <v>2.083474968400705</v>
@@ -5831,7 +5831,7 @@
         <v>2.354071705652902</v>
       </c>
       <c r="D81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E81">
         <v>2.083474968400705</v>
@@ -5931,7 +5931,7 @@
         <v>2.339781007767745</v>
       </c>
       <c r="D83" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E83">
         <v>2.057971444982259</v>
@@ -5981,7 +5981,7 @@
         <v>2.329489142802344</v>
       </c>
       <c r="D84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E84">
         <v>2.057971444982259</v>
@@ -6031,7 +6031,7 @@
         <v>2.407679580016858</v>
       </c>
       <c r="D85" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E85">
         <v>2.25849680191998</v>
@@ -6081,7 +6081,7 @@
         <v>2.36826330994766</v>
       </c>
       <c r="D86" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E86">
         <v>2.25849680191998</v>
@@ -6131,7 +6131,7 @@
         <v>3.548245528330676</v>
       </c>
       <c r="D87" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E87">
         <v>4.061344787936081</v>
@@ -6167,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6181,7 +6181,7 @@
         <v>4.409079280825154</v>
       </c>
       <c r="D88" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E88">
         <v>4.814235609417867</v>
@@ -6217,7 +6217,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6231,7 +6231,7 @@
         <v>5.769925742504288</v>
       </c>
       <c r="D89" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E89">
         <v>6.769399637973693</v>
@@ -6281,7 +6281,7 @@
         <v>7.229395624055007</v>
       </c>
       <c r="D90" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E90">
         <v>8.109917714666915</v>
@@ -6331,7 +6331,7 @@
         <v>5.828616664074527</v>
       </c>
       <c r="D91" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E91">
         <v>6.827923586794087</v>
@@ -6381,7 +6381,7 @@
         <v>6.627254795247419</v>
       </c>
       <c r="D92" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E92">
         <v>7.429368904817279</v>
@@ -6417,7 +6417,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6431,7 +6431,7 @@
         <v>6.647982466464144</v>
       </c>
       <c r="D93" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E93">
         <v>7.429368904817279</v>
@@ -6467,7 +6467,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6481,7 +6481,7 @@
         <v>6.738850879729914</v>
       </c>
       <c r="D94" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E94">
         <v>7.519850094731065</v>
@@ -6531,7 +6531,7 @@
         <v>6.79484616973682</v>
       </c>
       <c r="D95" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E95">
         <v>7.519850094731065</v>
@@ -6581,7 +6581,7 @@
         <v>7.382736713736916</v>
       </c>
       <c r="D96" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E96">
         <v>6.823146636869726</v>
@@ -6631,7 +6631,7 @@
         <v>4.077630001836678</v>
       </c>
       <c r="D97" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E97">
         <v>4.295890041790149</v>
@@ -6681,7 +6681,7 @@
         <v>4.085204721856269</v>
       </c>
       <c r="D98" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E98">
         <v>4.295890041790149</v>
@@ -6731,7 +6731,7 @@
         <v>0.2559344762264057</v>
       </c>
       <c r="D99" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E99">
         <v>0.4288461810550128</v>
@@ -6831,7 +6831,7 @@
         <v>0.3089776058983933</v>
       </c>
       <c r="D101" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E101">
         <v>0.07644783487002726</v>
@@ -6881,7 +6881,7 @@
         <v>0.2660659010697888</v>
       </c>
       <c r="D102" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E102">
         <v>-0.001905345815551129</v>
@@ -6981,7 +6981,7 @@
         <v>0.2889545424481916</v>
       </c>
       <c r="D104" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E104">
         <v>0.05610354580297638</v>
@@ -7031,7 +7031,7 @@
         <v>0.246096375222395</v>
       </c>
       <c r="D105" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E105">
         <v>-0.02246378529383364</v>
@@ -7131,7 +7131,7 @@
         <v>-1.630207146872417</v>
       </c>
       <c r="D107" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E107">
         <v>-1.215938554569574</v>
@@ -7181,7 +7181,7 @@
         <v>-1.036774334908403</v>
       </c>
       <c r="D108" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E108">
         <v>-1.383639958836433</v>
@@ -7231,7 +7231,7 @@
         <v>-1.076087772515599</v>
       </c>
       <c r="D109" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E109">
         <v>-1.383639958836433</v>
@@ -7281,7 +7281,7 @@
         <v>-1.110744491319196</v>
       </c>
       <c r="D110" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E110">
         <v>-1.383639958836433</v>
@@ -7331,7 +7331,7 @@
         <v>-1.598983240032837</v>
       </c>
       <c r="D111" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E111">
         <v>-1.755699646014843</v>
@@ -7381,7 +7381,7 @@
         <v>-2.012129891907831</v>
       </c>
       <c r="D112" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E112">
         <v>-1.639595934646165</v>
@@ -7431,7 +7431,7 @@
         <v>-2.069512610754847</v>
       </c>
       <c r="D113" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E113">
         <v>-1.639595934646165</v>
@@ -7481,7 +7481,7 @@
         <v>-1.470284212196077</v>
       </c>
       <c r="D114" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E114">
         <v>-1.828741009313617</v>
@@ -7531,7 +7531,7 @@
         <v>-1.508438532484321</v>
       </c>
       <c r="D115" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E115">
         <v>-1.828741009313617</v>
@@ -7581,7 +7581,7 @@
         <v>-1.542515692628445</v>
       </c>
       <c r="D116" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E116">
         <v>-1.828741009313617</v>
@@ -7631,7 +7631,7 @@
         <v>-2.044663849169496</v>
       </c>
       <c r="D117" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E117">
         <v>-2.204278048448881</v>
@@ -7681,7 +7681,7 @@
         <v>-2.572474789015972</v>
       </c>
       <c r="D118" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E118">
         <v>-2.124642573576088</v>
@@ -7731,7 +7731,7 @@
         <v>-1.96661100551972</v>
       </c>
       <c r="D119" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E119">
         <v>-2.338338572512225</v>
@@ -7781,7 +7781,7 @@
         <v>-2.003438248820469</v>
       </c>
       <c r="D120" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E120">
         <v>-2.338338572512225</v>
@@ -7831,7 +7831,7 @@
         <v>-2.036851870470842</v>
       </c>
       <c r="D121" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E121">
         <v>-2.338338572512225</v>
@@ -7881,7 +7881,7 @@
         <v>-3.407338082790915</v>
       </c>
       <c r="D122" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E122">
         <v>-2.849979157056712</v>
@@ -7931,7 +7931,7 @@
         <v>-3.324602190217494</v>
       </c>
       <c r="D123" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E123">
         <v>-2.849979157056712</v>
@@ -7981,7 +7981,7 @@
         <v>-2.794507371909873</v>
       </c>
       <c r="D124" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E124">
         <v>-3.10038849879556</v>
@@ -8031,7 +8031,7 @@
         <v>-2.708815881639428</v>
       </c>
       <c r="D125" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E125">
         <v>-3.10038849879556</v>
@@ -8081,7 +8081,7 @@
         <v>-2.743658619923814</v>
       </c>
       <c r="D126" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E126">
         <v>-3.10038849879556</v>
@@ -8131,7 +8131,7 @@
         <v>-2.776079989066007</v>
       </c>
       <c r="D127" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E127">
         <v>-3.10038849879556</v>
@@ -8181,7 +8181,7 @@
         <v>-4.198122324411599</v>
       </c>
       <c r="D128" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E128">
         <v>-3.609589249861864</v>
@@ -8231,7 +8231,7 @@
         <v>-4.112269016956628</v>
       </c>
       <c r="D129" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E129">
         <v>-3.609589249861864</v>
@@ -8281,7 +8281,7 @@
         <v>-3.54788263495192</v>
       </c>
       <c r="D130" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E130">
         <v>-3.898446708473204</v>
@@ -8331,7 +8331,7 @@
         <v>-3.48609132544005</v>
       </c>
       <c r="D131" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E131">
         <v>-3.898446708473204</v>
@@ -8381,7 +8381,7 @@
         <v>-3.518855787136733</v>
       </c>
       <c r="D132" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E132">
         <v>-3.898446708473204</v>
@@ -8431,7 +8431,7 @@
         <v>-3.550238017985075</v>
       </c>
       <c r="D133" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E133">
         <v>-3.898446708473204</v>
@@ -8481,7 +8481,7 @@
         <v>-4.300984707980247</v>
       </c>
       <c r="D134" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E134">
         <v>-3.791582878012612</v>
@@ -8531,7 +8531,7 @@
         <v>-3.728382471353138</v>
       </c>
       <c r="D135" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E135">
         <v>-4.089652052412703</v>
@@ -8581,7 +8581,7 @@
         <v>-3.672317363547791</v>
       </c>
       <c r="D136" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E136">
         <v>-4.089652052412703</v>
@@ -8631,7 +8631,7 @@
         <v>-3.704583894661299</v>
       </c>
       <c r="D137" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E137">
         <v>-4.089652052412703</v>
@@ -8681,7 +8681,7 @@
         <v>-3.735717160218051</v>
       </c>
       <c r="D138" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E138">
         <v>-4.089652052412703</v>
@@ -8731,7 +8731,7 @@
         <v>3.441688870966403</v>
       </c>
       <c r="D139" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E139">
         <v>3.651560048451251</v>
@@ -8831,7 +8831,7 @@
         <v>3.8022990056297</v>
       </c>
       <c r="D141" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E141">
         <v>3.836671882010169</v>
@@ -8881,7 +8881,7 @@
         <v>3.779869630048473</v>
       </c>
       <c r="D142" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E142">
         <v>3.98562223265952</v>
@@ -9181,7 +9181,7 @@
         <v>4.373222703065367</v>
       </c>
       <c r="D148" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E148">
         <v>4.431458212414677</v>
@@ -9231,7 +9231,7 @@
         <v>4.083529379419559</v>
       </c>
       <c r="D149" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E149">
         <v>4.233778249441884</v>
@@ -9267,7 +9267,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9281,7 +9281,7 @@
         <v>4.082413509772715</v>
       </c>
       <c r="D150" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E150">
         <v>4.233778249441884</v>
@@ -9317,7 +9317,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9331,7 +9331,7 @@
         <v>4.052868422995772</v>
       </c>
       <c r="D151" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E151">
         <v>4.233778249441884</v>
@@ -9367,7 +9367,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9381,7 +9381,7 @@
         <v>4.043984292642614</v>
       </c>
       <c r="D152" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E152">
         <v>4.233778249441884</v>
@@ -9417,7 +9417,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9431,7 +9431,7 @@
         <v>4.389563640876833</v>
       </c>
       <c r="D153" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E153">
         <v>4.179769684077565</v>
@@ -9467,7 +9467,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9481,7 +9481,7 @@
         <v>4.401546510148196</v>
       </c>
       <c r="D154" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E154">
         <v>4.411340466947465</v>
@@ -9517,7 +9517,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9531,7 +9531,7 @@
         <v>4.094971814749398</v>
       </c>
       <c r="D155" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E155">
         <v>4.264780591105191</v>
@@ -9581,7 +9581,7 @@
         <v>4.064216552539926</v>
       </c>
       <c r="D156" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E156">
         <v>4.264780591105191</v>
@@ -9631,7 +9631,7 @@
         <v>4.055253834032031</v>
       </c>
       <c r="D157" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E157">
         <v>4.264780591105191</v>
@@ -9681,7 +9681,7 @@
         <v>4.40044024149256</v>
       </c>
       <c r="D158" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E158">
         <v>4.1909134844194</v>
@@ -9731,7 +9731,7 @@
         <v>4.412706028120979</v>
       </c>
       <c r="D159" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E159">
         <v>4.40044024149256</v>
@@ -9781,7 +9781,7 @@
         <v>4.043749044780681</v>
       </c>
       <c r="D160" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E160">
         <v>4.215527927673731</v>
@@ -9831,7 +9831,7 @@
         <v>4.013415948257763</v>
       </c>
       <c r="D161" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E161">
         <v>4.215527927673731</v>
@@ -9881,7 +9881,7 @@
         <v>4.004805034488664</v>
       </c>
       <c r="D162" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E162">
         <v>4.215527927673731</v>
@@ -9931,7 +9931,7 @@
         <v>4.351750465643174</v>
       </c>
       <c r="D163" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E163">
         <v>4.141027572458107</v>
@@ -9981,7 +9981,7 @@
         <v>4.362749755211928</v>
       </c>
       <c r="D164" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E164">
         <v>4.328639196658452</v>
@@ -10031,7 +10031,7 @@
         <v>3.837290479346144</v>
       </c>
       <c r="D165" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E165">
         <v>4.04476916280097</v>
@@ -10081,7 +10081,7 @@
         <v>4.182943229511817</v>
       </c>
       <c r="D166" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E166">
         <v>3.968073337751268</v>
@@ -10181,7 +10181,7 @@
         <v>4.005765648245287</v>
       </c>
       <c r="D168" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E168">
         <v>3.78654312804322</v>
@@ -10231,7 +10231,7 @@
         <v>4.007765332737217</v>
       </c>
       <c r="D169" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E169">
         <v>3.953098876409263</v>
@@ -10281,7 +10281,7 @@
         <v>4.02454344355129</v>
       </c>
       <c r="D170" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E170">
         <v>3.953098876409263</v>
@@ -10331,7 +10331,7 @@
         <v>3.953616152889737</v>
       </c>
       <c r="D171" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E171">
         <v>3.677108955456802</v>
@@ -10381,7 +10381,7 @@
         <v>3.903905391470386</v>
       </c>
       <c r="D172" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E172">
         <v>3.812837536808245</v>
@@ -10431,7 +10431,7 @@
         <v>3.917887571538293</v>
       </c>
       <c r="D173" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E173">
         <v>3.812837536808245</v>
@@ -10481,7 +10481,7 @@
         <v>3.902034725100593</v>
       </c>
       <c r="D174" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E174">
         <v>3.623875720664222</v>
@@ -10531,7 +10531,7 @@
         <v>3.886926312984887</v>
       </c>
       <c r="D175" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E175">
         <v>3.769904630561744</v>
@@ -10581,7 +10581,7 @@
         <v>3.866005815203071</v>
       </c>
       <c r="D176" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E176">
         <v>3.769904630561744</v>
@@ -10631,7 +10631,7 @@
         <v>3.848331413478074</v>
       </c>
       <c r="D177" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E177">
         <v>3.568452652337633</v>
@@ -10681,7 +10681,7 @@
         <v>3.832050439973229</v>
       </c>
       <c r="D178" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E178">
         <v>3.65479424527226</v>
@@ -10731,7 +10731,7 @@
         <v>3.811989820543448</v>
       </c>
       <c r="D179" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E179">
         <v>3.65479424527226</v>
@@ -10781,7 +10781,7 @@
         <v>3.782176954997707</v>
       </c>
       <c r="D180" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E180">
         <v>3.500179710470706</v>
@@ -10831,7 +10831,7 @@
         <v>3.764451561002026</v>
       </c>
       <c r="D181" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E181">
         <v>3.586906482202889</v>
@@ -10881,7 +10881,7 @@
         <v>3.745450183265525</v>
       </c>
       <c r="D182" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E182">
         <v>3.586906482202889</v>
@@ -10931,7 +10931,7 @@
         <v>3.771581102618217</v>
       </c>
       <c r="D183" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E183">
         <v>3.489244544041217</v>
@@ -10981,7 +10981,7 @@
         <v>3.753624358133901</v>
       </c>
       <c r="D184" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E184">
         <v>3.576033009237036</v>
@@ -11031,7 +11031,7 @@
         <v>3.734792637422399</v>
       </c>
       <c r="D185" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E185">
         <v>3.576033009237036</v>
@@ -11081,7 +11081,7 @@
         <v>3.801691864414723</v>
       </c>
       <c r="D186" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E186">
         <v>3.520319551484772</v>
@@ -11131,7 +11131,7 @@
         <v>3.784392560144303</v>
       </c>
       <c r="D187" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E187">
         <v>3.606932699290218</v>
@@ -11181,7 +11181,7 @@
         <v>3.765078716609277</v>
       </c>
       <c r="D188" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E188">
         <v>3.606932699290218</v>
@@ -11231,7 +11231,7 @@
         <v>3.757917937598063</v>
       </c>
       <c r="D189" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E189">
         <v>3.593577848445167</v>
@@ -11281,7 +11281,7 @@
         <v>3.739662870733393</v>
       </c>
       <c r="D190" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E190">
         <v>3.562011857360458</v>
@@ -11331,7 +11331,7 @@
         <v>3.721049919767484</v>
       </c>
       <c r="D191" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E191">
         <v>3.562011857360458</v>
@@ -11381,7 +11381,7 @@
         <v>3.654060057628653</v>
       </c>
       <c r="D192" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E192">
         <v>3.486696449408235</v>
@@ -11431,7 +11431,7 @@
         <v>3.633537351463342</v>
       </c>
       <c r="D193" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E193">
         <v>3.455432810230278</v>
@@ -11481,7 +11481,7 @@
         <v>3.63416917105232</v>
       </c>
       <c r="D194" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E194">
         <v>3.680378253518446</v>
@@ -11531,7 +11531,7 @@
         <v>3.663638628212444</v>
       </c>
       <c r="D195" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E195">
         <v>3.496553872119646</v>
@@ -11581,7 +11581,7 @@
         <v>3.643325061142847</v>
       </c>
       <c r="D196" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E196">
         <v>3.515262347728926</v>
@@ -11631,7 +11631,7 @@
         <v>3.643970823338207</v>
       </c>
       <c r="D197" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E197">
         <v>3.346221676993885</v>
@@ -11731,7 +11731,7 @@
         <v>3.732518473414919</v>
       </c>
       <c r="D199" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E199">
         <v>3.567438952990316</v>
@@ -11781,7 +11781,7 @@
         <v>3.713708833096469</v>
       </c>
       <c r="D200" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E200">
         <v>3.585946905032777</v>
@@ -11831,7 +11831,7 @@
         <v>3.714454857075237</v>
       </c>
       <c r="D201" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E201">
         <v>3.415502569329999</v>
@@ -11931,7 +11931,7 @@
         <v>3.805132584430824</v>
       </c>
       <c r="D203" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E203">
         <v>3.642167011925171</v>
@@ -11981,7 +11981,7 @@
         <v>3.787908405051586</v>
       </c>
       <c r="D204" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E204">
         <v>3.660463569175736</v>
@@ -12031,7 +12031,7 @@
         <v>3.768539469929693</v>
       </c>
       <c r="D205" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E205">
         <v>3.660463569175736</v>
@@ -12081,7 +12081,7 @@
         <v>3.788760126426302</v>
       </c>
       <c r="D206" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E206">
         <v>3.488539469929694</v>
@@ -12167,7 +12167,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12181,7 +12181,7 @@
         <v>3.860377371854645</v>
       </c>
       <c r="D208" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E208">
         <v>3.699020090103688</v>
@@ -12217,7 +12217,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12231,7 +12231,7 @@
         <v>3.844359410541429</v>
       </c>
       <c r="D209" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E209">
         <v>3.717155818278784</v>
@@ -12267,7 +12267,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12281,7 +12281,7 @@
         <v>3.824105915504454</v>
       </c>
       <c r="D210" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E210">
         <v>3.717155818278784</v>
@@ -12317,7 +12317,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12331,7 +12331,7 @@
         <v>3.597834459154263</v>
       </c>
       <c r="D211" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E211">
         <v>3.522495138716523</v>
@@ -12367,7 +12367,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12381,7 +12381,7 @@
         <v>0.625943177311898</v>
       </c>
       <c r="D212" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E212">
         <v>0.1379206150209047</v>
@@ -12431,7 +12431,7 @@
         <v>0.7658867715844124</v>
       </c>
       <c r="D213" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E213">
         <v>0.1379206150209047</v>
@@ -12481,7 +12481,7 @@
         <v>0.5858867715844109</v>
       </c>
       <c r="D214" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E214">
         <v>0.1379206150209047</v>
@@ -12631,7 +12631,7 @@
         <v>0.663525902861652</v>
       </c>
       <c r="D217" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E217">
         <v>0.175066966398818</v>
@@ -12681,7 +12681,7 @@
         <v>0.5877553710930705</v>
       </c>
       <c r="D218" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E218">
         <v>0.175066966398818</v>
@@ -12731,7 +12731,7 @@
         <v>0.8023785617045647</v>
       </c>
       <c r="D219" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E219">
         <v>0.175066966398818</v>
@@ -12781,7 +12781,7 @@
         <v>0.6223785617045632</v>
       </c>
       <c r="D220" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E220">
         <v>0.175066966398818</v>
@@ -12931,7 +12931,7 @@
         <v>0.4716402043713206</v>
       </c>
       <c r="D223" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E223">
         <v>0.03601049292784353</v>
@@ -12981,7 +12981,7 @@
         <v>0.4737683280770817</v>
       </c>
       <c r="D224" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E224">
         <v>0.03601049292784353</v>
@@ -13031,7 +13031,7 @@
         <v>-0.4038754659271504</v>
       </c>
       <c r="D225" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E225">
         <v>-0.7248363937203361</v>
@@ -13081,7 +13081,7 @@
         <v>-0.3805801463088194</v>
       </c>
       <c r="D226" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E226">
         <v>-0.7248363937203361</v>
@@ -13131,7 +13131,7 @@
         <v>-0.4605801463088195</v>
       </c>
       <c r="D227" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E227">
         <v>-0.7248363937203361</v>
@@ -13181,7 +13181,7 @@
         <v>-1.654646533801483</v>
       </c>
       <c r="D228" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E228">
         <v>-1.429234276956707</v>
@@ -13217,7 +13217,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13231,7 +13231,7 @@
         <v>-1.787765390147543</v>
       </c>
       <c r="D229" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E229">
         <v>-1.429234276956707</v>
@@ -13267,7 +13267,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13281,7 +13281,7 @@
         <v>-1.544731674061682</v>
       </c>
       <c r="D230" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E230">
         <v>-1.809837684076546</v>
@@ -13331,7 +13331,7 @@
         <v>-1.469054674516903</v>
       </c>
       <c r="D231" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E231">
         <v>-1.809837684076546</v>
@@ -13381,7 +13381,7 @@
         <v>-1.543638678158672</v>
       </c>
       <c r="D232" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E232">
         <v>-1.809837684076546</v>
@@ -13431,7 +13431,7 @@
         <v>-2.073377674972123</v>
       </c>
       <c r="D233" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E233">
         <v>-1.780881696822737</v>
@@ -13481,7 +13481,7 @@
         <v>-1.652132987219185</v>
       </c>
       <c r="D234" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E234">
         <v>-1.934727966537217</v>
@@ -13531,7 +13531,7 @@
         <v>-1.649689974810006</v>
       </c>
       <c r="D235" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E235">
         <v>-1.934727966537217</v>
@@ -13581,7 +13581,7 @@
         <v>-2.180478984461589</v>
       </c>
       <c r="D236" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E236">
         <v>-1.915592959643229</v>
@@ -13631,7 +13631,7 @@
         <v>-1.737604814589712</v>
       </c>
       <c r="D237" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E237">
         <v>-2.018409182999145</v>
@@ -13681,7 +13681,7 @@
         <v>-2.26571206371097</v>
       </c>
       <c r="D238" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E238">
         <v>-1.998677305802289</v>
@@ -13731,7 +13731,7 @@
         <v>-1.819533600394442</v>
       </c>
       <c r="D239" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E239">
         <v>-2.22286478809788</v>
@@ -13781,7 +13781,7 @@
         <v>-2.347411998158703</v>
       </c>
       <c r="D240" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E240">
         <v>-2.078317578037055</v>
@@ -13831,7 +13831,7 @@
         <v>-2.415714139279594</v>
       </c>
       <c r="D241" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E241">
         <v>-2.144897816440613</v>
@@ -13881,7 +13881,7 @@
         <v>-2.436972664625649</v>
       </c>
       <c r="D242" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E242">
         <v>-2.200816202245704</v>
@@ -13931,7 +13931,7 @@
         <v>-2.516890282739048</v>
       </c>
       <c r="D243" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E243">
         <v>-2.243523300821257</v>
@@ -13981,7 +13981,7 @@
         <v>-2.522986556894401</v>
       </c>
       <c r="D244" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E244">
         <v>-2.3355828882186</v>
@@ -14031,7 +14031,7 @@
         <v>-3.131557245685132</v>
       </c>
       <c r="D245" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E245">
         <v>-3.347513294796991</v>
@@ -14081,7 +14081,7 @@
         <v>-3.047779776380045</v>
       </c>
       <c r="D246" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E246">
         <v>-3.377200086071589</v>
@@ -14131,7 +14131,7 @@
         <v>-3.069378665878359</v>
       </c>
       <c r="D247" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E247">
         <v>-3.377200086071589</v>
@@ -14181,7 +14181,7 @@
         <v>-3.163756593478626</v>
       </c>
       <c r="D248" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E248">
         <v>-3.379340932947848</v>
@@ -14231,7 +14231,7 @@
         <v>-3.07974680564689</v>
       </c>
       <c r="D249" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E249">
         <v>-3.410607490203656</v>
@@ -14281,7 +14281,7 @@
         <v>-3.102182041841141</v>
       </c>
       <c r="D250" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E250">
         <v>-3.410607490203656</v>
@@ -14331,7 +14331,7 @@
         <v>-3.524211405336349</v>
       </c>
       <c r="D251" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E251">
         <v>-3.577409447770004</v>
@@ -14381,7 +14381,7 @@
         <v>0.6985619802361995</v>
       </c>
       <c r="D252" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E252">
         <v>0.4443773057352942</v>
@@ -14431,7 +14431,7 @@
         <v>0.2116110986844824</v>
       </c>
       <c r="D253" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E253">
         <v>0.5643773057352952</v>
@@ -14481,7 +14481,7 @@
         <v>0.2545187614340296</v>
       </c>
       <c r="D254" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E254">
         <v>0.5643773057352952</v>
@@ -14531,7 +14531,7 @@
         <v>0.2430295661345721</v>
       </c>
       <c r="D255" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E255">
         <v>0.4588448916336674</v>
@@ -14581,7 +14581,7 @@
         <v>0.6450845842289681</v>
       </c>
       <c r="D256" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E256">
         <v>0.3235953889295118</v>
@@ -14681,7 +14681,7 @@
         <v>0.7941490617311544</v>
       </c>
       <c r="D258" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E258">
         <v>0.5413183118973173</v>
@@ -14731,7 +14731,7 @@
         <v>0.3097706370468654</v>
       </c>
       <c r="D259" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E259">
         <v>0.6613183118973183</v>
@@ -14781,7 +14781,7 @@
         <v>0.3533552621299467</v>
       </c>
       <c r="D260" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E260">
         <v>0.6613183118973183</v>
@@ -14831,7 +14831,7 @@
         <v>0.3410537120302486</v>
       </c>
       <c r="D261" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E261">
         <v>0.5582229621964121</v>
@@ -14881,7 +14881,7 @@
         <v>0.7515030630604631</v>
       </c>
       <c r="D262" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E262">
         <v>0.4292015129607663</v>
@@ -14981,7 +14981,7 @@
         <v>0.4166051310402512</v>
       </c>
       <c r="D264" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E264">
         <v>0.7668265845859583</v>
@@ -15031,7 +15031,7 @@
         <v>0.460926545737081</v>
       </c>
       <c r="D265" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E265">
         <v>0.7668265845859583</v>
@@ -15081,7 +15081,7 @@
         <v>0.4477408481008851</v>
       </c>
       <c r="D266" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E266">
         <v>0.6663836774945437</v>
@@ -15131,7 +15131,7 @@
         <v>0.8673263903415673</v>
       </c>
       <c r="D267" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E267">
         <v>0.5441406927053745</v>
@@ -15231,7 +15231,7 @@
         <v>0.4961745637454023</v>
       </c>
       <c r="D269" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E269">
         <v>0.8454082588161489</v>
@@ -15267,7 +15267,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15281,7 +15281,7 @@
         <v>0.5410447331505424</v>
       </c>
       <c r="D270" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E270">
         <v>0.8454082588161489</v>
@@ -15317,7 +15317,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15331,7 +15331,7 @@
         <v>0.5272005298643734</v>
       </c>
       <c r="D271" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E271">
         <v>0.7469408686746544</v>
@@ -15367,7 +15367,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15381,7 +15381,7 @@
         <v>0.953590630488117</v>
       </c>
       <c r="D272" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E272">
         <v>0.6297464272019511</v>
@@ -15417,7 +15417,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15467,7 +15467,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15481,7 +15481,7 @@
         <v>0.7398405907582468</v>
       </c>
       <c r="D274" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E274">
         <v>1.086049466183317</v>
@@ -15531,7 +15531,7 @@
         <v>0.7863912155220971</v>
       </c>
       <c r="D275" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E275">
         <v>1.086049466183317</v>
@@ -15581,7 +15581,7 @@
         <v>0.7705304658054768</v>
       </c>
       <c r="D276" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E276">
         <v>0.9936317153331773</v>
@@ -15631,7 +15631,7 @@
         <v>1.217758212877216</v>
       </c>
       <c r="D277" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E277">
         <v>0.891897463160598</v>
@@ -15731,7 +15731,7 @@
         <v>0.8404768364070323</v>
       </c>
       <c r="D279" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E279">
         <v>1.185436434299911</v>
@@ -15781,7 +15781,7 @@
         <v>0.8771704378117802</v>
       </c>
       <c r="D280" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E280">
         <v>1.185436434299911</v>
@@ -15831,7 +15831,7 @@
         <v>0.8710279028395735</v>
       </c>
       <c r="D281" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E281">
         <v>1.095517238514154</v>
@@ -15881,7 +15881,7 @@
         <v>1.326861784021968</v>
       </c>
       <c r="D282" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E282">
         <v>1.000168182617221</v>
@@ -16031,7 +16031,7 @@
         <v>0.9191467676646941</v>
       </c>
       <c r="D285" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E285">
         <v>1.263129773307477</v>
@@ -16081,7 +16081,7 @@
         <v>1.412150840530273</v>
       </c>
       <c r="D286" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E286">
         <v>1.084806177625463</v>
@@ -16181,7 +16181,7 @@
         <v>0.9146273854272415</v>
       </c>
       <c r="D288" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E288">
         <v>0.8634785090778685</v>
@@ -16231,7 +16231,7 @@
         <v>0.9881745201758667</v>
       </c>
       <c r="D289" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E289">
         <v>1.331300629580579</v>
@@ -16281,7 +16281,7 @@
         <v>1.486986445321696</v>
       </c>
       <c r="D290" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E290">
         <v>1.159070518258174</v>
@@ -16331,7 +16331,7 @@
         <v>1.384628046088775</v>
       </c>
       <c r="D291" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E291">
         <v>1.159070518258174</v>
@@ -16431,7 +16431,7 @@
         <v>1.568515655101596</v>
       </c>
       <c r="D293" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E293">
         <v>1.239977367658073</v>
@@ -16481,7 +16481,7 @@
         <v>1.463875267808676</v>
       </c>
       <c r="D294" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E294">
         <v>1.239977367658073</v>
@@ -16531,7 +16531,7 @@
         <v>0.9955922299886435</v>
       </c>
       <c r="D295" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E295">
         <v>0.9990028926204211</v>
@@ -16581,7 +16581,7 @@
         <v>1.677993157711763</v>
       </c>
       <c r="D296" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E296">
         <v>1.348619164141446</v>
@@ -16631,7 +16631,7 @@
         <v>1.570288514620596</v>
       </c>
       <c r="D297" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E297">
         <v>1.348619164141446</v>
@@ -16681,7 +16681,7 @@
         <v>1.106741144852402</v>
       </c>
       <c r="D298" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E298">
         <v>1.107784488901872</v>
@@ -16731,7 +16731,7 @@
         <v>1.742513494588377</v>
       </c>
       <c r="D299" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E299">
         <v>1.412646979362513</v>
@@ -16781,7 +16781,7 @@
         <v>1.633002938760204</v>
       </c>
       <c r="D300" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E300">
         <v>1.412646979362513</v>
@@ -16881,7 +16881,7 @@
         <v>1.805034484116738</v>
       </c>
       <c r="D302" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E302">
         <v>1.474690709428826</v>
@@ -16931,7 +16931,7 @@
         <v>1.69377397692772</v>
       </c>
       <c r="D303" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E303">
         <v>1.474690709428826</v>
@@ -16981,7 +16981,7 @@
         <v>1.722914540207936</v>
       </c>
       <c r="D304" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E304">
         <v>1.39274265286398</v>
@@ -17031,7 +17031,7 @@
         <v>1.235722033492567</v>
       </c>
       <c r="D305" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E305">
         <v>1.194518822084868</v>
@@ -17081,7 +17081,7 @@
         <v>1.870945052560478</v>
       </c>
       <c r="D306" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E306">
         <v>1.540098143762307</v>
@@ -17131,7 +17131,7 @@
         <v>1.757839720300515</v>
       </c>
       <c r="D307" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E307">
         <v>1.540098143762307</v>
@@ -17181,7 +17181,7 @@
         <v>1.785722448305086</v>
       </c>
       <c r="D308" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E308">
         <v>1.455298993906002</v>
@@ -17281,7 +17281,7 @@
         <v>1.899125582028087</v>
       </c>
       <c r="D310" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E310">
         <v>1.568063554684362</v>
@@ -17317,7 +17317,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17331,7 +17331,7 @@
         <v>1.785231481767759</v>
       </c>
       <c r="D311" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E311">
         <v>1.568063554684362</v>
@@ -17367,7 +17367,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17381,7 +17381,7 @@
         <v>1.812576413408444</v>
       </c>
       <c r="D312" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E312">
         <v>1.482045399736583</v>
@@ -17417,7 +17417,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17431,7 +17431,7 @@
         <v>1.331249636715539</v>
       </c>
       <c r="D313" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E313">
         <v>1.415762495439622</v>
@@ -17467,7 +17467,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17581,7 +17581,7 @@
         <v>1.822704074329991</v>
       </c>
       <c r="D316" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E316">
         <v>1.492132495928136</v>
@@ -17781,7 +17781,7 @@
         <v>1.844747253622594</v>
       </c>
       <c r="D320" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E320">
         <v>1.514087384782985</v>
@@ -18017,7 +18017,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18067,7 +18067,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -18081,7 +18081,7 @@
         <v>1.905060827919813</v>
       </c>
       <c r="D326" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E326">
         <v>1.574159382681151</v>
@@ -18117,7 +18117,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18167,7 +18167,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18217,7 +18217,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18267,7 +18267,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18281,7 +18281,7 @@
         <v>2.171983384191653</v>
       </c>
       <c r="D330" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E330">
         <v>2.204898359259156</v>
@@ -18431,7 +18431,7 @@
         <v>1.952914540694782</v>
       </c>
       <c r="D333" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E333">
         <v>1.62182142504447</v>
@@ -18631,7 +18631,7 @@
         <v>2.179252235816775</v>
       </c>
       <c r="D337" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E337">
         <v>2.212248088231984</v>
@@ -18781,7 +18781,7 @@
         <v>1.960486682373803</v>
       </c>
       <c r="D340" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E340">
         <v>1.629363237718101</v>
@@ -18931,7 +18931,7 @@
         <v>2.154780197587645</v>
       </c>
       <c r="D343" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E343">
         <v>2.187503760286814</v>
@@ -19081,7 +19081,7 @@
         <v>1.934993557709523</v>
       </c>
       <c r="D346" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E346">
         <v>1.603972221697336</v>
@@ -19381,7 +19381,7 @@
         <v>1.929708178794847</v>
       </c>
       <c r="D352" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E352">
         <v>1.580374956308318</v>
@@ -19431,7 +19431,7 @@
         <v>1.188709675226703</v>
       </c>
       <c r="D353" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E353">
         <v>0.9637105065777352</v>
@@ -19517,7 +19517,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19567,7 +19567,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19617,7 +19617,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19667,7 +19667,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19681,7 +19681,7 @@
         <v>1.195364511122933</v>
       </c>
       <c r="D358" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E358">
         <v>0.9294680860372049</v>
@@ -19717,7 +19717,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19931,7 +19931,7 @@
         <v>1.196880596489463</v>
       </c>
       <c r="D363" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E363">
         <v>1.117568433078354</v>
@@ -20181,7 +20181,7 @@
         <v>1.214608625915525</v>
       </c>
       <c r="D368" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E368">
         <v>1.283141571142766</v>
@@ -20381,7 +20381,7 @@
         <v>1.186887430408948</v>
       </c>
       <c r="D372" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E372">
         <v>1.285894308899635</v>
@@ -20531,7 +20531,7 @@
         <v>1.153653122665109</v>
       </c>
       <c r="D375" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E375">
         <v>1.257399888895324</v>
@@ -20617,7 +20617,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20667,7 +20667,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20781,7 +20781,7 @@
         <v>0.8759988973248651</v>
       </c>
       <c r="D380" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E380">
         <v>0.9501238499442906</v>
@@ -20831,7 +20831,7 @@
         <v>0.9307488427654169</v>
       </c>
       <c r="D381" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E381">
         <v>0.9501238499442906</v>
@@ -20981,7 +20981,7 @@
         <v>0.7617642371331348</v>
       </c>
       <c r="D384" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E384">
         <v>1.020980669197449</v>
@@ -21031,7 +21031,7 @@
         <v>0.8108619467829499</v>
       </c>
       <c r="D385" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E385">
         <v>1.020980669197449</v>
@@ -21181,7 +21181,7 @@
         <v>0.6948350874985758</v>
       </c>
       <c r="D388" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E388">
         <v>0.7907320904119164</v>
@@ -21231,7 +21231,7 @@
         <v>0.740621198598765</v>
       </c>
       <c r="D389" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E389">
         <v>0.7907320904119164</v>
@@ -21631,7 +21631,7 @@
         <v>0.6646904187964902</v>
       </c>
       <c r="D397" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E397">
         <v>0.5071832846035527</v>
@@ -21681,7 +21681,7 @@
         <v>0.7089849968098569</v>
       </c>
       <c r="D398" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E398">
         <v>0.5071832846035527</v>
@@ -21731,7 +21731,7 @@
         <v>0.6682342833905643</v>
       </c>
       <c r="D399" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E399">
         <v>0.5071832846035527</v>
@@ -21931,7 +21931,7 @@
         <v>0.7432347119479275</v>
       </c>
       <c r="D403" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E403">
         <v>0.6707453955694014</v>
@@ -21981,7 +21981,7 @@
         <v>0.7820857966962995</v>
       </c>
       <c r="D404" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E404">
         <v>0.6707453955694014</v>
@@ -22031,7 +22031,7 @@
         <v>0.7511762387887622</v>
       </c>
       <c r="D405" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E405">
         <v>0.6707453955694014</v>
@@ -22117,7 +22117,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22167,7 +22167,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22217,7 +22217,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22231,7 +22231,7 @@
         <v>0.8216522553499699</v>
       </c>
       <c r="D409" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E409">
         <v>1.394472460139291</v>
@@ -22267,7 +22267,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22281,7 +22281,7 @@
         <v>0.8629538883296561</v>
       </c>
       <c r="D410" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E410">
         <v>1.394472460139291</v>
@@ -22317,7 +22317,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22331,7 +22331,7 @@
         <v>0.8339843477719082</v>
       </c>
       <c r="D411" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E411">
         <v>1.394472460139291</v>
@@ -22367,7 +22367,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22531,7 +22531,7 @@
         <v>0.9101672579802429</v>
       </c>
       <c r="D415" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E415">
         <v>1.488980666072655</v>
@@ -22581,7 +22581,7 @@
         <v>0.9542349847921239</v>
       </c>
       <c r="D416" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E416">
         <v>1.488980666072655</v>
@@ -22631,7 +22631,7 @@
         <v>0.9274552685181989</v>
       </c>
       <c r="D417" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E417">
         <v>1.488980666072655</v>
@@ -22781,7 +22781,7 @@
         <v>0.9657431826212832</v>
       </c>
       <c r="D420" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E420">
         <v>1.548319543944599</v>
@@ -22831,7 +22831,7 @@
         <v>1.011547657078197</v>
       </c>
       <c r="D421" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E421">
         <v>1.548319543944599</v>
@@ -22881,7 +22881,7 @@
         <v>0.9861428660232558</v>
       </c>
       <c r="D422" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E422">
         <v>1.548319543944599</v>
@@ -22981,7 +22981,7 @@
         <v>0.8844661762798571</v>
       </c>
       <c r="D424" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E424">
         <v>1.461539406965473</v>
@@ -23031,7 +23031,7 @@
         <v>0.9277307442886018</v>
       </c>
       <c r="D425" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E425">
         <v>1.461539406965473</v>
@@ -23081,7 +23081,7 @@
         <v>0.9003151939621921</v>
       </c>
       <c r="D426" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E426">
         <v>1.461539406965473</v>
@@ -23131,7 +23131,7 @@
         <v>0.7931634996038204</v>
       </c>
       <c r="D427" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E427">
         <v>1.36405477822283</v>
@@ -23167,7 +23167,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23181,7 +23181,7 @@
         <v>0.8335748589664389</v>
       </c>
       <c r="D428" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E428">
         <v>1.36405477822283</v>
@@ -23217,7 +23217,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23231,7 +23231,7 @@
         <v>0.8039005184618464</v>
       </c>
       <c r="D429" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E429">
         <v>1.36405477822283</v>
@@ -23267,7 +23267,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23281,7 +23281,7 @@
         <v>0.8355917364899295</v>
       </c>
       <c r="D430" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E430">
         <v>1.409355760314769</v>
@@ -23331,7 +23331,7 @@
         <v>0.8773289782552389</v>
       </c>
       <c r="D431" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E431">
         <v>1.409355760314769</v>
@@ -23381,7 +23381,7 @@
         <v>0.8487042946527765</v>
       </c>
       <c r="D432" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E432">
         <v>1.409355760314769</v>
@@ -23467,7 +23467,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23481,7 +23481,7 @@
         <v>0.8424985093805963</v>
       </c>
       <c r="D434" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E434">
         <v>1.416730179286574</v>
@@ -23517,7 +23517,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23531,7 +23531,7 @@
         <v>0.8844515877987398</v>
       </c>
       <c r="D435" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E435">
         <v>1.416730179286574</v>
@@ -23567,7 +23567,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23581,7 +23581,7 @@
         <v>0.8559977748797696</v>
       </c>
       <c r="D436" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E436">
         <v>1.416730179286574</v>
@@ -23617,7 +23617,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23631,7 +23631,7 @@
         <v>1.3975439619608</v>
       </c>
       <c r="D437" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E437">
         <v>1.517299827158533</v>
@@ -23667,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23681,7 +23681,7 @@
         <v>0.884482412735685</v>
       </c>
       <c r="D438" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E438">
         <v>1.461556742764664</v>
@@ -23731,7 +23731,7 @@
         <v>0.927747488133674</v>
       </c>
       <c r="D439" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E439">
         <v>1.461556742764664</v>
@@ -23781,7 +23781,7 @@
         <v>0.9003323394904168</v>
       </c>
       <c r="D440" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E440">
         <v>1.461556742764664</v>
@@ -23831,7 +23831,7 @@
         <v>1.442917190847158</v>
       </c>
       <c r="D441" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E441">
         <v>1.680876518723414</v>
@@ -23881,7 +23881,7 @@
         <v>0.9079753490611466</v>
       </c>
       <c r="D442" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E442">
         <v>1.486640346653829</v>
@@ -23931,7 +23931,7 @@
         <v>0.9519745787193061</v>
       </c>
       <c r="D443" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E443">
         <v>1.486640346653829</v>
@@ -23981,7 +23981,7 @@
         <v>0.925140635532018</v>
       </c>
       <c r="D444" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E444">
         <v>1.486640346653829</v>
@@ -24031,7 +24031,7 @@
         <v>1.468306692344727</v>
       </c>
       <c r="D445" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E445">
         <v>1.705807173808378</v>
@@ -24081,7 +24081,7 @@
         <v>0.9564160406795352</v>
       </c>
       <c r="D446" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E446">
         <v>1.538360876767213</v>
@@ -24131,7 +24131,7 @@
         <v>1.00192904195077</v>
       </c>
       <c r="D447" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E447">
         <v>1.538360876767213</v>
@@ -24181,7 +24181,7 @@
         <v>0.976293501290499</v>
       </c>
       <c r="D448" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E448">
         <v>1.538360876767213</v>
@@ -24231,7 +24231,7 @@
         <v>1.520657960630226</v>
       </c>
       <c r="D449" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E449">
         <v>1.757212334835704</v>
@@ -24281,7 +24281,7 @@
         <v>1.001796159074114</v>
       </c>
       <c r="D450" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E450">
         <v>1.586813607344758</v>
@@ -24331,7 +24331,7 @@
         <v>1.04872728904518</v>
       </c>
       <c r="D451" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E451">
         <v>1.586813607344758</v>
@@ -24381,7 +24381,7 @@
         <v>1.024214433605608</v>
       </c>
       <c r="D452" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E452">
         <v>1.586813607344758</v>
@@ -24431,7 +24431,7 @@
         <v>1.569701578166034</v>
       </c>
       <c r="D453" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E453">
         <v>1.805369621934118</v>
@@ -24481,7 +24481,7 @@
         <v>1.131375070810735</v>
       </c>
       <c r="D454" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E454">
         <v>1.725166091230212</v>
@@ -24531,7 +24531,7 @@
         <v>1.182355541773569</v>
       </c>
       <c r="D455" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E455">
         <v>1.725166091230212</v>
@@ -24581,7 +24581,7 @@
         <v>1.161048414619149</v>
       </c>
       <c r="D456" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E456">
         <v>1.725166091230212</v>
@@ -24631,7 +24631,7 @@
         <v>1.709741287464726</v>
       </c>
       <c r="D457" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E457">
         <v>1.942878493112953</v>
@@ -24681,7 +24681,7 @@
         <v>1.720982982903215</v>
       </c>
       <c r="D458" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E458">
         <v>1.513336012736406</v>
@@ -24731,7 +24731,7 @@
         <v>1.281563945976974</v>
       </c>
       <c r="D459" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E459">
         <v>1.885524004819166</v>
@@ -24767,7 +24767,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24781,7 +24781,7 @@
         <v>1.337237819288754</v>
       </c>
       <c r="D460" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E460">
         <v>1.885524004819166</v>
@@ -24817,7 +24817,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24831,7 +24831,7 @@
         <v>1.319646302327247</v>
       </c>
       <c r="D461" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E461">
         <v>1.885524004819166</v>
@@ -24867,7 +24867,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24881,7 +24881,7 @@
         <v>1.87205478536574</v>
       </c>
       <c r="D462" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E462">
         <v>2.102258614545877</v>
@@ -24917,7 +24917,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24967,7 +24967,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24981,7 +24981,7 @@
         <v>1.349426747936501</v>
       </c>
       <c r="D464" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E464">
         <v>1.957981683994701</v>
@@ -25031,7 +25031,7 @@
         <v>1.407221333809515</v>
       </c>
       <c r="D465" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E465">
         <v>1.957981683994701</v>
@@ -25081,7 +25081,7 @@
         <v>1.391308714292319</v>
       </c>
       <c r="D466" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E466">
         <v>1.957981683994701</v>
@@ -25131,7 +25131,7 @@
         <v>1.945396094775123</v>
       </c>
       <c r="D467" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E467">
         <v>2.174274478604488</v>
@@ -25181,7 +25181,7 @@
         <v>1.944997010575388</v>
       </c>
       <c r="D468" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E468">
         <v>1.762411421355811</v>
@@ -25231,7 +25231,7 @@
         <v>1.948704215965599</v>
       </c>
       <c r="D469" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E469">
         <v>1.762411421355811</v>
@@ -25281,7 +25281,7 @@
         <v>1.477021972447642</v>
       </c>
       <c r="D470" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E470">
         <v>2.094216168498784</v>
@@ -25317,7 +25317,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25331,7 +25331,7 @@
         <v>1.53880390908663</v>
       </c>
       <c r="D471" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E471">
         <v>2.094216168498784</v>
@@ -25367,7 +25367,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25381,7 +25381,7 @@
         <v>1.526047942259163</v>
       </c>
       <c r="D472" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E472">
         <v>2.094216168498784</v>
@@ -25417,7 +25417,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25431,7 +25431,7 @@
         <v>2.083291975431695</v>
       </c>
       <c r="D473" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E473">
         <v>2.309678265032328</v>
@@ -25467,7 +25467,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25481,7 +25481,7 @@
         <v>2.076081167006756</v>
       </c>
       <c r="D474" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E474">
         <v>1.963341812553087</v>
@@ -25517,7 +25517,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25531,7 +25531,7 @@
         <v>2.080619070473213</v>
       </c>
       <c r="D475" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E475">
         <v>1.963341812553087</v>
@@ -25567,7 +25567,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25581,7 +25581,7 @@
         <v>1.550026715673766</v>
       </c>
       <c r="D476" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E476">
         <v>2.172163941214178</v>
@@ -25617,7 +25617,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25631,7 +25631,7 @@
         <v>1.614090050538571</v>
       </c>
       <c r="D477" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E477">
         <v>2.172163941214178</v>
@@ -25667,7 +25667,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25681,7 +25681,7 @@
         <v>1.603140190639875</v>
       </c>
       <c r="D478" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E478">
         <v>2.172163941214178</v>
@@ -25717,7 +25717,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25767,7 +25767,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25817,7 +25817,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25867,7 +25867,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25881,7 +25881,7 @@
         <v>1.623258385611686</v>
       </c>
       <c r="D482" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E482">
         <v>2.25035400547081</v>
@@ -25931,7 +25931,7 @@
         <v>1.68961021016205</v>
       </c>
       <c r="D483" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E483">
         <v>2.25035400547081</v>
@@ -25981,7 +25981,7 @@
         <v>1.680472071264423</v>
       </c>
       <c r="D484" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E484">
         <v>2.25035400547081</v>
@@ -26231,7 +26231,7 @@
         <v>1.762765525787095</v>
       </c>
       <c r="D489" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E489">
         <v>2.399306941595595</v>
@@ -26267,7 +26267,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26281,7 +26281,7 @@
         <v>1.83347694846794</v>
       </c>
       <c r="D490" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E490">
         <v>2.399306941595595</v>
@@ -26317,7 +26317,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26331,7 +26331,7 @@
         <v>1.827790158090278</v>
       </c>
       <c r="D491" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E491">
         <v>2.399306941595595</v>
@@ -26367,7 +26367,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26381,7 +26381,7 @@
         <v>2.392103367712614</v>
       </c>
       <c r="D492" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E492">
         <v>2.445799092797729</v>
@@ -26417,7 +26417,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26431,7 +26431,7 @@
         <v>2.418595518914747</v>
       </c>
       <c r="D493" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E493">
         <v>2.445799092797729</v>
@@ -26467,7 +26467,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26481,7 +26481,7 @@
         <v>1.833848033537286</v>
       </c>
       <c r="D494" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E494">
         <v>2.475202327474705</v>
@@ -26531,7 +26531,7 @@
         <v>1.90285254583169</v>
       </c>
       <c r="D495" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E495">
         <v>2.475202327474705</v>
@@ -26581,7 +26581,7 @@
         <v>2.468924307078055</v>
       </c>
       <c r="D496" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E496">
         <v>2.423641774387</v>
@@ -26631,7 +26631,7 @@
         <v>2.492269576426664</v>
       </c>
       <c r="D497" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E497">
         <v>2.423641774387</v>
@@ -26681,7 +26681,7 @@
         <v>1.851549056007959</v>
       </c>
       <c r="D498" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E498">
         <v>2.494101856675164</v>
@@ -26717,7 +26717,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26731,7 +26731,7 @@
         <v>1.92154464117507</v>
       </c>
       <c r="D499" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E499">
         <v>2.494101856675164</v>
@@ -26767,7 +26767,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26781,7 +26781,7 @@
         <v>2.488054318341933</v>
       </c>
       <c r="D500" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E500">
         <v>2.382011194841591</v>
@@ -26817,7 +26817,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26831,7 +26831,7 @@
         <v>2.510615948674913</v>
       </c>
       <c r="D501" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E501">
         <v>2.382011194841591</v>
@@ -26867,7 +26867,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26881,7 +26881,7 @@
         <v>1.864147259392827</v>
       </c>
       <c r="D502" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E502">
         <v>2.507553063414217</v>
@@ -26931,7 +26931,7 @@
         <v>1.934848212718206</v>
       </c>
       <c r="D503" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E503">
         <v>2.507553063414217</v>
@@ -26981,7 +26981,7 @@
         <v>2.501669564187559</v>
       </c>
       <c r="D504" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E504">
         <v>2.253673461558189</v>
@@ -27031,7 +27031,7 @@
         <v>2.523673461558189</v>
       </c>
       <c r="D505" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E505">
         <v>2.253673461558189</v>
@@ -27081,7 +27081,7 @@
         <v>1.945845237918145</v>
       </c>
       <c r="D506" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E506">
         <v>2.594782675902186</v>
@@ -27131,7 +27131,7 @@
         <v>2.022277901603086</v>
       </c>
       <c r="D507" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E507">
         <v>2.594782675902186</v>
@@ -27181,7 +27181,7 @@
         <v>2.021120427020333</v>
       </c>
       <c r="D508" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E508">
         <v>2.594782675902186</v>
@@ -27231,7 +27231,7 @@
         <v>2.589962952437578</v>
       </c>
       <c r="D509" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E509">
         <v>2.297723818642469</v>
@@ -27281,7 +27281,7 @@
         <v>2.608350012217243</v>
       </c>
       <c r="D510" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E510">
         <v>2.297723818642469</v>
@@ -27331,7 +27331,7 @@
         <v>2.266279845688224</v>
       </c>
       <c r="D511" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E511">
         <v>2.483614796034592</v>
@@ -27381,7 +27381,7 @@
         <v>2.307068900485583</v>
       </c>
       <c r="D512" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E512">
         <v>2.574468278923365</v>
@@ -27431,7 +27431,7 @@
         <v>2.687922383374356</v>
       </c>
       <c r="D513" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E513">
         <v>2.779436064877657</v>
@@ -27481,7 +27481,7 @@
         <v>2.719073751524686</v>
       </c>
       <c r="D514" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E514">
         <v>2.779436064877657</v>
@@ -27531,7 +27531,7 @@
         <v>2.661312059733931</v>
       </c>
       <c r="D515" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E515">
         <v>2.452036686439876</v>
@@ -27581,7 +27581,7 @@
         <v>2.178065180993424</v>
       </c>
       <c r="D516" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E516">
         <v>2.397102519605832</v>
@@ -27631,7 +27631,7 @@
         <v>2.220092336347903</v>
       </c>
       <c r="D517" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E517">
         <v>2.493217929862364</v>
@@ -27681,7 +27681,7 @@
         <v>2.606207746604436</v>
       </c>
       <c r="D518" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E518">
         <v>2.696173802411337</v>
@@ -27731,7 +27731,7 @@
         <v>2.637204352185126</v>
       </c>
       <c r="D519" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E519">
         <v>2.696173802411337</v>
@@ -27781,7 +27781,7 @@
         <v>2.575109308444452</v>
       </c>
       <c r="D520" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E520">
         <v>2.363048208896876</v>
@@ -27831,7 +27831,7 @@
         <v>2.12088326409676</v>
       </c>
       <c r="D521" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E521">
         <v>2.286141940050999</v>
@@ -27881,7 +27881,7 @@
         <v>2.130930583414695</v>
       </c>
       <c r="D522" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E522">
         <v>2.389006294323388</v>
@@ -27931,7 +27931,7 @@
         <v>2.501400616005236</v>
       </c>
       <c r="D523" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E523">
         <v>2.589381688278063</v>
@@ -27981,7 +27981,7 @@
         <v>2.532198723232519</v>
       </c>
       <c r="D524" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E524">
         <v>2.589381688278063</v>
@@ -28031,7 +28031,7 @@
         <v>2.464545725596433</v>
       </c>
       <c r="D525" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E525">
         <v>2.248911655687521</v>
@@ -28081,7 +28081,7 @@
         <v>2.140747071531653</v>
       </c>
       <c r="D526" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E526">
         <v>1.952012635521896</v>
@@ -28117,7 +28117,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28131,7 +28131,7 @@
         <v>2.120862122803493</v>
       </c>
       <c r="D527" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E527">
         <v>1.952012635521896</v>
@@ -28167,7 +28167,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28217,7 +28217,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28231,7 +28231,7 @@
         <v>2.111322327890854</v>
       </c>
       <c r="D529" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E529">
         <v>1.971667481706374</v>
@@ -28267,7 +28267,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28281,7 +28281,7 @@
         <v>2.100113320360155</v>
       </c>
       <c r="D530" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E530">
         <v>1.93087160618927</v>
@@ -28381,7 +28381,7 @@
         <v>2.090416634691801</v>
       </c>
       <c r="D532" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E532">
         <v>1.950644120440534</v>
@@ -28431,7 +28431,7 @@
         <v>1.821174920520916</v>
       </c>
       <c r="D533" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E533">
         <v>1.870719949023447</v>
@@ -28481,7 +28481,7 @@
         <v>3.677672300021996</v>
       </c>
       <c r="D534" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E534">
         <v>3.541994244446075</v>
@@ -29081,7 +29081,7 @@
         <v>3.978801242489368</v>
       </c>
       <c r="D546" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E546">
         <v>4.001638601163368</v>
@@ -29131,7 +29131,7 @@
         <v>3.972496123834499</v>
       </c>
       <c r="D547" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E547">
         <v>4.001638601163368</v>
@@ -29181,7 +29181,7 @@
         <v>3.880251497171022</v>
       </c>
       <c r="D548" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E548">
         <v>4.001638601163368</v>
@@ -29481,7 +29481,7 @@
         <v>4.022199580117016</v>
       </c>
       <c r="D554" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E554">
         <v>4.091206258231424</v>
@@ -29531,7 +29531,7 @@
         <v>4.065709597288629</v>
       </c>
       <c r="D555" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E555">
         <v>4.091206258231424</v>
@@ -29581,7 +29581,7 @@
         <v>4.074716275403038</v>
       </c>
       <c r="D556" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E556">
         <v>4.091206258231424</v>
@@ -29981,7 +29981,7 @@
         <v>4.048036218160957</v>
       </c>
       <c r="D564" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E564">
         <v>4.122590316821391</v>
@@ -30031,7 +30031,7 @@
         <v>4.091698514142259</v>
       </c>
       <c r="D565" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E565">
         <v>4.122590316821391</v>
@@ -30081,7 +30081,7 @@
         <v>4.100806711463127</v>
       </c>
       <c r="D566" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E566">
         <v>4.122590316821391</v>
@@ -30417,7 +30417,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30467,7 +30467,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30517,7 +30517,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30567,7 +30567,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30617,7 +30617,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30667,7 +30667,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -30781,7 +30781,7 @@
         <v>3.994175842561082</v>
       </c>
       <c r="D580" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E580">
         <v>3.987624320511637</v>
@@ -30831,7 +30831,7 @@
         <v>4.031968972954489</v>
       </c>
       <c r="D581" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E581">
         <v>3.987624320511637</v>
@@ -30881,7 +30881,7 @@
         <v>4.029762103347897</v>
       </c>
       <c r="D582" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E582">
         <v>3.987624320511637</v>
@@ -31031,7 +31031,7 @@
         <v>3.974502457741278</v>
       </c>
       <c r="D585" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E585">
         <v>4.02356250952716</v>
@@ -31081,7 +31081,7 @@
         <v>4.00977951012228</v>
       </c>
       <c r="D586" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E586">
         <v>4.02356250952716</v>
@@ -31381,7 +31381,7 @@
         <v>3.831405330516851</v>
       </c>
       <c r="D592" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E592">
         <v>3.850567996970952</v>
@@ -31431,7 +31431,7 @@
         <v>3.880964530341485</v>
       </c>
       <c r="D593" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E593">
         <v>3.850567996970952</v>
@@ -31617,7 +31617,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -31667,7 +31667,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -32381,7 +32381,7 @@
         <v>3.560372125976119</v>
       </c>
       <c r="D612" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E612">
         <v>3.5580450644216</v>
@@ -32581,7 +32581,7 @@
         <v>3.537985937044418</v>
       </c>
       <c r="D616" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E616">
         <v>3.543795194274905</v>
@@ -33081,7 +33081,7 @@
         <v>3.513407764343196</v>
       </c>
       <c r="D626" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E626">
         <v>3.432185734163389</v>
@@ -34231,7 +34231,7 @@
         <v>3.300340269867909</v>
       </c>
       <c r="D649" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E649">
         <v>3.32717886940423</v>
@@ -34281,7 +34281,7 @@
         <v>3.355120178326529</v>
       </c>
       <c r="D650" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E650">
         <v>3.32717886940423</v>
@@ -34331,7 +34331,7 @@
         <v>3.319715551327793</v>
       </c>
       <c r="D651" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E651">
         <v>3.32717886940423</v>
@@ -34531,7 +34531,7 @@
         <v>3.177869947980192</v>
       </c>
       <c r="D655" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E655">
         <v>3.00684994632877</v>
@@ -34581,7 +34581,7 @@
         <v>3.163573279753848</v>
       </c>
       <c r="D656" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E656">
         <v>3.00684994632877</v>
@@ -34631,7 +34631,7 @@
         <v>3.116679946053533</v>
       </c>
       <c r="D657" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E657">
         <v>3.00684994632877</v>
@@ -34731,7 +34731,7 @@
         <v>3.087400375663595</v>
       </c>
       <c r="D659" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E659">
         <v>3.241716253711907</v>
@@ -34781,7 +34781,7 @@
         <v>3.081905443957313</v>
       </c>
       <c r="D660" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E660">
         <v>2.925042268347651</v>
@@ -34831,7 +34831,7 @@
         <v>3.034452741518665</v>
       </c>
       <c r="D661" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E661">
         <v>2.925042268347651</v>
@@ -34931,7 +34931,7 @@
         <v>2.989312133043864</v>
       </c>
       <c r="D663" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E663">
         <v>2.907291204027289</v>
@@ -34981,7 +34981,7 @@
         <v>2.476500577738507</v>
       </c>
       <c r="D664" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E664">
         <v>2.193477149265671</v>
@@ -35031,7 +35031,7 @@
         <v>2.451590863540431</v>
       </c>
       <c r="D665" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E665">
         <v>2.193477149265671</v>
@@ -35081,7 +35081,7 @@
         <v>4.277467356934507</v>
       </c>
       <c r="D666" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E666">
         <v>4.250019035921865</v>
@@ -35131,7 +35131,7 @@
         <v>4.312388090974894</v>
       </c>
       <c r="D667" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E667">
         <v>4.250019035921865</v>
@@ -35181,7 +35181,7 @@
         <v>4.328265072623884</v>
       </c>
       <c r="D668" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E668">
         <v>4.250019035921865</v>
@@ -35231,7 +35231,7 @@
         <v>4.111896806998631</v>
       </c>
       <c r="D669" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E669">
         <v>4.346549444666274</v>
@@ -35281,7 +35281,7 @@
         <v>4.117244169330988</v>
       </c>
       <c r="D670" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E670">
         <v>4.346549444666274</v>
@@ -35331,7 +35331,7 @@
         <v>3.834254835686777</v>
       </c>
       <c r="D671" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E671">
         <v>4.016549444666274</v>
@@ -35381,7 +35381,7 @@
         <v>3.867454604316342</v>
       </c>
       <c r="D672" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E672">
         <v>3.899538778310484</v>
@@ -35431,7 +35431,7 @@
         <v>3.847454604316343</v>
       </c>
       <c r="D673" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E673">
         <v>3.899538778310484</v>
@@ -35481,7 +35481,7 @@
         <v>4.09540978178439</v>
       </c>
       <c r="D674" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E674">
         <v>4.330013928201403</v>
@@ -35531,7 +35531,7 @@
         <v>4.100805635367377</v>
       </c>
       <c r="D675" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E675">
         <v>4.330013928201403</v>
@@ -35581,7 +35581,7 @@
         <v>3.816701002958673</v>
       </c>
       <c r="D676" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E676">
         <v>4.000013928201403</v>
@@ -35631,7 +35631,7 @@
         <v>3.851743439112183</v>
       </c>
       <c r="D677" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E677">
         <v>3.891097828525042</v>
@@ -35681,7 +35681,7 @@
         <v>3.831743439112183</v>
       </c>
       <c r="D678" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E678">
         <v>3.891097828525042</v>
@@ -35781,7 +35781,7 @@
         <v>3.072514803912405</v>
       </c>
       <c r="D680" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E680">
         <v>3.774449448295682</v>
@@ -35831,7 +35831,7 @@
         <v>2.371533691899383</v>
       </c>
       <c r="D681" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E681">
         <v>2.931507151748597</v>
@@ -35881,7 +35881,7 @@
         <v>3.00124175024074</v>
       </c>
       <c r="D682" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E682">
         <v>3.689569720741245</v>
@@ -35931,7 +35931,7 @@
         <v>2.318595131284202</v>
       </c>
       <c r="D683" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E683">
         <v>2.868371291570359</v>
@@ -35981,7 +35981,7 @@
         <v>2.936132894431933</v>
       </c>
       <c r="D684" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E684">
         <v>3.612030992459847</v>
@@ -36031,7 +36031,7 @@
         <v>2.879002435988074</v>
       </c>
       <c r="D685" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E685">
         <v>3.543993810131251</v>
@@ -36081,7 +36081,7 @@
         <v>3.039849598930484</v>
       </c>
       <c r="D686" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E686">
         <v>3.542642379679147</v>
@@ -36131,7 +36131,7 @@
         <v>2.977447192513372</v>
       </c>
       <c r="D687" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E687">
         <v>2.899058823529414</v>
@@ -36181,7 +36181,7 @@
         <v>3.042101740294511</v>
       </c>
       <c r="D688" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E688">
         <v>3.545002623828647</v>
@@ -36281,7 +36281,7 @@
         <v>3.050868993661444</v>
       </c>
       <c r="D690" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E690">
         <v>3.554190705357193</v>
@@ -36431,7 +36431,7 @@
         <v>3.089396271713036</v>
       </c>
       <c r="D693" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E693">
         <v>3.594567292755261</v>
@@ -36481,7 +36481,7 @@
         <v>3.027786612060444</v>
       </c>
       <c r="D694" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E694">
         <v>3.145566633714636</v>
@@ -36531,7 +36531,7 @@
         <v>2.996371463540931</v>
       </c>
       <c r="D695" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E695">
         <v>3.145566633714636</v>
@@ -36581,7 +36581,7 @@
         <v>2.416022659343419</v>
       </c>
       <c r="D696" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E696">
         <v>2.867912855598218</v>
@@ -36631,7 +36631,7 @@
         <v>3.105522877654162</v>
       </c>
       <c r="D697" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E697">
         <v>3.611467975781562</v>
@@ -36681,7 +36681,7 @@
         <v>3.044171243696629</v>
       </c>
       <c r="D698" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E698">
         <v>3.05430849837813</v>
@@ -36731,7 +36731,7 @@
         <v>3.083632681399362</v>
       </c>
       <c r="D699" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E699">
         <v>3.05430849837813</v>
@@ -36781,7 +36781,7 @@
         <v>2.442409140573988</v>
       </c>
       <c r="D700" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E700">
         <v>2.897644102055196</v>
@@ -36831,7 +36831,7 @@
         <v>3.140364182095934</v>
       </c>
       <c r="D701" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E701">
         <v>3.647981662836538</v>
@@ -36881,7 +36881,7 @@
         <v>3.079570009009469</v>
       </c>
       <c r="D702" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E702">
         <v>2.916452842425499</v>
@@ -36931,7 +36931,7 @@
         <v>3.115129220614724</v>
       </c>
       <c r="D703" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E703">
         <v>2.916452842425499</v>
@@ -36981,7 +36981,7 @@
         <v>2.506084679240175</v>
       </c>
       <c r="D704" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E704">
         <v>2.946342336667283</v>
@@ -37031,7 +37031,7 @@
         <v>2.485628823792214</v>
       </c>
       <c r="D705" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E705">
         <v>2.946342336667283</v>
@@ -37081,7 +37081,7 @@
         <v>3.197432425781973</v>
       </c>
       <c r="D706" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E706">
         <v>3.707789182219507</v>
@@ -37131,7 +37131,7 @@
         <v>3.137551344594485</v>
       </c>
       <c r="D707" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E707">
         <v>2.906599994094392</v>
@@ -37181,7 +37181,7 @@
         <v>3.166718912906903</v>
       </c>
       <c r="D708" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E708">
         <v>2.906599994094392</v>
@@ -37231,7 +37231,7 @@
         <v>2.548771137606324</v>
       </c>
       <c r="D709" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E709">
         <v>3.017488605753604</v>
@@ -37281,7 +37281,7 @@
         <v>3.280806959867506</v>
       </c>
       <c r="D710" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E710">
         <v>3.795165693941145</v>
@@ -37331,7 +37331,7 @@
         <v>3.222259871225385</v>
       </c>
       <c r="D711" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E711">
         <v>2.962089491720224</v>
@@ -37381,7 +37381,7 @@
         <v>3.242089491720225</v>
       </c>
       <c r="D712" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E712">
         <v>2.962089491720224</v>
@@ -37431,7 +37431,7 @@
         <v>2.653191076884793</v>
       </c>
       <c r="D713" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E713">
         <v>3.092218373582619</v>
@@ -37481,7 +37481,7 @@
         <v>3.368380906542133</v>
       </c>
       <c r="D714" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E714">
         <v>3.886943190056155</v>
@@ -37531,7 +37531,7 @@
         <v>3.311235001046807</v>
       </c>
       <c r="D715" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E715">
         <v>2.886023832922186</v>
@@ -37581,7 +37581,7 @@
         <v>3.321256339514088</v>
       </c>
       <c r="D716" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E716">
         <v>2.886023832922186</v>
@@ -37631,7 +37631,7 @@
         <v>2.738191997996943</v>
       </c>
       <c r="D717" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E717">
         <v>3.189362283425077</v>
@@ -37681,7 +37681,7 @@
         <v>3.482221425888762</v>
       </c>
       <c r="D718" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E718">
         <v>4.006248054331422</v>
@@ -37731,7 +37731,7 @@
         <v>3.426896968702983</v>
       </c>
       <c r="D719" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E719">
         <v>2.985596340510704</v>
@@ -37781,7 +37781,7 @@
         <v>3.424168169003441</v>
       </c>
       <c r="D720" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E720">
         <v>2.985596340510704</v>
@@ -37831,7 +37831,7 @@
         <v>2.804657363903828</v>
       </c>
       <c r="D721" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E721">
         <v>3.265322701604374</v>
@@ -37881,7 +37881,7 @@
         <v>3.571237540942626</v>
       </c>
       <c r="D722" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E722">
         <v>4.099536942907871</v>
@@ -37931,7 +37931,7 @@
         <v>3.517337341597708</v>
       </c>
       <c r="D723" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E723">
         <v>3.063455769144483</v>
@@ -37981,7 +37981,7 @@
         <v>3.504638737012133</v>
       </c>
       <c r="D724" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E724">
         <v>3.063455769144483</v>
@@ -38031,7 +38031,7 @@
         <v>0.5561171847256032</v>
       </c>
       <c r="D725" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E725">
         <v>0.4330335026282048</v>
@@ -38081,7 +38081,7 @@
         <v>0.5838703236021816</v>
       </c>
       <c r="D726" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E726">
         <v>0.4330335026282048</v>
@@ -38231,7 +38231,7 @@
         <v>0.551213907254529</v>
       </c>
       <c r="D729" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E729">
         <v>0.4281448182448422</v>
@@ -38281,7 +38281,7 @@
         <v>0.5788357083417033</v>
       </c>
       <c r="D730" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E730">
         <v>0.4281448182448422</v>
@@ -38431,7 +38431,7 @@
         <v>0.5518269121620083</v>
       </c>
       <c r="D733" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E733">
         <v>0.4287559987329539</v>
@@ -38481,7 +38481,7 @@
         <v>0.5794651330234899</v>
       </c>
       <c r="D734" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E734">
         <v>0.4287559987329539</v>
@@ -38631,7 +38631,7 @@
         <v>0.555190648483161</v>
       </c>
       <c r="D737" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E737">
         <v>0.4321097239341025</v>
@@ -38681,7 +38681,7 @@
         <v>0.5829189694246733</v>
       </c>
       <c r="D738" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E738">
         <v>0.4321097239341025</v>
@@ -38831,7 +38831,7 @@
         <v>0.5690756953603548</v>
       </c>
       <c r="D741" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E741">
         <v>0.4459534462670192</v>
@@ -38881,7 +38881,7 @@
         <v>0.5971759372003635</v>
       </c>
       <c r="D742" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E742">
         <v>0.4459534462670192</v>
@@ -39031,7 +39031,7 @@
         <v>0.5772648724003702</v>
       </c>
       <c r="D745" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E745">
         <v>0.4541182507563208</v>
@@ -39081,7 +39081,7 @@
         <v>0.6055844671968078</v>
       </c>
       <c r="D746" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E746">
         <v>0.4541182507563208</v>
@@ -39231,7 +39231,7 @@
         <v>0.5864399744245681</v>
       </c>
       <c r="D749" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E749">
         <v>0.4632660459292559</v>
@@ -39281,7 +39281,7 @@
         <v>0.6150053308823686</v>
       </c>
       <c r="D750" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E750">
         <v>0.4632660459292559</v>
@@ -39431,7 +39431,7 @@
         <v>0.595932369726385</v>
       </c>
       <c r="D753" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E753">
         <v>0.4727301900545786</v>
@@ -39481,7 +39481,7 @@
         <v>0.6247519867726261</v>
       </c>
       <c r="D754" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E754">
         <v>0.4727301900545786</v>
@@ -39631,7 +39631,7 @@
         <v>0.608430208081792</v>
       </c>
       <c r="D757" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E757">
         <v>0.4851908324625001</v>
@@ -39681,7 +39681,7 @@
         <v>0.637584588655411</v>
       </c>
       <c r="D758" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E758">
         <v>0.4851908324625001</v>
@@ -39831,7 +39831,7 @@
         <v>0.6487552402128216</v>
       </c>
       <c r="D761" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E761">
         <v>0.496037697018247</v>
@@ -39981,7 +39981,7 @@
         <v>0.660243576041168</v>
       </c>
       <c r="D764" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E764">
         <v>0.5071930376051919</v>
@@ -40181,7 +40181,7 @@
         <v>0.6200014950680988</v>
       </c>
       <c r="D768" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E768">
         <v>0.5032178605940176</v>
@@ -40281,7 +40281,7 @@
         <v>0.6162587744088102</v>
       </c>
       <c r="D770" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E770">
         <v>0.5028669571717694</v>
@@ -40331,7 +40331,7 @@
         <v>0.6375579856807025</v>
       </c>
       <c r="D771" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E771">
         <v>0.5206716816708736</v>
@@ -40431,7 +40431,7 @@
         <v>0.6334559216463012</v>
       </c>
       <c r="D773" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E773">
         <v>0.5200127696413874</v>
@@ -40531,7 +40531,7 @@
         <v>0.6569511874884277</v>
       </c>
       <c r="D775" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E775">
         <v>0.5399514729417119</v>
@@ -41467,7 +41467,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41517,7 +41517,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41567,7 +41567,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41617,7 +41617,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41667,7 +41667,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -41931,7 +41931,7 @@
         <v>0.270836261272378</v>
       </c>
       <c r="D803" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E803">
         <v>0.09124596707246546</v>
@@ -42031,7 +42031,7 @@
         <v>0.2794126519714268</v>
       </c>
       <c r="D805" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E805">
         <v>0.06592505104991719</v>
@@ -42117,7 +42117,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42131,7 +42131,7 @@
         <v>0.1298112530385671</v>
       </c>
       <c r="D807" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E807">
         <v>0.07261882114189877</v>
@@ -42167,7 +42167,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42231,7 +42231,7 @@
         <v>0.1409299212154549</v>
       </c>
       <c r="D809" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E809">
         <v>0.08367689712163706</v>
@@ -42381,7 +42381,7 @@
         <v>0.1597535501777907</v>
       </c>
       <c r="D812" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E812">
         <v>0.1023979449997094</v>
@@ -42531,7 +42531,7 @@
         <v>0.1800760542101028</v>
       </c>
       <c r="D815" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E815">
         <v>0.122609699691246</v>
@@ -42681,7 +42681,7 @@
         <v>0.1921206757259357</v>
       </c>
       <c r="D818" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E818">
         <v>0.1345886829426881</v>
@@ -42831,7 +42831,7 @@
         <v>0.207445501992245</v>
       </c>
       <c r="D821" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E821">
         <v>0.149829995169398</v>
@@ -42981,7 +42981,7 @@
         <v>0.2264355115310135</v>
       </c>
       <c r="D824" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E824">
         <v>0.1687165169177645</v>
@@ -43131,7 +43131,7 @@
         <v>0.247602885402646</v>
       </c>
       <c r="D827" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E827">
         <v>0.189768537253312</v>
@@ -43281,7 +43281,7 @@
         <v>0.2658141232074192</v>
       </c>
       <c r="D830" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E830">
         <v>0.2078805312553342</v>
@@ -43431,7 +43431,7 @@
         <v>0.2841622296762241</v>
       </c>
       <c r="D833" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E833">
         <v>0.2261286480431108</v>
@@ -43581,7 +43581,7 @@
         <v>0.3008602884138671</v>
       </c>
       <c r="D836" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E836">
         <v>0.2427357091854532</v>
@@ -43731,7 +43731,7 @@
         <v>0.3157253050058326</v>
       </c>
       <c r="D839" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E839">
         <v>0.2575197175126123</v>
@@ -43881,7 +43881,7 @@
         <v>0.3256535453070422</v>
       </c>
       <c r="D842" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E842">
         <v>0.2673938529620443</v>
@@ -43981,7 +43981,7 @@
         <v>0.3356173056739165</v>
       </c>
       <c r="D844" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E844">
         <v>0.2773033149073001</v>
@@ -44081,7 +44081,7 @@
         <v>0.3554042853652533</v>
       </c>
       <c r="D846" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E846">
         <v>0.2969824636466409</v>
@@ -44231,7 +44231,7 @@
         <v>0.36895891007521</v>
       </c>
       <c r="D849" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E849">
         <v>0.3104632211919656</v>
@@ -44331,7 +44331,7 @@
         <v>0.3786093045418983</v>
       </c>
       <c r="D851" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E851">
         <v>0.3200610249531142</v>
@@ -44417,7 +44417,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44431,7 +44431,7 @@
         <v>0.37775626876864</v>
       </c>
       <c r="D853" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E853">
         <v>0.3192126378761673</v>
@@ -44467,7 +44467,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44531,7 +44531,7 @@
         <v>0.3789042474925317</v>
       </c>
       <c r="D855" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E855">
         <v>0.3203543605852142</v>
@@ -44631,7 +44631,7 @@
         <v>0.3814658379638036</v>
       </c>
       <c r="D857" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E857">
         <v>0.3229019914353897</v>
@@ -44731,7 +44731,7 @@
         <v>0.3806182450080593</v>
       </c>
       <c r="D859" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E859">
         <v>0.3220590175148264</v>
@@ -44831,7 +44831,7 @@
         <v>0.3721749196184598</v>
       </c>
       <c r="D861" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E861">
         <v>0.3136617047976493</v>
@@ -44931,7 +44931,7 @@
         <v>0.3561949085063132</v>
       </c>
       <c r="D863" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E863">
         <v>0.2977687782147251</v>
@@ -45031,7 +45031,7 @@
         <v>0.3203941118255811</v>
       </c>
       <c r="D865" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E865">
         <v>0.2621630812434246</v>
@@ -45131,7 +45131,7 @@
         <v>0.3042852051995242</v>
       </c>
       <c r="D867" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E867">
         <v>0.246141961574458</v>
@@ -45231,7 +45231,7 @@
         <v>0.2827161083084606</v>
       </c>
       <c r="D869" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E869">
         <v>0.2246904074457436</v>
@@ -45331,7 +45331,7 @@
         <v>0.2629830094488543</v>
       </c>
       <c r="D871" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E871">
         <v>0.2050648459096225</v>
@@ -45431,7 +45431,7 @@
         <v>0.2531682602441148</v>
       </c>
       <c r="D873" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E873">
         <v>0.195303583076571</v>
@@ -45531,7 +45531,7 @@
         <v>0.264044594240807</v>
       </c>
       <c r="D875" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E875">
         <v>0.2061206454983502</v>
@@ -45681,7 +45681,7 @@
         <v>0.2246564252284724</v>
       </c>
       <c r="D878" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E878">
         <v>0.1669471259084254</v>
@@ -45831,7 +45831,7 @@
         <v>0.1598063964288423</v>
       </c>
       <c r="D881" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E881">
         <v>0.1371622895973914</v>
@@ -45931,7 +45931,7 @@
         <v>0.011804494898219</v>
       </c>
       <c r="D883" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E883">
         <v>-0.0116461618053334</v>
@@ -46117,7 +46117,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46167,7 +46167,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46181,7 +46181,7 @@
         <v>0.1619145765582886</v>
       </c>
       <c r="D888" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E888">
         <v>0.3617858655291597</v>
@@ -46217,7 +46217,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46281,7 +46281,7 @@
         <v>0.2077085108365813</v>
       </c>
       <c r="D890" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E890">
         <v>0.4045012159904244</v>
@@ -46331,7 +46331,7 @@
         <v>1.135282743014287</v>
       </c>
       <c r="D891" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E891">
         <v>1.269330275206457</v>
@@ -46381,7 +46381,7 @@
         <v>1.309290665046315</v>
       </c>
       <c r="D892" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E892">
         <v>1.223338197238484</v>
@@ -46431,7 +46431,7 @@
         <v>1.05728794369645</v>
       </c>
       <c r="D893" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E893">
         <v>1.192699816401468</v>
@@ -46481,7 +46481,7 @@
         <v>1.284229192166463</v>
       </c>
       <c r="D894" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E894">
         <v>1.146935128518972</v>
@@ -46531,7 +46531,7 @@
         <v>1.279288249694003</v>
       </c>
       <c r="D895" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E895">
         <v>1.309288249694003</v>
@@ -46578,37 +46578,37 @@
         <v>206</v>
       </c>
       <c r="C896">
-        <v>1.490242187015885</v>
+        <v>1.481117416809536</v>
       </c>
       <c r="D896" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E896">
-        <v>1.525151612170286</v>
+        <v>1.473924255881686</v>
       </c>
       <c r="F896">
         <v>1</v>
       </c>
       <c r="G896">
-        <v>0.01106975781298412</v>
+        <v>0.01077888258319046</v>
       </c>
       <c r="H896">
-        <v>0.01069484838782972</v>
+        <v>0.01074607574411831</v>
       </c>
       <c r="I896">
-        <v>0.03490942515440132</v>
+        <v>-0.007193160927849718</v>
       </c>
       <c r="J896">
         <v>1.280683907215004</v>
       </c>
       <c r="K896">
-        <v>3.74</v>
+        <v>3.63</v>
       </c>
       <c r="L896">
-        <v>6.28</v>
+        <v>6.13</v>
       </c>
       <c r="M896">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="N896">
         <v>6.11</v>
@@ -46622,96 +46622,96 @@
     </row>
     <row r="897" spans="1:16">
       <c r="A897" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B897" t="s">
         <v>207</v>
       </c>
       <c r="C897">
-        <v>1.481117416809536</v>
+        <v>1.635010114276823</v>
       </c>
       <c r="D897" t="s">
         <v>343</v>
       </c>
       <c r="E897">
-        <v>1.525151612170286</v>
+        <v>1.369274172066662</v>
       </c>
       <c r="F897">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G897">
-        <v>0.01077888258319046</v>
+        <v>0.01090498988572318</v>
       </c>
       <c r="H897">
-        <v>0.01069484838782972</v>
+        <v>0.01119072582793334</v>
       </c>
       <c r="I897">
-        <v>0.04403419536075059</v>
+        <v>0.2657359422101608</v>
       </c>
       <c r="J897">
-        <v>1.280683907215004</v>
+        <v>1.31302829623886</v>
       </c>
       <c r="K897">
-        <v>3.63</v>
+        <v>3.53</v>
       </c>
       <c r="L897">
-        <v>6.13</v>
+        <v>6.27</v>
       </c>
       <c r="M897">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="N897">
-        <v>6.11</v>
+        <v>6.28</v>
       </c>
       <c r="O897">
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="898" spans="1:16">
       <c r="A898" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B898" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C898">
-        <v>1.635010114276823</v>
+        <v>1.363707284652937</v>
       </c>
       <c r="D898" t="s">
-        <v>206</v>
+        <v>342</v>
       </c>
       <c r="E898">
-        <v>1.369274172066662</v>
+        <v>1.356837567615325</v>
       </c>
       <c r="F898">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G898">
-        <v>0.01090498988572318</v>
+        <v>0.01089629271534706</v>
       </c>
       <c r="H898">
-        <v>0.01119072582793334</v>
+        <v>0.01086316243238468</v>
       </c>
       <c r="I898">
-        <v>0.2657359422101608</v>
+        <v>-0.006869717037611522</v>
       </c>
       <c r="J898">
         <v>1.31302829623886</v>
       </c>
       <c r="K898">
-        <v>3.53</v>
+        <v>3.63</v>
       </c>
       <c r="L898">
-        <v>6.27</v>
+        <v>6.13</v>
       </c>
       <c r="M898">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="N898">
-        <v>6.28</v>
+        <v>6.11</v>
       </c>
       <c r="O898">
         <v>1</v>
@@ -46722,151 +46722,51 @@
     </row>
     <row r="899" spans="1:16">
       <c r="A899" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B899" t="s">
         <v>207</v>
       </c>
       <c r="C899">
-        <v>1.363707284652937</v>
+        <v>1.631068392352668</v>
       </c>
       <c r="D899" t="s">
         <v>343</v>
       </c>
       <c r="E899">
-        <v>1.40935869946488</v>
+        <v>1.365097956770249</v>
       </c>
       <c r="F899">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G899">
-        <v>0.01089629271534706</v>
+        <v>0.01090893160764733</v>
       </c>
       <c r="H899">
-        <v>0.01081064130053512</v>
+        <v>0.01119490204322975</v>
       </c>
       <c r="I899">
-        <v>0.04565141481194335</v>
+        <v>0.2659704355824184</v>
       </c>
       <c r="J899">
-        <v>1.31302829623886</v>
+        <v>1.314144931344853</v>
       </c>
       <c r="K899">
-        <v>3.63</v>
+        <v>3.53</v>
       </c>
       <c r="L899">
-        <v>6.13</v>
+        <v>6.27</v>
       </c>
       <c r="M899">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="N899">
-        <v>6.11</v>
+        <v>6.28</v>
       </c>
       <c r="O899">
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="900" spans="1:16">
-      <c r="A900" s="1">
-        <v>0</v>
-      </c>
-      <c r="B900" t="s">
-        <v>208</v>
-      </c>
-      <c r="C900">
-        <v>1.631068392352668</v>
-      </c>
-      <c r="D900" t="s">
-        <v>206</v>
-      </c>
-      <c r="E900">
-        <v>1.365097956770249</v>
-      </c>
-      <c r="F900">
-        <v>-1</v>
-      </c>
-      <c r="G900">
-        <v>0.01090893160764733</v>
-      </c>
-      <c r="H900">
-        <v>0.01119490204322975</v>
-      </c>
-      <c r="I900">
-        <v>0.2659704355824184</v>
-      </c>
-      <c r="J900">
-        <v>1.314144931344853</v>
-      </c>
-      <c r="K900">
-        <v>3.53</v>
-      </c>
-      <c r="L900">
-        <v>6.27</v>
-      </c>
-      <c r="M900">
-        <v>3.74</v>
-      </c>
-      <c r="N900">
-        <v>6.28</v>
-      </c>
-      <c r="O900">
-        <v>1</v>
-      </c>
-      <c r="P900" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="901" spans="1:16">
-      <c r="A901" s="1">
-        <v>1</v>
-      </c>
-      <c r="B901" t="s">
-        <v>207</v>
-      </c>
-      <c r="C901">
-        <v>1.359653899218183</v>
-      </c>
-      <c r="D901" t="s">
-        <v>343</v>
-      </c>
-      <c r="E901">
-        <v>1.405361145785426</v>
-      </c>
-      <c r="F901">
-        <v>1</v>
-      </c>
-      <c r="G901">
-        <v>0.01090034610078182</v>
-      </c>
-      <c r="H901">
-        <v>0.01081463885421458</v>
-      </c>
-      <c r="I901">
-        <v>0.04570724656724234</v>
-      </c>
-      <c r="J901">
-        <v>1.314144931344853</v>
-      </c>
-      <c r="K901">
-        <v>3.63</v>
-      </c>
-      <c r="L901">
-        <v>6.13</v>
-      </c>
-      <c r="M901">
-        <v>3.58</v>
-      </c>
-      <c r="N901">
-        <v>6.11</v>
-      </c>
-      <c r="O901">
-        <v>1</v>
-      </c>
-      <c r="P901" t="s">
         <v>482</v>
       </c>
     </row>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2706" uniqueCount="483">
   <si>
     <t>trade_time</t>
   </si>
@@ -1045,7 +1045,7 @@
     <t>2021-08-23</t>
   </si>
   <si>
-    <t>2021-10-20</t>
+    <t>2021-10-21</t>
   </si>
   <si>
     <t>2021-10-08</t>
@@ -1820,7 +1820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P899"/>
+  <dimension ref="A1:P898"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -46584,7 +46584,7 @@
         <v>343</v>
       </c>
       <c r="E896">
-        <v>1.453924255881685</v>
+        <v>1.376731094953835</v>
       </c>
       <c r="F896">
         <v>1</v>
@@ -46593,10 +46593,10 @@
         <v>0.01077888258319046</v>
       </c>
       <c r="H896">
-        <v>0.01072607574411832</v>
+        <v>0.01062326890504616</v>
       </c>
       <c r="I896">
-        <v>-0.02719316092785018</v>
+        <v>-0.1043863218557002</v>
       </c>
       <c r="J896">
         <v>1.280683907215004</v>
@@ -46608,10 +46608,10 @@
         <v>6.13</v>
       </c>
       <c r="M896">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="N896">
-        <v>6.09</v>
+        <v>6</v>
       </c>
       <c r="O896">
         <v>1</v>
@@ -46634,7 +46634,7 @@
         <v>343</v>
       </c>
       <c r="E897">
-        <v>1.453924255881685</v>
+        <v>1.376731094953835</v>
       </c>
       <c r="F897">
         <v>1</v>
@@ -46643,10 +46643,10 @@
         <v>0.01074607574411831</v>
       </c>
       <c r="H897">
-        <v>0.01072607574411832</v>
+        <v>0.01062326890504616</v>
       </c>
       <c r="I897">
-        <v>-0.02000000000000046</v>
+        <v>-0.09719316092785046</v>
       </c>
       <c r="J897">
         <v>1.280683907215004</v>
@@ -46658,10 +46658,10 @@
         <v>6.11</v>
       </c>
       <c r="M897">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="N897">
-        <v>6.09</v>
+        <v>6</v>
       </c>
       <c r="O897">
         <v>1</v>
@@ -46717,56 +46717,6 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="899" spans="1:16">
-      <c r="A899" s="1">
-        <v>1</v>
-      </c>
-      <c r="B899" t="s">
-        <v>207</v>
-      </c>
-      <c r="C899">
-        <v>1.356837567615325</v>
-      </c>
-      <c r="D899" t="s">
-        <v>343</v>
-      </c>
-      <c r="E899">
-        <v>1.336837567615325</v>
-      </c>
-      <c r="F899">
-        <v>1</v>
-      </c>
-      <c r="G899">
-        <v>0.01086316243238468</v>
-      </c>
-      <c r="H899">
-        <v>0.01084316243238467</v>
-      </c>
-      <c r="I899">
-        <v>-0.02000000000000046</v>
-      </c>
-      <c r="J899">
-        <v>1.31302829623886</v>
-      </c>
-      <c r="K899">
-        <v>3.62</v>
-      </c>
-      <c r="L899">
-        <v>6.11</v>
-      </c>
-      <c r="M899">
-        <v>3.62</v>
-      </c>
-      <c r="N899">
-        <v>6.09</v>
-      </c>
-      <c r="O899">
-        <v>1</v>
-      </c>
-      <c r="P899" t="s">
         <v>482</v>
       </c>
     </row>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2706" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="484">
   <si>
     <t>trade_time</t>
   </si>
@@ -634,15 +634,15 @@
     <t>2021-08-20</t>
   </si>
   <si>
-    <t>2021-10-12</t>
-  </si>
-  <si>
-    <t>2021-10-19</t>
+    <t>2021-09-23</t>
   </si>
   <si>
     <t>2021-09-28</t>
   </si>
   <si>
+    <t>2021-10-21</t>
+  </si>
+  <si>
     <t>2016-08-08</t>
   </si>
   <si>
@@ -1045,12 +1045,12 @@
     <t>2021-08-23</t>
   </si>
   <si>
-    <t>2021-10-21</t>
-  </si>
-  <si>
     <t>2021-10-08</t>
   </si>
   <si>
+    <t>2021-10-25</t>
+  </si>
+  <si>
     <t>2016-07-11</t>
   </si>
   <si>
@@ -1463,6 +1463,9 @@
   </si>
   <si>
     <t>2021-09-24</t>
+  </si>
+  <si>
+    <t>2021-09-27</t>
   </si>
 </sst>
 </file>
@@ -1820,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P898"/>
+  <dimension ref="A1:P900"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -46578,40 +46581,40 @@
         <v>206</v>
       </c>
       <c r="C896">
-        <v>1.481117416809536</v>
+        <v>1.801469543304485</v>
       </c>
       <c r="D896" t="s">
         <v>343</v>
       </c>
       <c r="E896">
-        <v>1.376731094953835</v>
+        <v>1.490242187015885</v>
       </c>
       <c r="F896">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G896">
-        <v>0.01077888258319046</v>
+        <v>0.01127853045669551</v>
       </c>
       <c r="H896">
-        <v>0.01062326890504616</v>
+        <v>0.01106975781298412</v>
       </c>
       <c r="I896">
-        <v>-0.1043863218557002</v>
+        <v>0.3112273562886001</v>
       </c>
       <c r="J896">
         <v>1.280683907215004</v>
       </c>
       <c r="K896">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="L896">
-        <v>6.13</v>
+        <v>6.54</v>
       </c>
       <c r="M896">
-        <v>3.61</v>
+        <v>3.74</v>
       </c>
       <c r="N896">
-        <v>6</v>
+        <v>6.28</v>
       </c>
       <c r="O896">
         <v>1</v>
@@ -46628,40 +46631,40 @@
         <v>207</v>
       </c>
       <c r="C897">
-        <v>1.473924255881686</v>
+        <v>1.749185807531036</v>
       </c>
       <c r="D897" t="s">
         <v>343</v>
       </c>
       <c r="E897">
-        <v>1.376731094953835</v>
+        <v>1.490242187015885</v>
       </c>
       <c r="F897">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G897">
-        <v>0.01074607574411831</v>
+        <v>0.01079081419246897</v>
       </c>
       <c r="H897">
-        <v>0.01062326890504616</v>
+        <v>0.01106975781298412</v>
       </c>
       <c r="I897">
-        <v>-0.09719316092785046</v>
+        <v>0.2589436205151507</v>
       </c>
       <c r="J897">
         <v>1.280683907215004</v>
       </c>
       <c r="K897">
-        <v>3.62</v>
+        <v>3.53</v>
       </c>
       <c r="L897">
-        <v>6.11</v>
+        <v>6.27</v>
       </c>
       <c r="M897">
-        <v>3.61</v>
+        <v>3.74</v>
       </c>
       <c r="N897">
-        <v>6</v>
+        <v>6.28</v>
       </c>
       <c r="O897">
         <v>1</v>
@@ -46672,52 +46675,152 @@
     </row>
     <row r="898" spans="1:16">
       <c r="A898" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B898" t="s">
         <v>208</v>
       </c>
       <c r="C898">
-        <v>1.635010114276823</v>
+        <v>1.376731094953835</v>
       </c>
       <c r="D898" t="s">
         <v>344</v>
       </c>
       <c r="E898">
-        <v>1.369274172066662</v>
+        <v>1.362696899593085</v>
       </c>
       <c r="F898">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G898">
-        <v>0.01090498988572318</v>
+        <v>0.01062326890504616</v>
       </c>
       <c r="H898">
-        <v>0.01119072582793334</v>
+        <v>0.01073730310040692</v>
       </c>
       <c r="I898">
-        <v>0.2657359422101608</v>
+        <v>-0.01403419536075035</v>
       </c>
       <c r="J898">
+        <v>1.280683907215004</v>
+      </c>
+      <c r="K898">
+        <v>3.61</v>
+      </c>
+      <c r="L898">
+        <v>6</v>
+      </c>
+      <c r="M898">
+        <v>3.66</v>
+      </c>
+      <c r="N898">
+        <v>6.05</v>
+      </c>
+      <c r="O898">
+        <v>1</v>
+      </c>
+      <c r="P898" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="899" spans="1:16">
+      <c r="A899" s="1">
+        <v>0</v>
+      </c>
+      <c r="B899" t="s">
+        <v>208</v>
+      </c>
+      <c r="C899">
+        <v>1.259967850577714</v>
+      </c>
+      <c r="D899" t="s">
+        <v>344</v>
+      </c>
+      <c r="E899">
+        <v>1.244316435765771</v>
+      </c>
+      <c r="F899">
+        <v>1</v>
+      </c>
+      <c r="G899">
+        <v>0.01074003214942229</v>
+      </c>
+      <c r="H899">
+        <v>0.01085568356423423</v>
+      </c>
+      <c r="I899">
+        <v>-0.0156514148119431</v>
+      </c>
+      <c r="J899">
         <v>1.31302829623886</v>
       </c>
-      <c r="K898">
-        <v>3.53</v>
-      </c>
-      <c r="L898">
-        <v>6.27</v>
-      </c>
-      <c r="M898">
-        <v>3.74</v>
-      </c>
-      <c r="N898">
-        <v>6.28</v>
-      </c>
-      <c r="O898">
-        <v>1</v>
-      </c>
-      <c r="P898" t="s">
+      <c r="K899">
+        <v>3.61</v>
+      </c>
+      <c r="L899">
+        <v>6</v>
+      </c>
+      <c r="M899">
+        <v>3.66</v>
+      </c>
+      <c r="N899">
+        <v>6.05</v>
+      </c>
+      <c r="O899">
+        <v>1</v>
+      </c>
+      <c r="P899" t="s">
         <v>482</v>
+      </c>
+    </row>
+    <row r="900" spans="1:16">
+      <c r="A900" s="1">
+        <v>0</v>
+      </c>
+      <c r="B900" t="s">
+        <v>208</v>
+      </c>
+      <c r="C900">
+        <v>1.25593679784508</v>
+      </c>
+      <c r="D900" t="s">
+        <v>344</v>
+      </c>
+      <c r="E900">
+        <v>1.240229551277837</v>
+      </c>
+      <c r="F900">
+        <v>1</v>
+      </c>
+      <c r="G900">
+        <v>0.01074406320215492</v>
+      </c>
+      <c r="H900">
+        <v>0.01085977044872216</v>
+      </c>
+      <c r="I900">
+        <v>-0.01570724656724298</v>
+      </c>
+      <c r="J900">
+        <v>1.314144931344853</v>
+      </c>
+      <c r="K900">
+        <v>3.61</v>
+      </c>
+      <c r="L900">
+        <v>6</v>
+      </c>
+      <c r="M900">
+        <v>3.66</v>
+      </c>
+      <c r="N900">
+        <v>6.05</v>
+      </c>
+      <c r="O900">
+        <v>1</v>
+      </c>
+      <c r="P900" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2700" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2703" uniqueCount="484">
   <si>
     <t>trade_time</t>
   </si>
@@ -1051,7 +1051,7 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-10-27</t>
+    <t>2021-10-28</t>
   </si>
   <si>
     <t>2016-07-12</t>
@@ -1823,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P896"/>
+  <dimension ref="A1:P897"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -46437,7 +46437,7 @@
         <v>345</v>
       </c>
       <c r="E893">
-        <v>1.313924255881686</v>
+        <v>1.349185807531036</v>
       </c>
       <c r="F893">
         <v>1</v>
@@ -46446,10 +46446,10 @@
         <v>0.01062326890504616</v>
       </c>
       <c r="H893">
-        <v>0.01058607574411831</v>
+        <v>0.01039081419246896</v>
       </c>
       <c r="I893">
-        <v>-0.06280683907214968</v>
+        <v>-0.02754528742279927</v>
       </c>
       <c r="J893">
         <v>1.280683907215004</v>
@@ -46461,10 +46461,10 @@
         <v>6</v>
       </c>
       <c r="M893">
-        <v>3.62</v>
+        <v>3.53</v>
       </c>
       <c r="N893">
-        <v>5.95</v>
+        <v>5.87</v>
       </c>
       <c r="O893">
         <v>1</v>
@@ -46487,7 +46487,7 @@
         <v>345</v>
       </c>
       <c r="E894">
-        <v>1.196837567615325</v>
+        <v>1.235010114276824</v>
       </c>
       <c r="F894">
         <v>1</v>
@@ -46496,10 +46496,10 @@
         <v>0.01086194413015901</v>
       </c>
       <c r="H894">
-        <v>0.01070316243238468</v>
+        <v>0.01050498988572318</v>
       </c>
       <c r="I894">
-        <v>-0.001218302225669099</v>
+        <v>0.03695424443582951</v>
       </c>
       <c r="J894">
         <v>1.31302829623886</v>
@@ -46511,10 +46511,10 @@
         <v>6.03</v>
       </c>
       <c r="M894">
-        <v>3.62</v>
+        <v>3.53</v>
       </c>
       <c r="N894">
-        <v>5.95</v>
+        <v>5.87</v>
       </c>
       <c r="O894">
         <v>1</v>
@@ -46525,101 +46525,151 @@
     </row>
     <row r="895" spans="1:16">
       <c r="A895" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B895" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C895">
-        <v>1.19394665265094</v>
+        <v>1.201186152803382</v>
       </c>
       <c r="D895" t="s">
         <v>345</v>
       </c>
       <c r="E895">
-        <v>1.192795348531631</v>
+        <v>1.235010114276824</v>
       </c>
       <c r="F895">
         <v>1</v>
       </c>
       <c r="G895">
-        <v>0.01086605334734906</v>
+        <v>0.01083881384719662</v>
       </c>
       <c r="H895">
-        <v>0.01070720465146837</v>
+        <v>0.01050498988572318</v>
       </c>
       <c r="I895">
-        <v>-0.001151304119308527</v>
+        <v>0.03382396147344124</v>
       </c>
       <c r="J895">
-        <v>1.314144931344853</v>
+        <v>1.31302829623886</v>
       </c>
       <c r="K895">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="L895">
-        <v>6.03</v>
+        <v>6.02</v>
       </c>
       <c r="M895">
-        <v>3.62</v>
+        <v>3.53</v>
       </c>
       <c r="N895">
-        <v>5.95</v>
+        <v>5.87</v>
       </c>
       <c r="O895">
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="896" spans="1:16">
       <c r="A896" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B896" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C896">
-        <v>1.197088101964388</v>
+        <v>1.19394665265094</v>
       </c>
       <c r="D896" t="s">
         <v>345</v>
       </c>
       <c r="E896">
-        <v>1.192795348531631</v>
+        <v>1.231068392352668</v>
       </c>
       <c r="F896">
         <v>1</v>
       </c>
       <c r="G896">
-        <v>0.01084291189803561</v>
+        <v>0.01086605334734906</v>
       </c>
       <c r="H896">
-        <v>0.01070720465146837</v>
+        <v>0.01050893160764733</v>
       </c>
       <c r="I896">
-        <v>-0.004292753432756591</v>
+        <v>0.03712173970172827</v>
       </c>
       <c r="J896">
         <v>1.314144931344853</v>
       </c>
       <c r="K896">
+        <v>3.68</v>
+      </c>
+      <c r="L896">
+        <v>6.03</v>
+      </c>
+      <c r="M896">
+        <v>3.53</v>
+      </c>
+      <c r="N896">
+        <v>5.87</v>
+      </c>
+      <c r="O896">
+        <v>1</v>
+      </c>
+      <c r="P896" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="897" spans="1:16">
+      <c r="A897" s="1">
+        <v>1</v>
+      </c>
+      <c r="B897" t="s">
+        <v>210</v>
+      </c>
+      <c r="C897">
+        <v>1.197088101964388</v>
+      </c>
+      <c r="D897" t="s">
+        <v>345</v>
+      </c>
+      <c r="E897">
+        <v>1.231068392352668</v>
+      </c>
+      <c r="F897">
+        <v>1</v>
+      </c>
+      <c r="G897">
+        <v>0.01084291189803561</v>
+      </c>
+      <c r="H897">
+        <v>0.01050893160764733</v>
+      </c>
+      <c r="I897">
+        <v>0.03398029038828021</v>
+      </c>
+      <c r="J897">
+        <v>1.314144931344853</v>
+      </c>
+      <c r="K897">
         <v>3.67</v>
       </c>
-      <c r="L896">
+      <c r="L897">
         <v>6.02</v>
       </c>
-      <c r="M896">
-        <v>3.62</v>
-      </c>
-      <c r="N896">
-        <v>5.95</v>
-      </c>
-      <c r="O896">
-        <v>1</v>
-      </c>
-      <c r="P896" t="s">
+      <c r="M897">
+        <v>3.53</v>
+      </c>
+      <c r="N897">
+        <v>5.87</v>
+      </c>
+      <c r="O897">
+        <v>1</v>
+      </c>
+      <c r="P897" t="s">
         <v>483</v>
       </c>
     </row>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2676" uniqueCount="483">
   <si>
     <t>trade_time</t>
   </si>
@@ -1049,6 +1049,9 @@
   </si>
   <si>
     <t>2021-10-08</t>
+  </si>
+  <si>
+    <t>2021-11-02</t>
   </si>
   <si>
     <t>2021-11-01</t>
@@ -1914,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1964,7 +1967,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2014,7 +2017,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2064,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2114,7 +2117,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2164,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2214,7 +2217,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2264,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2314,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2364,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2414,7 +2417,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2464,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2514,7 +2517,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2564,7 +2567,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2614,7 +2617,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2664,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2714,7 +2717,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2764,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2814,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2864,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2914,7 +2917,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2964,7 +2967,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3014,7 +3017,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3064,7 +3067,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3114,7 +3117,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3164,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3214,7 +3217,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3264,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3314,7 +3317,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3364,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3414,7 +3417,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3464,7 +3467,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3514,7 +3517,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3564,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3614,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3664,7 +3667,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3714,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3764,7 +3767,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3814,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3864,7 +3867,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3914,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4064,7 +4067,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4114,7 +4117,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4264,7 +4267,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4314,7 +4317,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4364,7 +4367,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4414,7 +4417,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4564,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4614,7 +4617,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4664,7 +4667,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4714,7 +4717,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4764,7 +4767,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5014,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5064,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5114,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5164,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5514,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5564,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5614,7 +5617,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5864,7 +5867,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5914,7 +5917,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5964,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6014,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6064,7 +6067,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6114,7 +6117,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6164,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6364,7 +6367,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6414,7 +6417,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6464,7 +6467,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6514,7 +6517,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6564,7 +6567,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6614,7 +6617,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6664,7 +6667,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6714,7 +6717,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6764,7 +6767,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6814,7 +6817,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6864,7 +6867,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6914,7 +6917,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6964,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7014,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7064,7 +7067,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7114,7 +7117,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7164,7 +7167,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7214,7 +7217,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7264,7 +7267,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7314,7 +7317,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7364,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7414,7 +7417,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -8014,7 +8017,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8064,7 +8067,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8114,7 +8117,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8164,7 +8167,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8214,7 +8217,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8264,7 +8267,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8314,7 +8317,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8464,7 +8467,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -9064,7 +9067,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9114,7 +9117,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9164,7 +9167,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9214,7 +9217,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9264,7 +9267,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9464,7 +9467,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9514,7 +9517,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9564,7 +9567,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9764,7 +9767,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9814,7 +9817,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9864,7 +9867,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9914,7 +9917,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9964,7 +9967,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10014,7 +10017,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10064,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10114,7 +10117,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10164,7 +10167,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10364,7 +10367,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10414,7 +10417,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10464,7 +10467,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10514,7 +10517,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10564,7 +10567,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10614,7 +10617,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10664,7 +10667,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10714,7 +10717,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10764,7 +10767,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10814,7 +10817,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10864,7 +10867,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10914,7 +10917,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11164,7 +11167,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11214,7 +11217,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11264,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11314,7 +11317,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11364,7 +11367,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11664,7 +11667,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11714,7 +11717,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11764,7 +11767,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11814,7 +11817,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11864,7 +11867,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11914,7 +11917,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11964,7 +11967,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12014,7 +12017,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12064,7 +12067,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12114,7 +12117,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12164,7 +12167,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12564,7 +12567,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12614,7 +12617,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12664,7 +12667,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12714,7 +12717,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13214,7 +13217,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13264,7 +13267,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13314,7 +13317,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13364,7 +13367,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13414,7 +13417,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13464,7 +13467,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13514,7 +13517,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13564,7 +13567,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13614,7 +13617,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13664,7 +13667,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13714,7 +13717,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13764,7 +13767,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13814,7 +13817,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13864,7 +13867,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13914,7 +13917,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13964,7 +13967,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14014,7 +14017,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14064,7 +14067,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14114,7 +14117,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14164,7 +14167,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14214,7 +14217,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14764,7 +14767,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14814,7 +14817,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14864,7 +14867,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14914,7 +14917,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14964,7 +14967,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15014,7 +15017,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15064,7 +15067,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15114,7 +15117,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15164,7 +15167,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15214,7 +15217,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15264,7 +15267,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15314,7 +15317,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15364,7 +15367,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15414,7 +15417,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15464,7 +15467,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15514,7 +15517,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15564,7 +15567,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15614,7 +15617,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15664,7 +15667,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15864,7 +15867,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15914,7 +15917,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15964,7 +15967,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -16364,7 +16367,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16414,7 +16417,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16464,7 +16467,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16514,7 +16517,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16764,7 +16767,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16814,7 +16817,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16864,7 +16867,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16914,7 +16917,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17914,7 +17917,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17964,7 +17967,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -18014,7 +18017,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18064,7 +18067,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -18114,7 +18117,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18164,7 +18167,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18214,7 +18217,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18264,7 +18267,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18314,7 +18317,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18364,7 +18367,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18414,7 +18417,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18464,7 +18467,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18514,7 +18517,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18564,7 +18567,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18614,7 +18617,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18664,7 +18667,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18714,7 +18717,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -19014,7 +19017,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19064,7 +19067,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19114,7 +19117,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19164,7 +19167,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19214,7 +19217,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19264,7 +19267,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19314,7 +19317,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19364,7 +19367,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19414,7 +19417,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19464,7 +19467,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19514,7 +19517,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19564,7 +19567,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19614,7 +19617,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19664,7 +19667,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19964,7 +19967,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20014,7 +20017,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20064,7 +20067,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20114,7 +20117,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20164,7 +20167,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20214,7 +20217,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20264,7 +20267,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20314,7 +20317,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20564,7 +20567,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20614,7 +20617,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20664,7 +20667,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20714,7 +20717,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20764,7 +20767,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20814,7 +20817,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20864,7 +20867,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20914,7 +20917,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20964,7 +20967,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21014,7 +21017,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -23164,7 +23167,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23214,7 +23217,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23264,7 +23267,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23314,7 +23317,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23364,7 +23367,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23414,7 +23417,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23464,7 +23467,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23514,7 +23517,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -26614,7 +26617,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26664,7 +26667,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26714,7 +26717,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26764,7 +26767,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26814,7 +26817,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26864,7 +26867,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26914,7 +26917,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26964,7 +26967,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27014,7 +27017,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27064,7 +27067,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27114,7 +27117,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27164,7 +27167,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27214,7 +27217,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27264,7 +27267,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27314,7 +27317,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27764,7 +27767,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27814,7 +27817,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27864,7 +27867,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27914,7 +27917,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28114,7 +28117,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28164,7 +28167,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28214,7 +28217,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28264,7 +28267,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28314,7 +28317,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28364,7 +28367,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28414,7 +28417,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28464,7 +28467,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28514,7 +28517,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28564,7 +28567,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28614,7 +28617,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28664,7 +28667,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29164,7 +29167,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29214,7 +29217,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29264,7 +29267,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29314,7 +29317,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29364,7 +29367,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29414,7 +29417,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29464,7 +29467,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29514,7 +29517,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29564,7 +29567,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29614,7 +29617,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30214,7 +30217,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30264,7 +30267,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30314,7 +30317,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30364,7 +30367,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30414,7 +30417,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30464,7 +30467,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30514,7 +30517,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30964,7 +30967,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31014,7 +31017,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31164,7 +31167,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31214,7 +31217,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31264,7 +31267,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31314,7 +31317,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31364,7 +31367,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31414,7 +31417,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -34364,7 +34367,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34414,7 +34417,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34464,7 +34467,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34514,7 +34517,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34564,7 +34567,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34614,7 +34617,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -34664,7 +34667,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34714,7 +34717,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34764,7 +34767,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34814,7 +34817,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34864,7 +34867,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34914,7 +34917,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34964,7 +34967,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35014,7 +35017,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35064,7 +35067,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35114,7 +35117,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35164,7 +35167,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35214,7 +35217,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35264,7 +35267,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35464,7 +35467,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35514,7 +35517,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35564,7 +35567,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35614,7 +35617,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35664,7 +35667,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35714,7 +35717,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35764,7 +35767,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35814,7 +35817,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35864,7 +35867,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35914,7 +35917,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35964,7 +35967,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36014,7 +36017,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36064,7 +36067,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36114,7 +36117,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36164,7 +36167,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36214,7 +36217,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36264,7 +36267,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36314,7 +36317,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36364,7 +36367,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36414,7 +36417,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36464,7 +36467,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36714,7 +36717,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36764,7 +36767,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36814,7 +36817,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36864,7 +36867,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36914,7 +36917,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36964,7 +36967,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37014,7 +37017,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37064,7 +37067,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37114,7 +37117,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37164,7 +37167,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37214,7 +37217,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37264,7 +37267,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37314,7 +37317,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37364,7 +37367,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37414,7 +37417,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37464,7 +37467,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37514,7 +37517,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37564,7 +37567,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37614,7 +37617,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37664,7 +37667,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37714,7 +37717,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37764,7 +37767,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37814,7 +37817,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37864,7 +37867,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37914,7 +37917,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37964,7 +37967,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38014,7 +38017,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38064,7 +38067,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38114,7 +38117,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38164,7 +38167,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38214,7 +38217,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38264,7 +38267,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38314,7 +38317,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38364,7 +38367,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38414,7 +38417,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38464,7 +38467,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38514,7 +38517,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38564,7 +38567,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38614,7 +38617,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38664,7 +38667,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -38714,7 +38717,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -38764,7 +38767,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -38814,7 +38817,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -38864,7 +38867,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -38914,7 +38917,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38964,7 +38967,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39014,7 +39017,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39064,7 +39067,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39264,7 +39267,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39314,7 +39317,7 @@
         <v>1</v>
       </c>
       <c r="P750" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39364,7 +39367,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39464,7 +39467,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39514,7 +39517,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39564,7 +39567,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39614,7 +39617,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39664,7 +39667,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -39714,7 +39717,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -39764,7 +39767,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -39814,7 +39817,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39864,7 +39867,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39914,7 +39917,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39964,7 +39967,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40014,7 +40017,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40064,7 +40067,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40114,7 +40117,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -40164,7 +40167,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40214,7 +40217,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40264,7 +40267,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40314,7 +40317,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40364,7 +40367,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40414,7 +40417,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40464,7 +40467,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40514,7 +40517,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40564,7 +40567,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40614,7 +40617,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40664,7 +40667,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40964,7 +40967,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41014,7 +41017,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41064,7 +41067,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41114,7 +41117,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41264,7 +41267,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41314,7 +41317,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41464,7 +41467,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41514,7 +41517,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41564,7 +41567,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41614,7 +41617,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41664,7 +41667,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -41864,7 +41867,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -41914,7 +41917,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -41964,7 +41967,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42014,7 +42017,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42064,7 +42067,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42114,7 +42117,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42164,7 +42167,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42214,7 +42217,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42264,7 +42267,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42614,7 +42617,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42664,7 +42667,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -42714,7 +42717,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -42914,7 +42917,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -42964,7 +42967,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43014,7 +43017,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43064,7 +43067,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43114,7 +43117,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43164,7 +43167,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43314,7 +43317,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43364,7 +43367,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43414,7 +43417,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43464,7 +43467,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43514,7 +43517,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43764,7 +43767,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43814,7 +43817,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43864,7 +43867,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43914,7 +43917,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44214,7 +44217,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44264,7 +44267,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44314,7 +44317,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44364,7 +44367,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44514,7 +44517,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44564,7 +44567,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44614,7 +44617,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44664,7 +44667,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -45114,7 +45117,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45164,7 +45167,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45514,7 +45517,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45564,7 +45567,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45714,7 +45717,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -45764,7 +45767,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -45814,7 +45817,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -45864,7 +45867,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -45914,7 +45917,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -45964,7 +45967,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -45981,7 +45984,7 @@
         <v>345</v>
       </c>
       <c r="E884">
-        <v>1.490413163819635</v>
+        <v>1.401992646603186</v>
       </c>
       <c r="F884">
         <v>1</v>
@@ -45990,10 +45993,10 @@
         <v>0.01062326890504616</v>
       </c>
       <c r="H884">
-        <v>0.01042958683618036</v>
+        <v>0.01041800735339681</v>
       </c>
       <c r="I884">
-        <v>0.1136820688658</v>
+        <v>0.02526155164935062</v>
       </c>
       <c r="J884">
         <v>1.280683907215004</v>
@@ -46005,16 +46008,16 @@
         <v>6</v>
       </c>
       <c r="M884">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="N884">
-        <v>5.96</v>
+        <v>5.91</v>
       </c>
       <c r="O884">
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46028,7 +46031,7 @@
         <v>1.198055869840994</v>
       </c>
       <c r="D885" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E885">
         <v>1.377531246126376</v>
@@ -46064,7 +46067,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46078,7 +46081,7 @@
         <v>1.201186152803382</v>
       </c>
       <c r="D886" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E886">
         <v>1.377531246126376</v>
@@ -46114,7 +46117,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46128,7 +46131,7 @@
         <v>1.19394665265094</v>
       </c>
       <c r="D887" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E887">
         <v>1.373634189606462</v>
@@ -46164,7 +46167,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46178,7 +46181,7 @@
         <v>1.197088101964388</v>
       </c>
       <c r="D888" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E888">
         <v>1.373634189606462</v>
@@ -46214,7 +46217,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -1051,7 +1051,7 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-11-02</t>
+    <t>2021-11-03</t>
   </si>
   <si>
     <t>2021-11-01</t>
@@ -45984,7 +45984,7 @@
         <v>345</v>
       </c>
       <c r="E884">
-        <v>1.401992646603186</v>
+        <v>1.371992646603186</v>
       </c>
       <c r="F884">
         <v>1</v>
@@ -45993,10 +45993,10 @@
         <v>0.01062326890504616</v>
       </c>
       <c r="H884">
-        <v>0.01041800735339681</v>
+        <v>0.01038800735339681</v>
       </c>
       <c r="I884">
-        <v>0.02526155164935062</v>
+        <v>-0.004738448350649627</v>
       </c>
       <c r="J884">
         <v>1.280683907215004</v>
@@ -46011,7 +46011,7 @@
         <v>3.52</v>
       </c>
       <c r="N884">
-        <v>5.91</v>
+        <v>5.88</v>
       </c>
       <c r="O884">
         <v>1</v>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -1051,7 +1051,7 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-11-08</t>
+    <t>2021-11-09</t>
   </si>
   <si>
     <t>2021-11-01</t>
@@ -45478,7 +45478,7 @@
         <v>345</v>
       </c>
       <c r="E874">
-        <v>1.513572129386736</v>
+        <v>1.507606324747486</v>
       </c>
       <c r="F874">
         <v>1</v>
@@ -45487,10 +45487,10 @@
         <v>0.01062326890504616</v>
       </c>
       <c r="H874">
-        <v>0.01060642787061326</v>
+        <v>0.01047239367525252</v>
       </c>
       <c r="I874">
-        <v>0.1368410344329005</v>
+        <v>0.1308752297936504</v>
       </c>
       <c r="J874">
         <v>1.280683907215004</v>
@@ -45502,10 +45502,10 @@
         <v>6</v>
       </c>
       <c r="M874">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N874">
-        <v>6.06</v>
+        <v>5.99</v>
       </c>
       <c r="O874">
         <v>1</v>
@@ -45528,7 +45528,7 @@
         <v>345</v>
       </c>
       <c r="E875">
-        <v>1.513572129386736</v>
+        <v>1.507606324747486</v>
       </c>
       <c r="F875">
         <v>1</v>
@@ -45537,10 +45537,10 @@
         <v>0.01038800735339681</v>
       </c>
       <c r="H875">
-        <v>0.01060642787061326</v>
+        <v>0.01047239367525252</v>
       </c>
       <c r="I875">
-        <v>0.1415794827835501</v>
+        <v>0.1356136781443</v>
       </c>
       <c r="J875">
         <v>1.280683907215004</v>
@@ -45552,10 +45552,10 @@
         <v>5.88</v>
       </c>
       <c r="M875">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N875">
-        <v>6.06</v>
+        <v>5.99</v>
       </c>
       <c r="O875">
         <v>1</v>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -1036,7 +1036,7 @@
     <t>2021-11-18</t>
   </si>
   <si>
-    <t>2021-11-23</t>
+    <t>2021-11-24</t>
   </si>
   <si>
     <t>2021-10-21</t>
@@ -44298,7 +44298,7 @@
         <v>340</v>
       </c>
       <c r="E851">
-        <v>1.206143889104274</v>
+        <v>1.182404455029051</v>
       </c>
       <c r="F851">
         <v>1</v>
@@ -44307,10 +44307,10 @@
         <v>0.01086820469608378</v>
       </c>
       <c r="H851">
-        <v>0.01105385611089573</v>
+        <v>0.01097759554497095</v>
       </c>
       <c r="I851">
-        <v>0.05434858518805807</v>
+        <v>0.03060915111283524</v>
       </c>
       <c r="J851">
         <v>1.31302829623886</v>
@@ -44322,10 +44322,10 @@
         <v>6.01</v>
       </c>
       <c r="M851">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="N851">
-        <v>6.13</v>
+        <v>6.08</v>
       </c>
       <c r="O851">
         <v>1</v>
@@ -44398,7 +44398,7 @@
         <v>340</v>
       </c>
       <c r="E853">
-        <v>1.2019565074568</v>
+        <v>1.178239406083698</v>
       </c>
       <c r="F853">
         <v>1</v>
@@ -44407,10 +44407,10 @@
         <v>0.01087233624597596</v>
       </c>
       <c r="H853">
-        <v>0.0110580434925432</v>
+        <v>0.0109817605939163</v>
       </c>
       <c r="I853">
-        <v>0.0542927534327573</v>
+        <v>0.03057565205965496</v>
       </c>
       <c r="J853">
         <v>1.314144931344853</v>
@@ -44422,10 +44422,10 @@
         <v>6.01</v>
       </c>
       <c r="M853">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="N853">
-        <v>6.13</v>
+        <v>6.08</v>
       </c>
       <c r="O853">
         <v>1</v>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -1036,7 +1036,7 @@
     <t>2021-11-18</t>
   </si>
   <si>
-    <t>2021-11-24</t>
+    <t>2021-11-25</t>
   </si>
   <si>
     <t>2021-10-21</t>
@@ -44298,7 +44298,7 @@
         <v>340</v>
       </c>
       <c r="E851">
-        <v>1.182404455029051</v>
+        <v>1.106143889104274</v>
       </c>
       <c r="F851">
         <v>1</v>
@@ -44307,10 +44307,10 @@
         <v>0.01086820469608378</v>
       </c>
       <c r="H851">
-        <v>0.01097759554497095</v>
+        <v>0.01095385611089573</v>
       </c>
       <c r="I851">
-        <v>0.03060915111283524</v>
+        <v>-0.04565141481194157</v>
       </c>
       <c r="J851">
         <v>1.31302829623886</v>
@@ -44322,10 +44322,10 @@
         <v>6.01</v>
       </c>
       <c r="M851">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="N851">
-        <v>6.08</v>
+        <v>6.03</v>
       </c>
       <c r="O851">
         <v>1</v>
@@ -44398,7 +44398,7 @@
         <v>340</v>
       </c>
       <c r="E853">
-        <v>1.178239406083698</v>
+        <v>1.101956507456801</v>
       </c>
       <c r="F853">
         <v>1</v>
@@ -44407,10 +44407,10 @@
         <v>0.01087233624597596</v>
       </c>
       <c r="H853">
-        <v>0.0109817605939163</v>
+        <v>0.0109580434925432</v>
       </c>
       <c r="I853">
-        <v>0.03057565205965496</v>
+        <v>-0.04570724656724234</v>
       </c>
       <c r="J853">
         <v>1.314144931344853</v>
@@ -44422,10 +44422,10 @@
         <v>6.01</v>
       </c>
       <c r="M853">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="N853">
-        <v>6.08</v>
+        <v>6.03</v>
       </c>
       <c r="O853">
         <v>1</v>

--- a/s60_signal/position-01766-601766.xlsx
+++ b/s60_signal/position-01766-601766.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2562" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2562" uniqueCount="471">
   <si>
     <t>trade_time</t>
   </si>
@@ -1034,6 +1034,9 @@
   </si>
   <si>
     <t>2021-11-29</t>
+  </si>
+  <si>
+    <t>2021-11-30</t>
   </si>
   <si>
     <t>2016-07-28</t>
@@ -1878,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1928,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1978,7 +1981,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2028,7 +2031,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2078,7 +2081,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2128,7 +2131,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2178,7 +2181,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2228,7 +2231,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2278,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2328,7 +2331,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2428,7 +2431,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2478,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2528,7 +2531,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2578,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2628,7 +2631,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2678,7 +2681,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2928,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2978,7 +2981,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3028,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3078,7 +3081,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3328,7 +3331,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3378,7 +3381,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3428,7 +3431,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3478,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3528,7 +3531,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3778,7 +3781,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3828,7 +3831,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3878,7 +3881,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3928,7 +3931,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3978,7 +3981,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4028,7 +4031,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4078,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4278,7 +4281,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4328,7 +4331,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4378,7 +4381,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4428,7 +4431,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4478,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4528,7 +4531,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4578,7 +4581,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4628,7 +4631,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4678,7 +4681,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4728,7 +4731,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4778,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4828,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4878,7 +4881,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4928,7 +4931,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4978,7 +4981,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5028,7 +5031,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5078,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5128,7 +5131,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5178,7 +5181,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5228,7 +5231,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5278,7 +5281,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5328,7 +5331,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5928,7 +5931,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5978,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6028,7 +6031,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6078,7 +6081,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6128,7 +6131,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6178,7 +6181,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6228,7 +6231,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6378,7 +6381,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6978,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7028,7 +7031,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7078,7 +7081,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7128,7 +7131,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7178,7 +7181,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7378,7 +7381,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7428,7 +7431,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7478,7 +7481,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7678,7 +7681,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7728,7 +7731,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7778,7 +7781,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7828,7 +7831,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7878,7 +7881,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7928,7 +7931,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7978,7 +7981,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8028,7 +8031,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8078,7 +8081,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -8278,7 +8281,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8328,7 +8331,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8378,7 +8381,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8428,7 +8431,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8478,7 +8481,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8528,7 +8531,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8578,7 +8581,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8628,7 +8631,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8678,7 +8681,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8728,7 +8731,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8778,7 +8781,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8828,7 +8831,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9078,7 +9081,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9128,7 +9131,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9178,7 +9181,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9228,7 +9231,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9278,7 +9281,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9578,7 +9581,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9628,7 +9631,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9678,7 +9681,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9728,7 +9731,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9778,7 +9781,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9828,7 +9831,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9878,7 +9881,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9928,7 +9931,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9978,7 +9981,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10028,7 +10031,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10078,7 +10081,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10478,7 +10481,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10528,7 +10531,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10578,7 +10581,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10628,7 +10631,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11128,7 +11131,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11178,7 +11181,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11228,7 +11231,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11278,7 +11281,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11328,7 +11331,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11378,7 +11381,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11428,7 +11431,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11478,7 +11481,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11528,7 +11531,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11578,7 +11581,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11628,7 +11631,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11678,7 +11681,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11728,7 +11731,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11778,7 +11781,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11828,7 +11831,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11878,7 +11881,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11928,7 +11931,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11978,7 +11981,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12028,7 +12031,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12078,7 +12081,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12128,7 +12131,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12678,7 +12681,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12728,7 +12731,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12778,7 +12781,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12828,7 +12831,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12878,7 +12881,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12928,7 +12931,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12978,7 +12981,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -13028,7 +13031,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -13078,7 +13081,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -13128,7 +13131,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13178,7 +13181,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13228,7 +13231,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13278,7 +13281,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13328,7 +13331,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13378,7 +13381,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13428,7 +13431,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13478,7 +13481,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13528,7 +13531,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13578,7 +13581,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13778,7 +13781,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13828,7 +13831,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13878,7 +13881,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14278,7 +14281,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14328,7 +14331,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14378,7 +14381,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14428,7 +14431,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14678,7 +14681,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14728,7 +14731,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14778,7 +14781,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14828,7 +14831,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -15828,7 +15831,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15878,7 +15881,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15928,7 +15931,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15978,7 +15981,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -16028,7 +16031,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16078,7 +16081,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16128,7 +16131,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16178,7 +16181,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16228,7 +16231,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16278,7 +16281,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16328,7 +16331,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16378,7 +16381,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16428,7 +16431,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16478,7 +16481,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16528,7 +16531,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16578,7 +16581,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16628,7 +16631,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16928,7 +16931,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16978,7 +16981,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17028,7 +17031,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17078,7 +17081,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17128,7 +17131,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17178,7 +17181,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17228,7 +17231,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17278,7 +17281,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17328,7 +17331,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17378,7 +17381,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17428,7 +17431,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17478,7 +17481,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17528,7 +17531,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17578,7 +17581,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17878,7 +17881,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17928,7 +17931,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17978,7 +17981,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18028,7 +18031,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -18078,7 +18081,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18128,7 +18131,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18178,7 +18181,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18228,7 +18231,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18478,7 +18481,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18528,7 +18531,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18578,7 +18581,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18628,7 +18631,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18678,7 +18681,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18728,7 +18731,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18778,7 +18781,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18828,7 +18831,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18878,7 +18881,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18928,7 +18931,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -21078,7 +21081,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21128,7 +21131,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21178,7 +21181,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21228,7 +21231,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21278,7 +21281,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21328,7 +21331,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21378,7 +21381,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21428,7 +21431,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -24528,7 +24531,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24578,7 +24581,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24628,7 +24631,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24678,7 +24681,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24728,7 +24731,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24778,7 +24781,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24828,7 +24831,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24878,7 +24881,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24928,7 +24931,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24978,7 +24981,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25028,7 +25031,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25078,7 +25081,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25128,7 +25131,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25178,7 +25181,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25228,7 +25231,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25678,7 +25681,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25728,7 +25731,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25778,7 +25781,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25828,7 +25831,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26028,7 +26031,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26078,7 +26081,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26128,7 +26131,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26178,7 +26181,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26228,7 +26231,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26278,7 +26281,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26328,7 +26331,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26378,7 +26381,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26428,7 +26431,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26478,7 +26481,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26528,7 +26531,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26578,7 +26581,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27078,7 +27081,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27128,7 +27131,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27178,7 +27181,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27228,7 +27231,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27278,7 +27281,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27328,7 +27331,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27378,7 +27381,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27428,7 +27431,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27478,7 +27481,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27528,7 +27531,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28128,7 +28131,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28178,7 +28181,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28228,7 +28231,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28278,7 +28281,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28328,7 +28331,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28378,7 +28381,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28428,7 +28431,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28878,7 +28881,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28928,7 +28931,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29078,7 +29081,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29128,7 +29131,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29178,7 +29181,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29228,7 +29231,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29278,7 +29281,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29328,7 +29331,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -32278,7 +32281,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32328,7 +32331,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32378,7 +32381,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32428,7 +32431,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32478,7 +32481,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32528,7 +32531,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32578,7 +32581,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -32628,7 +32631,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -32678,7 +32681,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -32728,7 +32731,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -32778,7 +32781,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -32828,7 +32831,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -32878,7 +32881,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -32928,7 +32931,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -32978,7 +32981,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33028,7 +33031,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33078,7 +33081,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33128,7 +33131,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33178,7 +33181,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33378,7 +33381,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33428,7 +33431,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33478,7 +33481,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33528,7 +33531,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33578,7 +33581,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -33628,7 +33631,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -33678,7 +33681,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -33728,7 +33731,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -33778,7 +33781,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -33828,7 +33831,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -33878,7 +33881,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -33928,7 +33931,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -33978,7 +33981,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34028,7 +34031,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34078,7 +34081,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34128,7 +34131,7 @@
         <v>1</v>
       </c>
       <c r="P647" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34178,7 +34181,7 @@
         <v>1</v>
       </c>
       <c r="P648" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34228,7 +34231,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34278,7 +34281,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34328,7 +34331,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34378,7 +34381,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34628,7 +34631,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -34678,7 +34681,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -34728,7 +34731,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -34778,7 +34781,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -34828,7 +34831,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -34878,7 +34881,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -34928,7 +34931,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -34978,7 +34981,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35028,7 +35031,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35078,7 +35081,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35128,7 +35131,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35178,7 +35181,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35228,7 +35231,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35278,7 +35281,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35328,7 +35331,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35378,7 +35381,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35428,7 +35431,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35478,7 +35481,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35528,7 +35531,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35578,7 +35581,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -35628,7 +35631,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -35678,7 +35681,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -35728,7 +35731,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -35778,7 +35781,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -35828,7 +35831,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -35878,7 +35881,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -35928,7 +35931,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -35978,7 +35981,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36028,7 +36031,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36078,7 +36081,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36128,7 +36131,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36178,7 +36181,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36228,7 +36231,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36278,7 +36281,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36328,7 +36331,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36378,7 +36381,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36428,7 +36431,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36478,7 +36481,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36528,7 +36531,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36578,7 +36581,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -36628,7 +36631,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -36678,7 +36681,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -36728,7 +36731,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -36778,7 +36781,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -36828,7 +36831,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -36878,7 +36881,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -36928,7 +36931,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -36978,7 +36981,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37178,7 +37181,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37228,7 +37231,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37278,7 +37281,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37378,7 +37381,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37428,7 +37431,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37478,7 +37481,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37528,7 +37531,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37578,7 +37581,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -37628,7 +37631,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -37678,7 +37681,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -37728,7 +37731,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -37778,7 +37781,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -37828,7 +37831,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -37878,7 +37881,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -37928,7 +37931,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -37978,7 +37981,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38028,7 +38031,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38078,7 +38081,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38128,7 +38131,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38178,7 +38181,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38228,7 +38231,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38278,7 +38281,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38328,7 +38331,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38378,7 +38381,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38428,7 +38431,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38478,7 +38481,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38528,7 +38531,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38578,7 +38581,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38878,7 +38881,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -38928,7 +38931,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -38978,7 +38981,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39028,7 +39031,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39178,7 +39181,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39228,7 +39231,7 @@
         <v>1</v>
       </c>
       <c r="P749" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39378,7 +39381,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39428,7 +39431,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39478,7 +39481,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39528,7 +39531,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39578,7 +39581,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39778,7 +39781,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -39828,7 +39831,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -39878,7 +39881,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -39928,7 +39931,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -39978,7 +39981,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40028,7 +40031,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40078,7 +40081,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -40128,7 +40131,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40178,7 +40181,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40528,7 +40531,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40578,7 +40581,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40628,7 +40631,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -40828,7 +40831,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -40878,7 +40881,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -40928,7 +40931,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -40978,7 +40981,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41028,7 +41031,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41078,7 +41081,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41228,7 +41231,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41278,7 +41281,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41328,7 +41331,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41378,7 +41381,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41428,7 +41431,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41678,7 +41681,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -41728,7 +41731,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -41778,7 +41781,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -41828,7 +41831,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42128,7 +42131,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42178,7 +42181,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42228,7 +42231,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42278,7 +42281,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42428,7 +42431,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42478,7 +42481,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42528,7 +42531,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42578,7 +42581,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43028,7 +43031,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43078,7 +43081,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43428,7 +43431,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43478,7 +43481,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43628,7 +43631,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43678,7 +43681,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -43728,7 +43731,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -43778,7 +43781,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -43828,7 +43831,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -43878,7 +43881,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -43928,7 +43931,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -43978,7 +43981,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44028,7 +44031,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44078,7 +44081,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44128,7 +44131,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44178,7 +44181,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44192,10 +44195,10 @@
         <v>1.147663754024043</v>
       </c>
       <c r="D849" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E849">
-        <v>1.232219696471978</v>
+        <v>1.543058537546807</v>
       </c>
       <c r="F849">
         <v>1</v>
@@ -44204,10 +44207,10 @@
         <v>0.01087233624597596</v>
       </c>
       <c r="H849">
-        <v>0.01066778030352802</v>
+        <v>0.01063694146245319</v>
       </c>
       <c r="I849">
-        <v>0.08455594244793474</v>
+        <v>0.3953947835227645</v>
       </c>
       <c r="J849">
         <v>1.314144931344853</v>
@@ -44219,16 +44222,16 @@
         <v>6.01</v>
       </c>
       <c r="M849">
-        <v>3.59</v>
+        <v>3.46</v>
       </c>
       <c r="N849">
-        <v>5.95</v>
+        <v>6.09</v>
       </c>
       <c r="O849">
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44242,10 +44245,10 @@
         <v>1.101956507456801</v>
       </c>
       <c r="D850" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E850">
-        <v>1.232219696471978</v>
+        <v>1.543058537546807</v>
       </c>
       <c r="F850">
         <v>1</v>
@@ -44254,10 +44257,10 @@
         <v>0.0109580434925432</v>
       </c>
       <c r="H850">
-        <v>0.01066778030352802</v>
+        <v>0.01063694146245319</v>
       </c>
       <c r="I850">
-        <v>0.1302631890151771</v>
+        <v>0.4411020300900068</v>
       </c>
       <c r="J850">
         <v>1.314144931344853</v>
@@ -44269,16 +44272,16 @@
         <v>6.03</v>
       </c>
       <c r="M850">
-        <v>3.59</v>
+        <v>3.46</v>
       </c>
       <c r="N850">
-        <v>5.95</v>
+        <v>6.09</v>
       </c>
       <c r="O850">
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
